--- a/documents/GameDev_Priority_Scoring (2).xlsx
+++ b/documents/GameDev_Priority_Scoring (2).xlsx
@@ -7,30 +7,60 @@
     <sheet state="visible" name="Скоринг" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'GameDev Priority'!$A$1:$I$18</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'GameDev Priority'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="Xbtw11L5K0b2B7xTiAjj+EgulL72IZOHvsN96sI+3Fs="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="Ip884DpSOA0bxAeXGcGuAnn3tvXNlDU0DwV1UNPohOc="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="77">
+  <si>
+    <t>Задача</t>
+  </si>
+  <si>
+    <t>Категория</t>
+  </si>
+  <si>
+    <t>Приближение к релизу</t>
+  </si>
+  <si>
+    <t>Удобство геймплея</t>
+  </si>
+  <si>
+    <t>Ценность контента</t>
+  </si>
+  <si>
+    <t>Удержание</t>
+  </si>
+  <si>
+    <t>Итого</t>
+  </si>
   <si>
     <t>Критерий</t>
   </si>
   <si>
-    <t>Задача</t>
+    <t>Статус</t>
+  </si>
+  <si>
+    <t>Сложность</t>
+  </si>
+  <si>
+    <t>Сделать пресс-релиз</t>
   </si>
   <si>
     <t>Вес</t>
   </si>
   <si>
     <t>0</t>
+  </si>
+  <si>
+    <t>Герои - мета</t>
   </si>
   <si>
     <t>1</t>
@@ -42,61 +72,37 @@
     <t>3</t>
   </si>
   <si>
-    <t>Категория</t>
-  </si>
-  <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>Приближение к релизу</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>Удобство геймплея</t>
+    <t>Нужно для Vertical Slice</t>
   </si>
   <si>
-    <t>Ценность контента</t>
-  </si>
-  <si>
-    <t>Удержание</t>
+    <t>Не влияет</t>
   </si>
   <si>
     <t>40%</t>
   </si>
   <si>
-    <t>Не влияет</t>
-  </si>
-  <si>
-    <t>Итого</t>
+    <t>Фундаментальная механика</t>
   </si>
   <si>
     <t>Небольшое улучшение</t>
   </si>
   <si>
-    <t>Второстепенная функция</t>
+    <t>Критично для удержания</t>
   </si>
   <si>
-    <t>Статус</t>
-  </si>
-  <si>
-    <t>Сложность</t>
+    <t>Второстепенная функция</t>
   </si>
   <si>
     <t>Важная система</t>
   </si>
   <si>
-    <t>Нужно для Vertical Slice</t>
-  </si>
-  <si>
-    <t>Сделать пресс-релиз</t>
-  </si>
-  <si>
     <t>Без этого релиз невозможен</t>
-  </si>
-  <si>
-    <t>Герои - мета</t>
   </si>
   <si>
     <t>25%</t>
@@ -132,9 +138,6 @@
     <t>Крупная система</t>
   </si>
   <si>
-    <t>Фундаментальная механика</t>
-  </si>
-  <si>
     <t>15%</t>
   </si>
   <si>
@@ -148,9 +151,6 @@
   </si>
   <si>
     <t>Сильно повышает интерес</t>
-  </si>
-  <si>
-    <t>Критично для удержания</t>
   </si>
   <si>
     <t>Справочно, не входит в Итого</t>
@@ -178,12 +178,6 @@
   </si>
   <si>
     <t xml:space="preserve">Оптимизация </t>
-  </si>
-  <si>
-    <t>Когда мы накапливаем предметы мы нажимаем "merge" и тогда можем мержить предметы за ману. Новая механика которая расширяет возможности слияния предметов используя упрощенные, популярные merge 2 механики</t>
-  </si>
-  <si>
-    <t>Новая фича</t>
   </si>
   <si>
     <r>
@@ -337,17 +331,16 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -357,6 +350,7 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -378,11 +372,11 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -634,81 +628,81 @@
   </cols>
   <sheetData>
     <row r="1" ht="79.5" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="2" t="s">
+    </row>
+    <row r="2" ht="79.5" customHeight="1">
+      <c r="A2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="D2" s="7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" ht="79.5" customHeight="1">
-      <c r="A2" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>43</v>
+      <c r="F2" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="G2" s="9">
         <f>IF(C2&amp;D2&amp;E2&amp;F2="", "", (IFNA(MATCH(C2, 'Скоринг'!$C$2:$H$2, 0)-1, 0) * 'Скоринг'!$B$2) + (IFNA(MATCH(D2, 'Скоринг'!$C$3:$H$3, 0)-1, 0) * 'Скоринг'!$B$3) + (IFNA(MATCH(E2, 'Скоринг'!$C$4:$H$4, 0)-1, 0) * 'Скоринг'!$B$4) + (IFNA(MATCH(F2, 'Скоринг'!$C$5:$H$5, 0)-1, 0) * 'Скоринг'!$B$5))</f>
         <v>3.35</v>
       </c>
       <c r="H2" s="9" t="str">
-        <f t="shared" ref="H2:H18" si="1">IF(G2="","",IFS(G2&gt;=4,"🔥 Высокий",G2&gt;=2.5,"⚡ Средний",TRUE,"💤 Низкий"))</f>
+        <f t="shared" ref="H2:H17" si="1">IF(G2="","",IFS(G2&gt;=4,"🔥 Высокий",G2&gt;=2.5,"⚡ Средний",TRUE,"💤 Низкий"))</f>
         <v>⚡ Средний</v>
       </c>
       <c r="I2" s="10">
         <v>4.0</v>
       </c>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
-      <c r="Z2" s="7"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
     </row>
     <row r="3" ht="79.5" customHeight="1">
       <c r="A3" s="11" t="s">
@@ -718,16 +712,16 @@
         <v>52</v>
       </c>
       <c r="C3" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="14" t="s">
         <v>24</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="14" t="s">
-        <v>43</v>
       </c>
       <c r="G3" s="15">
         <f>IF(C3&amp;D3&amp;E3&amp;F3="", "", (IFNA(MATCH(C3, 'Скоринг'!$C$2:$H$2, 0)-1, 0) * 'Скоринг'!$B$2) + (IFNA(MATCH(D3, 'Скоринг'!$C$3:$H$3, 0)-1, 0) * 'Скоринг'!$B$3) + (IFNA(MATCH(E3, 'Скоринг'!$C$4:$H$4, 0)-1, 0) * 'Скоринг'!$B$4) + (IFNA(MATCH(F3, 'Скоринг'!$C$5:$H$5, 0)-1, 0) * 'Скоринг'!$B$5))</f>
@@ -749,51 +743,51 @@
         <v>54</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>30</v>
+        <v>27</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>32</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="G4" s="15">
         <f>IF(C4&amp;D4&amp;E4&amp;F4="", "", (IFNA(MATCH(C4, 'Скоринг'!$C$2:$H$2, 0)-1, 0) * 'Скоринг'!$B$2) + (IFNA(MATCH(D4, 'Скоринг'!$C$3:$H$3, 0)-1, 0) * 'Скоринг'!$B$3) + (IFNA(MATCH(E4, 'Скоринг'!$C$4:$H$4, 0)-1, 0) * 'Скоринг'!$B$4) + (IFNA(MATCH(F4, 'Скоринг'!$C$5:$H$5, 0)-1, 0) * 'Скоринг'!$B$5))</f>
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="H4" s="15" t="str">
         <f t="shared" si="1"/>
         <v>🔥 Высокий</v>
       </c>
       <c r="I4" s="15">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="5" ht="79.5" customHeight="1">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="11" t="s">
         <v>55</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C5" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="14" t="s">
         <v>24</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>43</v>
       </c>
       <c r="G5" s="15">
         <f>IF(C5&amp;D5&amp;E5&amp;F5="", "", (IFNA(MATCH(C5, 'Скоринг'!$C$2:$H$2, 0)-1, 0) * 'Скоринг'!$B$2) + (IFNA(MATCH(D5, 'Скоринг'!$C$3:$H$3, 0)-1, 0) * 'Скоринг'!$B$3) + (IFNA(MATCH(E5, 'Скоринг'!$C$4:$H$4, 0)-1, 0) * 'Скоринг'!$B$4) + (IFNA(MATCH(F5, 'Скоринг'!$C$5:$H$5, 0)-1, 0) * 'Скоринг'!$B$5))</f>
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="H5" s="15" t="str">
         <f t="shared" si="1"/>
@@ -804,178 +798,178 @@
       </c>
     </row>
     <row r="6" ht="79.5" customHeight="1">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>52</v>
-      </c>
       <c r="C6" s="14" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="G6" s="15">
         <f>IF(C6&amp;D6&amp;E6&amp;F6="", "", (IFNA(MATCH(C6, 'Скоринг'!$C$2:$H$2, 0)-1, 0) * 'Скоринг'!$B$2) + (IFNA(MATCH(D6, 'Скоринг'!$C$3:$H$3, 0)-1, 0) * 'Скоринг'!$B$3) + (IFNA(MATCH(E6, 'Скоринг'!$C$4:$H$4, 0)-1, 0) * 'Скоринг'!$B$4) + (IFNA(MATCH(F6, 'Скоринг'!$C$5:$H$5, 0)-1, 0) * 'Скоринг'!$B$5))</f>
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="H6" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>🔥 Высокий</v>
+        <v>⚡ Средний</v>
       </c>
       <c r="I6" s="15">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="7" ht="79.5" customHeight="1">
-      <c r="A7" s="16" t="s">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="7" ht="140.25" customHeight="1">
+      <c r="A7" s="17" t="s">
         <v>58</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F7" s="14" t="s">
         <v>43</v>
       </c>
       <c r="G7" s="15">
         <f>IF(C7&amp;D7&amp;E7&amp;F7="", "", (IFNA(MATCH(C7, 'Скоринг'!$C$2:$H$2, 0)-1, 0) * 'Скоринг'!$B$2) + (IFNA(MATCH(D7, 'Скоринг'!$C$3:$H$3, 0)-1, 0) * 'Скоринг'!$B$3) + (IFNA(MATCH(E7, 'Скоринг'!$C$4:$H$4, 0)-1, 0) * 'Скоринг'!$B$4) + (IFNA(MATCH(F7, 'Скоринг'!$C$5:$H$5, 0)-1, 0) * 'Скоринг'!$B$5))</f>
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="H7" s="15" t="str">
         <f t="shared" si="1"/>
         <v>⚡ Средний</v>
       </c>
       <c r="I7" s="15">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="8" ht="140.25" customHeight="1">
-      <c r="A8" s="16" t="s">
-        <v>60</v>
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="8" ht="79.5" customHeight="1">
+      <c r="A8" s="17" t="s">
+        <v>59</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G8" s="15">
         <f>IF(C8&amp;D8&amp;E8&amp;F8="", "", (IFNA(MATCH(C8, 'Скоринг'!$C$2:$H$2, 0)-1, 0) * 'Скоринг'!$B$2) + (IFNA(MATCH(D8, 'Скоринг'!$C$3:$H$3, 0)-1, 0) * 'Скоринг'!$B$3) + (IFNA(MATCH(E8, 'Скоринг'!$C$4:$H$4, 0)-1, 0) * 'Скоринг'!$B$4) + (IFNA(MATCH(F8, 'Скоринг'!$C$5:$H$5, 0)-1, 0) * 'Скоринг'!$B$5))</f>
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="H8" s="15" t="str">
         <f t="shared" si="1"/>
         <v>⚡ Средний</v>
       </c>
-      <c r="I8" s="15">
-        <v>4.0</v>
+      <c r="I8" s="18">
+        <v>1.0</v>
       </c>
     </row>
     <row r="9" ht="79.5" customHeight="1">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="14" t="s">
+      <c r="C9" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="9">
         <f>IF(C9&amp;D9&amp;E9&amp;F9="", "", (IFNA(MATCH(C9, 'Скоринг'!$C$2:$H$2, 0)-1, 0) * 'Скоринг'!$B$2) + (IFNA(MATCH(D9, 'Скоринг'!$C$3:$H$3, 0)-1, 0) * 'Скоринг'!$B$3) + (IFNA(MATCH(E9, 'Скоринг'!$C$4:$H$4, 0)-1, 0) * 'Скоринг'!$B$4) + (IFNA(MATCH(F9, 'Скоринг'!$C$5:$H$5, 0)-1, 0) * 'Скоринг'!$B$5))</f>
-        <v>3.15</v>
-      </c>
-      <c r="H9" s="15" t="str">
+        <v>3.05</v>
+      </c>
+      <c r="H9" s="9" t="str">
         <f t="shared" si="1"/>
         <v>⚡ Средний</v>
       </c>
-      <c r="I9" s="18">
-        <v>1.0</v>
+      <c r="I9" s="9">
+        <v>2.0</v>
       </c>
     </row>
     <row r="10" ht="79.5" customHeight="1">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" s="9">
+      <c r="C10" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="15">
         <f>IF(C10&amp;D10&amp;E10&amp;F10="", "", (IFNA(MATCH(C10, 'Скоринг'!$C$2:$H$2, 0)-1, 0) * 'Скоринг'!$B$2) + (IFNA(MATCH(D10, 'Скоринг'!$C$3:$H$3, 0)-1, 0) * 'Скоринг'!$B$3) + (IFNA(MATCH(E10, 'Скоринг'!$C$4:$H$4, 0)-1, 0) * 'Скоринг'!$B$4) + (IFNA(MATCH(F10, 'Скоринг'!$C$5:$H$5, 0)-1, 0) * 'Скоринг'!$B$5))</f>
-        <v>3.05</v>
-      </c>
-      <c r="H10" s="9" t="str">
+        <v>3</v>
+      </c>
+      <c r="H10" s="15" t="str">
         <f t="shared" si="1"/>
         <v>⚡ Средний</v>
       </c>
-      <c r="I10" s="9">
-        <v>2.0</v>
+      <c r="I10" s="15">
+        <v>5.0</v>
       </c>
     </row>
     <row r="11" ht="79.5" customHeight="1">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="17" t="s">
         <v>64</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>65</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G11" s="15">
         <f>IF(C11&amp;D11&amp;E11&amp;F11="", "", (IFNA(MATCH(C11, 'Скоринг'!$C$2:$H$2, 0)-1, 0) * 'Скоринг'!$B$2) + (IFNA(MATCH(D11, 'Скоринг'!$C$3:$H$3, 0)-1, 0) * 'Скоринг'!$B$3) + (IFNA(MATCH(E11, 'Скоринг'!$C$4:$H$4, 0)-1, 0) * 'Скоринг'!$B$4) + (IFNA(MATCH(F11, 'Скоринг'!$C$5:$H$5, 0)-1, 0) * 'Скоринг'!$B$5))</f>
@@ -986,27 +980,27 @@
         <v>⚡ Средний</v>
       </c>
       <c r="I11" s="15">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="12" ht="79.5" customHeight="1">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="17" t="s">
         <v>66</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G12" s="15">
         <f>IF(C12&amp;D12&amp;E12&amp;F12="", "", (IFNA(MATCH(C12, 'Скоринг'!$C$2:$H$2, 0)-1, 0) * 'Скоринг'!$B$2) + (IFNA(MATCH(D12, 'Скоринг'!$C$3:$H$3, 0)-1, 0) * 'Скоринг'!$B$3) + (IFNA(MATCH(E12, 'Скоринг'!$C$4:$H$4, 0)-1, 0) * 'Скоринг'!$B$4) + (IFNA(MATCH(F12, 'Скоринг'!$C$5:$H$5, 0)-1, 0) * 'Скоринг'!$B$5))</f>
@@ -1017,31 +1011,48 @@
         <v>⚡ Средний</v>
       </c>
       <c r="I12" s="15">
-        <v>4.0</v>
-      </c>
+        <v>2.0</v>
+      </c>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="19"/>
+      <c r="Y12" s="19"/>
+      <c r="Z12" s="19"/>
     </row>
     <row r="13" ht="79.5" customHeight="1">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>56</v>
-      </c>
       <c r="C13" s="14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" s="14" t="s">
         <v>41</v>
       </c>
       <c r="G13" s="15">
         <f>IF(C13&amp;D13&amp;E13&amp;F13="", "", (IFNA(MATCH(C13, 'Скоринг'!$C$2:$H$2, 0)-1, 0) * 'Скоринг'!$B$2) + (IFNA(MATCH(D13, 'Скоринг'!$C$3:$H$3, 0)-1, 0) * 'Скоринг'!$B$3) + (IFNA(MATCH(E13, 'Скоринг'!$C$4:$H$4, 0)-1, 0) * 'Скоринг'!$B$4) + (IFNA(MATCH(F13, 'Скоринг'!$C$5:$H$5, 0)-1, 0) * 'Скоринг'!$B$5))</f>
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="H13" s="15" t="str">
         <f t="shared" si="1"/>
@@ -1050,190 +1061,190 @@
       <c r="I13" s="15">
         <v>2.0</v>
       </c>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="19"/>
-      <c r="Q13" s="19"/>
-      <c r="R13" s="19"/>
-      <c r="S13" s="19"/>
-      <c r="T13" s="19"/>
-      <c r="U13" s="19"/>
-      <c r="V13" s="19"/>
-      <c r="W13" s="19"/>
-      <c r="X13" s="19"/>
-      <c r="Y13" s="19"/>
-      <c r="Z13" s="19"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="6"/>
+      <c r="T13" s="6"/>
+      <c r="U13" s="6"/>
+      <c r="V13" s="6"/>
+      <c r="W13" s="6"/>
+      <c r="X13" s="6"/>
+      <c r="Y13" s="6"/>
+      <c r="Z13" s="6"/>
     </row>
     <row r="14" ht="79.5" customHeight="1">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="B14" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="G14" s="15">
+      <c r="B14" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" s="9">
         <f>IF(C14&amp;D14&amp;E14&amp;F14="", "", (IFNA(MATCH(C14, 'Скоринг'!$C$2:$H$2, 0)-1, 0) * 'Скоринг'!$B$2) + (IFNA(MATCH(D14, 'Скоринг'!$C$3:$H$3, 0)-1, 0) * 'Скоринг'!$B$3) + (IFNA(MATCH(E14, 'Скоринг'!$C$4:$H$4, 0)-1, 0) * 'Скоринг'!$B$4) + (IFNA(MATCH(F14, 'Скоринг'!$C$5:$H$5, 0)-1, 0) * 'Скоринг'!$B$5))</f>
         <v>2.8</v>
       </c>
-      <c r="H14" s="15" t="str">
+      <c r="H14" s="9" t="str">
         <f t="shared" si="1"/>
         <v>⚡ Средний</v>
       </c>
-      <c r="I14" s="15">
-        <v>2.0</v>
-      </c>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="7"/>
-      <c r="R14" s="7"/>
-      <c r="S14" s="7"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="7"/>
-      <c r="V14" s="7"/>
-      <c r="W14" s="7"/>
-      <c r="X14" s="7"/>
-      <c r="Y14" s="7"/>
-      <c r="Z14" s="7"/>
+      <c r="I14" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="6"/>
+      <c r="U14" s="6"/>
+      <c r="V14" s="6"/>
+      <c r="W14" s="6"/>
+      <c r="X14" s="6"/>
+      <c r="Y14" s="6"/>
+      <c r="Z14" s="6"/>
     </row>
     <row r="15" ht="79.5" customHeight="1">
-      <c r="A15" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F15" s="7" t="s">
+      <c r="A15" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="15">
         <f>IF(C15&amp;D15&amp;E15&amp;F15="", "", (IFNA(MATCH(C15, 'Скоринг'!$C$2:$H$2, 0)-1, 0) * 'Скоринг'!$B$2) + (IFNA(MATCH(D15, 'Скоринг'!$C$3:$H$3, 0)-1, 0) * 'Скоринг'!$B$3) + (IFNA(MATCH(E15, 'Скоринг'!$C$4:$H$4, 0)-1, 0) * 'Скоринг'!$B$4) + (IFNA(MATCH(F15, 'Скоринг'!$C$5:$H$5, 0)-1, 0) * 'Скоринг'!$B$5))</f>
-        <v>2.8</v>
-      </c>
-      <c r="H15" s="9" t="str">
+        <v>2.6</v>
+      </c>
+      <c r="H15" s="15" t="str">
         <f t="shared" si="1"/>
         <v>⚡ Средний</v>
       </c>
-      <c r="I15" s="9">
-        <v>1.0</v>
-      </c>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="7"/>
-      <c r="V15" s="7"/>
-      <c r="W15" s="7"/>
-      <c r="X15" s="7"/>
-      <c r="Y15" s="7"/>
-      <c r="Z15" s="7"/>
+      <c r="I15" s="15">
+        <v>3.0</v>
+      </c>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="6"/>
+      <c r="T15" s="6"/>
+      <c r="U15" s="6"/>
+      <c r="V15" s="6"/>
+      <c r="W15" s="6"/>
+      <c r="X15" s="6"/>
+      <c r="Y15" s="6"/>
+      <c r="Z15" s="6"/>
     </row>
     <row r="16" ht="79.5" customHeight="1">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" s="14" t="s">
+      <c r="C16" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="9">
+        <f>IF(C16&amp;D16&amp;E16&amp;F16="", "", (IFNA(MATCH(C16, 'Скоринг'!$C$2:$H$2, 0)-1, 0) * 'Скоринг'!$B$2) + (IFNA(MATCH(D16, 'Скоринг'!$C$3:$H$3, 0)-1, 0) * 'Скоринг'!$B$3) + (IFNA(MATCH(E16, 'Скоринг'!$C$4:$H$4, 0)-1, 0) * 'Скоринг'!$B$4) + (IFNA(MATCH(F16, 'Скоринг'!$C$5:$H$5, 0)-1, 0) * 'Скоринг'!$B$5))</f>
+        <v>1.9</v>
+      </c>
+      <c r="H16" s="9" t="str">
+        <f t="shared" si="1"/>
+        <v>💤 Низкий</v>
+      </c>
+      <c r="I16" s="9">
+        <v>2.0</v>
+      </c>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="6"/>
+      <c r="R16" s="6"/>
+      <c r="S16" s="6"/>
+      <c r="T16" s="6"/>
+      <c r="U16" s="6"/>
+      <c r="V16" s="6"/>
+      <c r="W16" s="6"/>
+      <c r="X16" s="6"/>
+      <c r="Y16" s="6"/>
+      <c r="Z16" s="6"/>
+    </row>
+    <row r="17" ht="153.0" customHeight="1">
+      <c r="A17" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="G16" s="15">
-        <f>IF(C16&amp;D16&amp;E16&amp;F16="", "", (IFNA(MATCH(C16, 'Скоринг'!$C$2:$H$2, 0)-1, 0) * 'Скоринг'!$B$2) + (IFNA(MATCH(D16, 'Скоринг'!$C$3:$H$3, 0)-1, 0) * 'Скоринг'!$B$3) + (IFNA(MATCH(E16, 'Скоринг'!$C$4:$H$4, 0)-1, 0) * 'Скоринг'!$B$4) + (IFNA(MATCH(F16, 'Скоринг'!$C$5:$H$5, 0)-1, 0) * 'Скоринг'!$B$5))</f>
-        <v>2.6</v>
-      </c>
-      <c r="H16" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v>⚡ Средний</v>
-      </c>
-      <c r="I16" s="15">
-        <v>3.0</v>
-      </c>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="7"/>
-      <c r="W16" s="7"/>
-      <c r="X16" s="7"/>
-      <c r="Y16" s="7"/>
-      <c r="Z16" s="7"/>
-    </row>
-    <row r="17" ht="79.5" customHeight="1">
-      <c r="A17" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>41</v>
       </c>
       <c r="G17" s="9">
         <f>IF(C17&amp;D17&amp;E17&amp;F17="", "", (IFNA(MATCH(C17, 'Скоринг'!$C$2:$H$2, 0)-1, 0) * 'Скоринг'!$B$2) + (IFNA(MATCH(D17, 'Скоринг'!$C$3:$H$3, 0)-1, 0) * 'Скоринг'!$B$3) + (IFNA(MATCH(E17, 'Скоринг'!$C$4:$H$4, 0)-1, 0) * 'Скоринг'!$B$4) + (IFNA(MATCH(F17, 'Скоринг'!$C$5:$H$5, 0)-1, 0) * 'Скоринг'!$B$5))</f>
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="H17" s="9" t="str">
         <f t="shared" si="1"/>
@@ -1242,75 +1253,40 @@
       <c r="I17" s="9">
         <v>2.0</v>
       </c>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="7"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="7"/>
-      <c r="W17" s="7"/>
-      <c r="X17" s="7"/>
-      <c r="Y17" s="7"/>
-      <c r="Z17" s="7"/>
-    </row>
-    <row r="18" ht="153.0" customHeight="1">
-      <c r="A18" s="20" t="s">
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="6"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="6"/>
+      <c r="T17" s="6"/>
+      <c r="U17" s="6"/>
+      <c r="V17" s="6"/>
+      <c r="W17" s="6"/>
+      <c r="X17" s="6"/>
+      <c r="Y17" s="6"/>
+      <c r="Z17" s="6"/>
+    </row>
+    <row r="18" ht="72.75" customHeight="1">
+      <c r="A18" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="12"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="8"/>
+    </row>
+    <row r="19" ht="41.25" customHeight="1">
+      <c r="A19" s="11" t="s">
         <v>75</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G18" s="9">
-        <f>IF(C18&amp;D18&amp;E18&amp;F18="", "", (IFNA(MATCH(C18, 'Скоринг'!$C$2:$H$2, 0)-1, 0) * 'Скоринг'!$B$2) + (IFNA(MATCH(D18, 'Скоринг'!$C$3:$H$3, 0)-1, 0) * 'Скоринг'!$B$3) + (IFNA(MATCH(E18, 'Скоринг'!$C$4:$H$4, 0)-1, 0) * 'Скоринг'!$B$4) + (IFNA(MATCH(F18, 'Скоринг'!$C$5:$H$5, 0)-1, 0) * 'Скоринг'!$B$5))</f>
-        <v>0.6</v>
-      </c>
-      <c r="H18" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v>💤 Низкий</v>
-      </c>
-      <c r="I18" s="9">
-        <v>2.0</v>
-      </c>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="7"/>
-      <c r="W18" s="7"/>
-      <c r="X18" s="7"/>
-      <c r="Y18" s="7"/>
-      <c r="Z18" s="7"/>
-    </row>
-    <row r="19" ht="72.75" customHeight="1">
-      <c r="A19" s="11" t="s">
-        <v>76</v>
       </c>
       <c r="B19" s="12"/>
       <c r="C19" s="21"/>
@@ -1319,11 +1295,11 @@
       <c r="F19" s="21"/>
       <c r="G19" s="22"/>
       <c r="H19" s="23"/>
-      <c r="I19" s="4"/>
-    </row>
-    <row r="20" ht="41.25" customHeight="1">
+      <c r="I19" s="8"/>
+    </row>
+    <row r="20" ht="77.25" customHeight="1">
       <c r="A20" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="21"/>
@@ -1332,12 +1308,10 @@
       <c r="F20" s="21"/>
       <c r="G20" s="22"/>
       <c r="H20" s="23"/>
-      <c r="I20" s="4"/>
-    </row>
-    <row r="21" ht="77.25" customHeight="1">
-      <c r="A21" s="11" t="s">
-        <v>78</v>
-      </c>
+      <c r="I20" s="8"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="17"/>
       <c r="B21" s="12"/>
       <c r="C21" s="21"/>
       <c r="D21" s="21"/>
@@ -1345,10 +1319,10 @@
       <c r="F21" s="21"/>
       <c r="G21" s="22"/>
       <c r="H21" s="23"/>
-      <c r="I21" s="4"/>
+      <c r="I21" s="8"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="16"/>
+      <c r="A22" s="17"/>
       <c r="B22" s="12"/>
       <c r="C22" s="21"/>
       <c r="D22" s="21"/>
@@ -1356,10 +1330,10 @@
       <c r="F22" s="21"/>
       <c r="G22" s="22"/>
       <c r="H22" s="23"/>
-      <c r="I22" s="4"/>
+      <c r="I22" s="8"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="16"/>
+      <c r="A23" s="17"/>
       <c r="B23" s="12"/>
       <c r="C23" s="21"/>
       <c r="D23" s="21"/>
@@ -1367,10 +1341,10 @@
       <c r="F23" s="21"/>
       <c r="G23" s="22"/>
       <c r="H23" s="23"/>
-      <c r="I23" s="4"/>
+      <c r="I23" s="8"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="16"/>
+      <c r="A24" s="17"/>
       <c r="B24" s="12"/>
       <c r="C24" s="21"/>
       <c r="D24" s="21"/>
@@ -1378,10 +1352,10 @@
       <c r="F24" s="21"/>
       <c r="G24" s="22"/>
       <c r="H24" s="23"/>
-      <c r="I24" s="4"/>
+      <c r="I24" s="8"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="16"/>
+      <c r="A25" s="17"/>
       <c r="B25" s="12"/>
       <c r="C25" s="21"/>
       <c r="D25" s="21"/>
@@ -1389,10 +1363,10 @@
       <c r="F25" s="21"/>
       <c r="G25" s="22"/>
       <c r="H25" s="23"/>
-      <c r="I25" s="4"/>
+      <c r="I25" s="8"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="16"/>
+      <c r="A26" s="17"/>
       <c r="B26" s="12"/>
       <c r="C26" s="21"/>
       <c r="D26" s="21"/>
@@ -1400,10 +1374,10 @@
       <c r="F26" s="21"/>
       <c r="G26" s="22"/>
       <c r="H26" s="23"/>
-      <c r="I26" s="4"/>
+      <c r="I26" s="8"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="16"/>
+      <c r="A27" s="17"/>
       <c r="B27" s="12"/>
       <c r="C27" s="21"/>
       <c r="D27" s="21"/>
@@ -1411,10 +1385,10 @@
       <c r="F27" s="21"/>
       <c r="G27" s="22"/>
       <c r="H27" s="23"/>
-      <c r="I27" s="4"/>
+      <c r="I27" s="8"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="16"/>
+      <c r="A28" s="17"/>
       <c r="B28" s="12"/>
       <c r="C28" s="21"/>
       <c r="D28" s="21"/>
@@ -1422,10 +1396,10 @@
       <c r="F28" s="21"/>
       <c r="G28" s="22"/>
       <c r="H28" s="23"/>
-      <c r="I28" s="4"/>
+      <c r="I28" s="8"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="16"/>
+      <c r="A29" s="17"/>
       <c r="B29" s="12"/>
       <c r="C29" s="21"/>
       <c r="D29" s="21"/>
@@ -1433,10 +1407,10 @@
       <c r="F29" s="21"/>
       <c r="G29" s="22"/>
       <c r="H29" s="23"/>
-      <c r="I29" s="4"/>
+      <c r="I29" s="8"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="16"/>
+      <c r="A30" s="17"/>
       <c r="B30" s="12"/>
       <c r="C30" s="21"/>
       <c r="D30" s="21"/>
@@ -1444,10 +1418,10 @@
       <c r="F30" s="21"/>
       <c r="G30" s="22"/>
       <c r="H30" s="23"/>
-      <c r="I30" s="4"/>
+      <c r="I30" s="8"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="16"/>
+      <c r="A31" s="17"/>
       <c r="B31" s="12"/>
       <c r="C31" s="21"/>
       <c r="D31" s="21"/>
@@ -1455,10 +1429,10 @@
       <c r="F31" s="21"/>
       <c r="G31" s="22"/>
       <c r="H31" s="23"/>
-      <c r="I31" s="4"/>
+      <c r="I31" s="8"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="16"/>
+      <c r="A32" s="17"/>
       <c r="B32" s="12"/>
       <c r="C32" s="21"/>
       <c r="D32" s="21"/>
@@ -1466,10 +1440,10 @@
       <c r="F32" s="21"/>
       <c r="G32" s="22"/>
       <c r="H32" s="23"/>
-      <c r="I32" s="4"/>
+      <c r="I32" s="8"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="16"/>
+      <c r="A33" s="17"/>
       <c r="B33" s="12"/>
       <c r="C33" s="21"/>
       <c r="D33" s="21"/>
@@ -1477,10 +1451,10 @@
       <c r="F33" s="21"/>
       <c r="G33" s="22"/>
       <c r="H33" s="23"/>
-      <c r="I33" s="4"/>
+      <c r="I33" s="8"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="16"/>
+      <c r="A34" s="17"/>
       <c r="B34" s="12"/>
       <c r="C34" s="21"/>
       <c r="D34" s="21"/>
@@ -1488,10 +1462,10 @@
       <c r="F34" s="21"/>
       <c r="G34" s="22"/>
       <c r="H34" s="23"/>
-      <c r="I34" s="4"/>
+      <c r="I34" s="8"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="16"/>
+      <c r="A35" s="17"/>
       <c r="B35" s="12"/>
       <c r="C35" s="21"/>
       <c r="D35" s="21"/>
@@ -1499,10 +1473,10 @@
       <c r="F35" s="21"/>
       <c r="G35" s="22"/>
       <c r="H35" s="23"/>
-      <c r="I35" s="4"/>
+      <c r="I35" s="8"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="16"/>
+      <c r="A36" s="17"/>
       <c r="B36" s="12"/>
       <c r="C36" s="21"/>
       <c r="D36" s="21"/>
@@ -1510,10 +1484,10 @@
       <c r="F36" s="21"/>
       <c r="G36" s="22"/>
       <c r="H36" s="23"/>
-      <c r="I36" s="4"/>
+      <c r="I36" s="8"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="16"/>
+      <c r="A37" s="17"/>
       <c r="B37" s="12"/>
       <c r="C37" s="21"/>
       <c r="D37" s="21"/>
@@ -1521,10 +1495,10 @@
       <c r="F37" s="21"/>
       <c r="G37" s="22"/>
       <c r="H37" s="23"/>
-      <c r="I37" s="4"/>
+      <c r="I37" s="8"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="16"/>
+      <c r="A38" s="17"/>
       <c r="B38" s="12"/>
       <c r="C38" s="21"/>
       <c r="D38" s="21"/>
@@ -1532,10 +1506,10 @@
       <c r="F38" s="21"/>
       <c r="G38" s="22"/>
       <c r="H38" s="23"/>
-      <c r="I38" s="4"/>
+      <c r="I38" s="8"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="16"/>
+      <c r="A39" s="17"/>
       <c r="B39" s="12"/>
       <c r="C39" s="21"/>
       <c r="D39" s="21"/>
@@ -1543,10 +1517,10 @@
       <c r="F39" s="21"/>
       <c r="G39" s="22"/>
       <c r="H39" s="23"/>
-      <c r="I39" s="4"/>
+      <c r="I39" s="8"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="16"/>
+      <c r="A40" s="17"/>
       <c r="B40" s="12"/>
       <c r="C40" s="21"/>
       <c r="D40" s="21"/>
@@ -1554,10 +1528,10 @@
       <c r="F40" s="21"/>
       <c r="G40" s="22"/>
       <c r="H40" s="23"/>
-      <c r="I40" s="4"/>
+      <c r="I40" s="8"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="16"/>
+      <c r="A41" s="17"/>
       <c r="B41" s="12"/>
       <c r="C41" s="21"/>
       <c r="D41" s="21"/>
@@ -1565,10 +1539,10 @@
       <c r="F41" s="21"/>
       <c r="G41" s="22"/>
       <c r="H41" s="23"/>
-      <c r="I41" s="4"/>
+      <c r="I41" s="8"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="16"/>
+      <c r="A42" s="17"/>
       <c r="B42" s="12"/>
       <c r="C42" s="21"/>
       <c r="D42" s="21"/>
@@ -1576,10 +1550,10 @@
       <c r="F42" s="21"/>
       <c r="G42" s="22"/>
       <c r="H42" s="23"/>
-      <c r="I42" s="4"/>
+      <c r="I42" s="8"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="16"/>
+      <c r="A43" s="17"/>
       <c r="B43" s="12"/>
       <c r="C43" s="21"/>
       <c r="D43" s="21"/>
@@ -1587,10 +1561,10 @@
       <c r="F43" s="21"/>
       <c r="G43" s="22"/>
       <c r="H43" s="23"/>
-      <c r="I43" s="4"/>
+      <c r="I43" s="8"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="16"/>
+      <c r="A44" s="17"/>
       <c r="B44" s="12"/>
       <c r="C44" s="21"/>
       <c r="D44" s="21"/>
@@ -1598,10 +1572,10 @@
       <c r="F44" s="21"/>
       <c r="G44" s="22"/>
       <c r="H44" s="23"/>
-      <c r="I44" s="4"/>
+      <c r="I44" s="8"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="16"/>
+      <c r="A45" s="17"/>
       <c r="B45" s="12"/>
       <c r="C45" s="21"/>
       <c r="D45" s="21"/>
@@ -1609,10 +1583,10 @@
       <c r="F45" s="21"/>
       <c r="G45" s="22"/>
       <c r="H45" s="23"/>
-      <c r="I45" s="4"/>
+      <c r="I45" s="8"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="16"/>
+      <c r="A46" s="17"/>
       <c r="B46" s="12"/>
       <c r="C46" s="21"/>
       <c r="D46" s="21"/>
@@ -1620,10 +1594,10 @@
       <c r="F46" s="21"/>
       <c r="G46" s="22"/>
       <c r="H46" s="23"/>
-      <c r="I46" s="4"/>
+      <c r="I46" s="8"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="16"/>
+      <c r="A47" s="17"/>
       <c r="B47" s="12"/>
       <c r="C47" s="21"/>
       <c r="D47" s="21"/>
@@ -1631,10 +1605,10 @@
       <c r="F47" s="21"/>
       <c r="G47" s="22"/>
       <c r="H47" s="23"/>
-      <c r="I47" s="4"/>
+      <c r="I47" s="8"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="16"/>
+      <c r="A48" s="17"/>
       <c r="B48" s="12"/>
       <c r="C48" s="21"/>
       <c r="D48" s="21"/>
@@ -1642,10 +1616,10 @@
       <c r="F48" s="21"/>
       <c r="G48" s="22"/>
       <c r="H48" s="23"/>
-      <c r="I48" s="4"/>
+      <c r="I48" s="8"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="16"/>
+      <c r="A49" s="17"/>
       <c r="B49" s="12"/>
       <c r="C49" s="21"/>
       <c r="D49" s="21"/>
@@ -1653,10 +1627,10 @@
       <c r="F49" s="21"/>
       <c r="G49" s="22"/>
       <c r="H49" s="23"/>
-      <c r="I49" s="4"/>
+      <c r="I49" s="8"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="16"/>
+      <c r="A50" s="17"/>
       <c r="B50" s="12"/>
       <c r="C50" s="21"/>
       <c r="D50" s="21"/>
@@ -1664,10 +1638,10 @@
       <c r="F50" s="21"/>
       <c r="G50" s="22"/>
       <c r="H50" s="23"/>
-      <c r="I50" s="4"/>
+      <c r="I50" s="8"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="16"/>
+      <c r="A51" s="17"/>
       <c r="B51" s="12"/>
       <c r="C51" s="21"/>
       <c r="D51" s="21"/>
@@ -1675,10 +1649,10 @@
       <c r="F51" s="21"/>
       <c r="G51" s="22"/>
       <c r="H51" s="23"/>
-      <c r="I51" s="4"/>
+      <c r="I51" s="8"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="16"/>
+      <c r="A52" s="17"/>
       <c r="B52" s="12"/>
       <c r="C52" s="21"/>
       <c r="D52" s="21"/>
@@ -1686,10 +1660,10 @@
       <c r="F52" s="21"/>
       <c r="G52" s="22"/>
       <c r="H52" s="23"/>
-      <c r="I52" s="4"/>
+      <c r="I52" s="8"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="16"/>
+      <c r="A53" s="17"/>
       <c r="B53" s="12"/>
       <c r="C53" s="21"/>
       <c r="D53" s="21"/>
@@ -1697,10 +1671,10 @@
       <c r="F53" s="21"/>
       <c r="G53" s="22"/>
       <c r="H53" s="23"/>
-      <c r="I53" s="4"/>
+      <c r="I53" s="8"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="16"/>
+      <c r="A54" s="17"/>
       <c r="B54" s="12"/>
       <c r="C54" s="21"/>
       <c r="D54" s="21"/>
@@ -1708,10 +1682,10 @@
       <c r="F54" s="21"/>
       <c r="G54" s="22"/>
       <c r="H54" s="23"/>
-      <c r="I54" s="4"/>
+      <c r="I54" s="8"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="16"/>
+      <c r="A55" s="17"/>
       <c r="B55" s="12"/>
       <c r="C55" s="21"/>
       <c r="D55" s="21"/>
@@ -1719,10 +1693,10 @@
       <c r="F55" s="21"/>
       <c r="G55" s="22"/>
       <c r="H55" s="23"/>
-      <c r="I55" s="4"/>
+      <c r="I55" s="8"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="16"/>
+      <c r="A56" s="17"/>
       <c r="B56" s="12"/>
       <c r="C56" s="21"/>
       <c r="D56" s="21"/>
@@ -1730,10 +1704,10 @@
       <c r="F56" s="21"/>
       <c r="G56" s="22"/>
       <c r="H56" s="23"/>
-      <c r="I56" s="4"/>
+      <c r="I56" s="8"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="16"/>
+      <c r="A57" s="17"/>
       <c r="B57" s="12"/>
       <c r="C57" s="21"/>
       <c r="D57" s="21"/>
@@ -1741,10 +1715,10 @@
       <c r="F57" s="21"/>
       <c r="G57" s="22"/>
       <c r="H57" s="23"/>
-      <c r="I57" s="4"/>
+      <c r="I57" s="8"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="16"/>
+      <c r="A58" s="17"/>
       <c r="B58" s="12"/>
       <c r="C58" s="21"/>
       <c r="D58" s="21"/>
@@ -1752,10 +1726,10 @@
       <c r="F58" s="21"/>
       <c r="G58" s="22"/>
       <c r="H58" s="23"/>
-      <c r="I58" s="4"/>
+      <c r="I58" s="8"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="16"/>
+      <c r="A59" s="17"/>
       <c r="B59" s="12"/>
       <c r="C59" s="21"/>
       <c r="D59" s="21"/>
@@ -1763,10 +1737,10 @@
       <c r="F59" s="21"/>
       <c r="G59" s="22"/>
       <c r="H59" s="23"/>
-      <c r="I59" s="4"/>
+      <c r="I59" s="8"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="16"/>
+      <c r="A60" s="17"/>
       <c r="B60" s="12"/>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
@@ -1774,10 +1748,10 @@
       <c r="F60" s="21"/>
       <c r="G60" s="22"/>
       <c r="H60" s="23"/>
-      <c r="I60" s="4"/>
+      <c r="I60" s="8"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="16"/>
+      <c r="A61" s="17"/>
       <c r="B61" s="12"/>
       <c r="C61" s="21"/>
       <c r="D61" s="21"/>
@@ -1785,10 +1759,10 @@
       <c r="F61" s="21"/>
       <c r="G61" s="22"/>
       <c r="H61" s="23"/>
-      <c r="I61" s="4"/>
+      <c r="I61" s="8"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="16"/>
+      <c r="A62" s="17"/>
       <c r="B62" s="12"/>
       <c r="C62" s="21"/>
       <c r="D62" s="21"/>
@@ -1796,10 +1770,10 @@
       <c r="F62" s="21"/>
       <c r="G62" s="22"/>
       <c r="H62" s="23"/>
-      <c r="I62" s="4"/>
+      <c r="I62" s="8"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="16"/>
+      <c r="A63" s="17"/>
       <c r="B63" s="12"/>
       <c r="C63" s="21"/>
       <c r="D63" s="21"/>
@@ -1807,10 +1781,10 @@
       <c r="F63" s="21"/>
       <c r="G63" s="22"/>
       <c r="H63" s="23"/>
-      <c r="I63" s="4"/>
+      <c r="I63" s="8"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="16"/>
+      <c r="A64" s="17"/>
       <c r="B64" s="12"/>
       <c r="C64" s="21"/>
       <c r="D64" s="21"/>
@@ -1818,10 +1792,10 @@
       <c r="F64" s="21"/>
       <c r="G64" s="22"/>
       <c r="H64" s="23"/>
-      <c r="I64" s="4"/>
+      <c r="I64" s="8"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="16"/>
+      <c r="A65" s="17"/>
       <c r="B65" s="12"/>
       <c r="C65" s="21"/>
       <c r="D65" s="21"/>
@@ -1829,10 +1803,10 @@
       <c r="F65" s="21"/>
       <c r="G65" s="22"/>
       <c r="H65" s="23"/>
-      <c r="I65" s="4"/>
+      <c r="I65" s="8"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="16"/>
+      <c r="A66" s="17"/>
       <c r="B66" s="12"/>
       <c r="C66" s="21"/>
       <c r="D66" s="21"/>
@@ -1840,10 +1814,10 @@
       <c r="F66" s="21"/>
       <c r="G66" s="22"/>
       <c r="H66" s="23"/>
-      <c r="I66" s="4"/>
+      <c r="I66" s="8"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="16"/>
+      <c r="A67" s="17"/>
       <c r="B67" s="12"/>
       <c r="C67" s="21"/>
       <c r="D67" s="21"/>
@@ -1851,10 +1825,10 @@
       <c r="F67" s="21"/>
       <c r="G67" s="22"/>
       <c r="H67" s="23"/>
-      <c r="I67" s="4"/>
+      <c r="I67" s="8"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="16"/>
+      <c r="A68" s="17"/>
       <c r="B68" s="12"/>
       <c r="C68" s="21"/>
       <c r="D68" s="21"/>
@@ -1862,10 +1836,10 @@
       <c r="F68" s="21"/>
       <c r="G68" s="22"/>
       <c r="H68" s="23"/>
-      <c r="I68" s="4"/>
+      <c r="I68" s="8"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="16"/>
+      <c r="A69" s="17"/>
       <c r="B69" s="12"/>
       <c r="C69" s="21"/>
       <c r="D69" s="21"/>
@@ -1873,10 +1847,10 @@
       <c r="F69" s="21"/>
       <c r="G69" s="22"/>
       <c r="H69" s="23"/>
-      <c r="I69" s="4"/>
+      <c r="I69" s="8"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="16"/>
+      <c r="A70" s="17"/>
       <c r="B70" s="12"/>
       <c r="C70" s="21"/>
       <c r="D70" s="21"/>
@@ -1884,10 +1858,10 @@
       <c r="F70" s="21"/>
       <c r="G70" s="22"/>
       <c r="H70" s="23"/>
-      <c r="I70" s="4"/>
+      <c r="I70" s="8"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="16"/>
+      <c r="A71" s="17"/>
       <c r="B71" s="12"/>
       <c r="C71" s="21"/>
       <c r="D71" s="21"/>
@@ -1895,10 +1869,10 @@
       <c r="F71" s="21"/>
       <c r="G71" s="22"/>
       <c r="H71" s="23"/>
-      <c r="I71" s="4"/>
+      <c r="I71" s="8"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="16"/>
+      <c r="A72" s="17"/>
       <c r="B72" s="12"/>
       <c r="C72" s="21"/>
       <c r="D72" s="21"/>
@@ -1906,10 +1880,10 @@
       <c r="F72" s="21"/>
       <c r="G72" s="22"/>
       <c r="H72" s="23"/>
-      <c r="I72" s="4"/>
+      <c r="I72" s="8"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="16"/>
+      <c r="A73" s="17"/>
       <c r="B73" s="12"/>
       <c r="C73" s="21"/>
       <c r="D73" s="21"/>
@@ -1917,10 +1891,10 @@
       <c r="F73" s="21"/>
       <c r="G73" s="22"/>
       <c r="H73" s="23"/>
-      <c r="I73" s="4"/>
+      <c r="I73" s="8"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="16"/>
+      <c r="A74" s="17"/>
       <c r="B74" s="12"/>
       <c r="C74" s="21"/>
       <c r="D74" s="21"/>
@@ -1928,10 +1902,10 @@
       <c r="F74" s="21"/>
       <c r="G74" s="22"/>
       <c r="H74" s="23"/>
-      <c r="I74" s="4"/>
+      <c r="I74" s="8"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="16"/>
+      <c r="A75" s="17"/>
       <c r="B75" s="12"/>
       <c r="C75" s="21"/>
       <c r="D75" s="21"/>
@@ -1939,10 +1913,10 @@
       <c r="F75" s="21"/>
       <c r="G75" s="22"/>
       <c r="H75" s="23"/>
-      <c r="I75" s="4"/>
+      <c r="I75" s="8"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="16"/>
+      <c r="A76" s="17"/>
       <c r="B76" s="12"/>
       <c r="C76" s="21"/>
       <c r="D76" s="21"/>
@@ -1950,10 +1924,10 @@
       <c r="F76" s="21"/>
       <c r="G76" s="22"/>
       <c r="H76" s="23"/>
-      <c r="I76" s="4"/>
+      <c r="I76" s="8"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="16"/>
+      <c r="A77" s="17"/>
       <c r="B77" s="12"/>
       <c r="C77" s="21"/>
       <c r="D77" s="21"/>
@@ -1961,10 +1935,10 @@
       <c r="F77" s="21"/>
       <c r="G77" s="22"/>
       <c r="H77" s="23"/>
-      <c r="I77" s="4"/>
+      <c r="I77" s="8"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="16"/>
+      <c r="A78" s="17"/>
       <c r="B78" s="12"/>
       <c r="C78" s="21"/>
       <c r="D78" s="21"/>
@@ -1972,10 +1946,10 @@
       <c r="F78" s="21"/>
       <c r="G78" s="22"/>
       <c r="H78" s="23"/>
-      <c r="I78" s="4"/>
+      <c r="I78" s="8"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="16"/>
+      <c r="A79" s="17"/>
       <c r="B79" s="12"/>
       <c r="C79" s="21"/>
       <c r="D79" s="21"/>
@@ -1983,10 +1957,10 @@
       <c r="F79" s="21"/>
       <c r="G79" s="22"/>
       <c r="H79" s="23"/>
-      <c r="I79" s="4"/>
+      <c r="I79" s="8"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="16"/>
+      <c r="A80" s="17"/>
       <c r="B80" s="12"/>
       <c r="C80" s="21"/>
       <c r="D80" s="21"/>
@@ -1994,10 +1968,10 @@
       <c r="F80" s="21"/>
       <c r="G80" s="22"/>
       <c r="H80" s="23"/>
-      <c r="I80" s="4"/>
+      <c r="I80" s="8"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="16"/>
+      <c r="A81" s="17"/>
       <c r="B81" s="12"/>
       <c r="C81" s="21"/>
       <c r="D81" s="21"/>
@@ -2005,10 +1979,10 @@
       <c r="F81" s="21"/>
       <c r="G81" s="22"/>
       <c r="H81" s="23"/>
-      <c r="I81" s="4"/>
+      <c r="I81" s="8"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="16"/>
+      <c r="A82" s="17"/>
       <c r="B82" s="12"/>
       <c r="C82" s="21"/>
       <c r="D82" s="21"/>
@@ -2016,10 +1990,10 @@
       <c r="F82" s="21"/>
       <c r="G82" s="22"/>
       <c r="H82" s="23"/>
-      <c r="I82" s="4"/>
+      <c r="I82" s="8"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="16"/>
+      <c r="A83" s="17"/>
       <c r="B83" s="12"/>
       <c r="C83" s="21"/>
       <c r="D83" s="21"/>
@@ -2027,10 +2001,10 @@
       <c r="F83" s="21"/>
       <c r="G83" s="22"/>
       <c r="H83" s="23"/>
-      <c r="I83" s="4"/>
+      <c r="I83" s="8"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="16"/>
+      <c r="A84" s="17"/>
       <c r="B84" s="12"/>
       <c r="C84" s="21"/>
       <c r="D84" s="21"/>
@@ -2038,10 +2012,10 @@
       <c r="F84" s="21"/>
       <c r="G84" s="22"/>
       <c r="H84" s="23"/>
-      <c r="I84" s="4"/>
+      <c r="I84" s="8"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="16"/>
+      <c r="A85" s="17"/>
       <c r="B85" s="12"/>
       <c r="C85" s="21"/>
       <c r="D85" s="21"/>
@@ -2049,10 +2023,10 @@
       <c r="F85" s="21"/>
       <c r="G85" s="22"/>
       <c r="H85" s="23"/>
-      <c r="I85" s="4"/>
+      <c r="I85" s="8"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="16"/>
+      <c r="A86" s="17"/>
       <c r="B86" s="12"/>
       <c r="C86" s="21"/>
       <c r="D86" s="21"/>
@@ -2060,10 +2034,10 @@
       <c r="F86" s="21"/>
       <c r="G86" s="22"/>
       <c r="H86" s="23"/>
-      <c r="I86" s="4"/>
+      <c r="I86" s="8"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="16"/>
+      <c r="A87" s="17"/>
       <c r="B87" s="12"/>
       <c r="C87" s="21"/>
       <c r="D87" s="21"/>
@@ -2071,10 +2045,10 @@
       <c r="F87" s="21"/>
       <c r="G87" s="22"/>
       <c r="H87" s="23"/>
-      <c r="I87" s="4"/>
+      <c r="I87" s="8"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="16"/>
+      <c r="A88" s="17"/>
       <c r="B88" s="12"/>
       <c r="C88" s="21"/>
       <c r="D88" s="21"/>
@@ -2082,10 +2056,10 @@
       <c r="F88" s="21"/>
       <c r="G88" s="22"/>
       <c r="H88" s="23"/>
-      <c r="I88" s="4"/>
+      <c r="I88" s="8"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="16"/>
+      <c r="A89" s="17"/>
       <c r="B89" s="12"/>
       <c r="C89" s="21"/>
       <c r="D89" s="21"/>
@@ -2093,10 +2067,10 @@
       <c r="F89" s="21"/>
       <c r="G89" s="22"/>
       <c r="H89" s="23"/>
-      <c r="I89" s="4"/>
+      <c r="I89" s="8"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="16"/>
+      <c r="A90" s="17"/>
       <c r="B90" s="12"/>
       <c r="C90" s="21"/>
       <c r="D90" s="21"/>
@@ -2104,10 +2078,10 @@
       <c r="F90" s="21"/>
       <c r="G90" s="22"/>
       <c r="H90" s="23"/>
-      <c r="I90" s="4"/>
+      <c r="I90" s="8"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="16"/>
+      <c r="A91" s="17"/>
       <c r="B91" s="12"/>
       <c r="C91" s="21"/>
       <c r="D91" s="21"/>
@@ -2115,10 +2089,10 @@
       <c r="F91" s="21"/>
       <c r="G91" s="22"/>
       <c r="H91" s="23"/>
-      <c r="I91" s="4"/>
+      <c r="I91" s="8"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="16"/>
+      <c r="A92" s="17"/>
       <c r="B92" s="12"/>
       <c r="C92" s="21"/>
       <c r="D92" s="21"/>
@@ -2126,10 +2100,10 @@
       <c r="F92" s="21"/>
       <c r="G92" s="22"/>
       <c r="H92" s="23"/>
-      <c r="I92" s="4"/>
+      <c r="I92" s="8"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="16"/>
+      <c r="A93" s="17"/>
       <c r="B93" s="12"/>
       <c r="C93" s="21"/>
       <c r="D93" s="21"/>
@@ -2137,10 +2111,10 @@
       <c r="F93" s="21"/>
       <c r="G93" s="22"/>
       <c r="H93" s="23"/>
-      <c r="I93" s="4"/>
+      <c r="I93" s="8"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="16"/>
+      <c r="A94" s="17"/>
       <c r="B94" s="12"/>
       <c r="C94" s="21"/>
       <c r="D94" s="21"/>
@@ -2148,10 +2122,10 @@
       <c r="F94" s="21"/>
       <c r="G94" s="22"/>
       <c r="H94" s="23"/>
-      <c r="I94" s="4"/>
+      <c r="I94" s="8"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="16"/>
+      <c r="A95" s="17"/>
       <c r="B95" s="12"/>
       <c r="C95" s="21"/>
       <c r="D95" s="21"/>
@@ -2159,10 +2133,10 @@
       <c r="F95" s="21"/>
       <c r="G95" s="22"/>
       <c r="H95" s="23"/>
-      <c r="I95" s="4"/>
+      <c r="I95" s="8"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="16"/>
+      <c r="A96" s="17"/>
       <c r="B96" s="12"/>
       <c r="C96" s="21"/>
       <c r="D96" s="21"/>
@@ -2170,10 +2144,10 @@
       <c r="F96" s="21"/>
       <c r="G96" s="22"/>
       <c r="H96" s="23"/>
-      <c r="I96" s="4"/>
+      <c r="I96" s="8"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="16"/>
+      <c r="A97" s="17"/>
       <c r="B97" s="12"/>
       <c r="C97" s="21"/>
       <c r="D97" s="21"/>
@@ -2181,10 +2155,10 @@
       <c r="F97" s="21"/>
       <c r="G97" s="22"/>
       <c r="H97" s="23"/>
-      <c r="I97" s="4"/>
+      <c r="I97" s="8"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="16"/>
+      <c r="A98" s="17"/>
       <c r="B98" s="12"/>
       <c r="C98" s="21"/>
       <c r="D98" s="21"/>
@@ -2192,10 +2166,10 @@
       <c r="F98" s="21"/>
       <c r="G98" s="22"/>
       <c r="H98" s="23"/>
-      <c r="I98" s="4"/>
+      <c r="I98" s="8"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="16"/>
+      <c r="A99" s="17"/>
       <c r="B99" s="12"/>
       <c r="C99" s="21"/>
       <c r="D99" s="21"/>
@@ -2203,10 +2177,10 @@
       <c r="F99" s="21"/>
       <c r="G99" s="22"/>
       <c r="H99" s="23"/>
-      <c r="I99" s="4"/>
+      <c r="I99" s="8"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="16"/>
+      <c r="A100" s="17"/>
       <c r="B100" s="12"/>
       <c r="C100" s="21"/>
       <c r="D100" s="21"/>
@@ -2214,10 +2188,10 @@
       <c r="F100" s="21"/>
       <c r="G100" s="22"/>
       <c r="H100" s="23"/>
-      <c r="I100" s="4"/>
+      <c r="I100" s="8"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="16"/>
+      <c r="A101" s="17"/>
       <c r="B101" s="12"/>
       <c r="C101" s="21"/>
       <c r="D101" s="21"/>
@@ -2225,10 +2199,10 @@
       <c r="F101" s="21"/>
       <c r="G101" s="22"/>
       <c r="H101" s="23"/>
-      <c r="I101" s="4"/>
+      <c r="I101" s="8"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="16"/>
+      <c r="A102" s="17"/>
       <c r="B102" s="12"/>
       <c r="C102" s="21"/>
       <c r="D102" s="21"/>
@@ -2236,10 +2210,10 @@
       <c r="F102" s="21"/>
       <c r="G102" s="22"/>
       <c r="H102" s="23"/>
-      <c r="I102" s="4"/>
+      <c r="I102" s="8"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="16"/>
+      <c r="A103" s="17"/>
       <c r="B103" s="12"/>
       <c r="C103" s="21"/>
       <c r="D103" s="21"/>
@@ -2247,10 +2221,10 @@
       <c r="F103" s="21"/>
       <c r="G103" s="22"/>
       <c r="H103" s="23"/>
-      <c r="I103" s="4"/>
+      <c r="I103" s="8"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="16"/>
+      <c r="A104" s="17"/>
       <c r="B104" s="12"/>
       <c r="C104" s="21"/>
       <c r="D104" s="21"/>
@@ -2258,10 +2232,10 @@
       <c r="F104" s="21"/>
       <c r="G104" s="22"/>
       <c r="H104" s="23"/>
-      <c r="I104" s="4"/>
+      <c r="I104" s="8"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="16"/>
+      <c r="A105" s="17"/>
       <c r="B105" s="12"/>
       <c r="C105" s="21"/>
       <c r="D105" s="21"/>
@@ -2269,10 +2243,10 @@
       <c r="F105" s="21"/>
       <c r="G105" s="22"/>
       <c r="H105" s="23"/>
-      <c r="I105" s="4"/>
+      <c r="I105" s="8"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="16"/>
+      <c r="A106" s="17"/>
       <c r="B106" s="12"/>
       <c r="C106" s="21"/>
       <c r="D106" s="21"/>
@@ -2280,10 +2254,10 @@
       <c r="F106" s="21"/>
       <c r="G106" s="22"/>
       <c r="H106" s="23"/>
-      <c r="I106" s="4"/>
+      <c r="I106" s="8"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="16"/>
+      <c r="A107" s="17"/>
       <c r="B107" s="12"/>
       <c r="C107" s="21"/>
       <c r="D107" s="21"/>
@@ -2291,10 +2265,10 @@
       <c r="F107" s="21"/>
       <c r="G107" s="22"/>
       <c r="H107" s="23"/>
-      <c r="I107" s="4"/>
+      <c r="I107" s="8"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="16"/>
+      <c r="A108" s="17"/>
       <c r="B108" s="12"/>
       <c r="C108" s="21"/>
       <c r="D108" s="21"/>
@@ -2302,10 +2276,10 @@
       <c r="F108" s="21"/>
       <c r="G108" s="22"/>
       <c r="H108" s="23"/>
-      <c r="I108" s="4"/>
+      <c r="I108" s="8"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="16"/>
+      <c r="A109" s="17"/>
       <c r="B109" s="12"/>
       <c r="C109" s="21"/>
       <c r="D109" s="21"/>
@@ -2313,10 +2287,10 @@
       <c r="F109" s="21"/>
       <c r="G109" s="22"/>
       <c r="H109" s="23"/>
-      <c r="I109" s="4"/>
+      <c r="I109" s="8"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="16"/>
+      <c r="A110" s="17"/>
       <c r="B110" s="12"/>
       <c r="C110" s="21"/>
       <c r="D110" s="21"/>
@@ -2324,10 +2298,10 @@
       <c r="F110" s="21"/>
       <c r="G110" s="22"/>
       <c r="H110" s="23"/>
-      <c r="I110" s="4"/>
+      <c r="I110" s="8"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="16"/>
+      <c r="A111" s="17"/>
       <c r="B111" s="12"/>
       <c r="C111" s="21"/>
       <c r="D111" s="21"/>
@@ -2335,10 +2309,10 @@
       <c r="F111" s="21"/>
       <c r="G111" s="22"/>
       <c r="H111" s="23"/>
-      <c r="I111" s="4"/>
+      <c r="I111" s="8"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="16"/>
+      <c r="A112" s="17"/>
       <c r="B112" s="12"/>
       <c r="C112" s="21"/>
       <c r="D112" s="21"/>
@@ -2346,10 +2320,10 @@
       <c r="F112" s="21"/>
       <c r="G112" s="22"/>
       <c r="H112" s="23"/>
-      <c r="I112" s="4"/>
+      <c r="I112" s="8"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="16"/>
+      <c r="A113" s="17"/>
       <c r="B113" s="12"/>
       <c r="C113" s="21"/>
       <c r="D113" s="21"/>
@@ -2357,10 +2331,10 @@
       <c r="F113" s="21"/>
       <c r="G113" s="22"/>
       <c r="H113" s="23"/>
-      <c r="I113" s="4"/>
+      <c r="I113" s="8"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="16"/>
+      <c r="A114" s="17"/>
       <c r="B114" s="12"/>
       <c r="C114" s="21"/>
       <c r="D114" s="21"/>
@@ -2368,10 +2342,10 @@
       <c r="F114" s="21"/>
       <c r="G114" s="22"/>
       <c r="H114" s="23"/>
-      <c r="I114" s="4"/>
+      <c r="I114" s="8"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="16"/>
+      <c r="A115" s="17"/>
       <c r="B115" s="12"/>
       <c r="C115" s="21"/>
       <c r="D115" s="21"/>
@@ -2379,10 +2353,10 @@
       <c r="F115" s="21"/>
       <c r="G115" s="22"/>
       <c r="H115" s="23"/>
-      <c r="I115" s="4"/>
+      <c r="I115" s="8"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="16"/>
+      <c r="A116" s="17"/>
       <c r="B116" s="12"/>
       <c r="C116" s="21"/>
       <c r="D116" s="21"/>
@@ -2390,10 +2364,10 @@
       <c r="F116" s="21"/>
       <c r="G116" s="22"/>
       <c r="H116" s="23"/>
-      <c r="I116" s="4"/>
+      <c r="I116" s="8"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="16"/>
+      <c r="A117" s="17"/>
       <c r="B117" s="12"/>
       <c r="C117" s="21"/>
       <c r="D117" s="21"/>
@@ -2401,10 +2375,10 @@
       <c r="F117" s="21"/>
       <c r="G117" s="22"/>
       <c r="H117" s="23"/>
-      <c r="I117" s="4"/>
+      <c r="I117" s="8"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="16"/>
+      <c r="A118" s="17"/>
       <c r="B118" s="12"/>
       <c r="C118" s="21"/>
       <c r="D118" s="21"/>
@@ -2412,10 +2386,10 @@
       <c r="F118" s="21"/>
       <c r="G118" s="22"/>
       <c r="H118" s="23"/>
-      <c r="I118" s="4"/>
+      <c r="I118" s="8"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="16"/>
+      <c r="A119" s="17"/>
       <c r="B119" s="12"/>
       <c r="C119" s="21"/>
       <c r="D119" s="21"/>
@@ -2423,10 +2397,10 @@
       <c r="F119" s="21"/>
       <c r="G119" s="22"/>
       <c r="H119" s="23"/>
-      <c r="I119" s="4"/>
+      <c r="I119" s="8"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="16"/>
+      <c r="A120" s="17"/>
       <c r="B120" s="12"/>
       <c r="C120" s="21"/>
       <c r="D120" s="21"/>
@@ -2434,10 +2408,10 @@
       <c r="F120" s="21"/>
       <c r="G120" s="22"/>
       <c r="H120" s="23"/>
-      <c r="I120" s="4"/>
+      <c r="I120" s="8"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="16"/>
+      <c r="A121" s="17"/>
       <c r="B121" s="12"/>
       <c r="C121" s="21"/>
       <c r="D121" s="21"/>
@@ -2445,10 +2419,10 @@
       <c r="F121" s="21"/>
       <c r="G121" s="22"/>
       <c r="H121" s="23"/>
-      <c r="I121" s="4"/>
+      <c r="I121" s="8"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="16"/>
+      <c r="A122" s="17"/>
       <c r="B122" s="12"/>
       <c r="C122" s="21"/>
       <c r="D122" s="21"/>
@@ -2456,10 +2430,10 @@
       <c r="F122" s="21"/>
       <c r="G122" s="22"/>
       <c r="H122" s="23"/>
-      <c r="I122" s="4"/>
+      <c r="I122" s="8"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="16"/>
+      <c r="A123" s="17"/>
       <c r="B123" s="12"/>
       <c r="C123" s="21"/>
       <c r="D123" s="21"/>
@@ -2467,10 +2441,10 @@
       <c r="F123" s="21"/>
       <c r="G123" s="22"/>
       <c r="H123" s="23"/>
-      <c r="I123" s="4"/>
+      <c r="I123" s="8"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="16"/>
+      <c r="A124" s="17"/>
       <c r="B124" s="12"/>
       <c r="C124" s="21"/>
       <c r="D124" s="21"/>
@@ -2478,10 +2452,10 @@
       <c r="F124" s="21"/>
       <c r="G124" s="22"/>
       <c r="H124" s="23"/>
-      <c r="I124" s="4"/>
+      <c r="I124" s="8"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="16"/>
+      <c r="A125" s="17"/>
       <c r="B125" s="12"/>
       <c r="C125" s="21"/>
       <c r="D125" s="21"/>
@@ -2489,10 +2463,10 @@
       <c r="F125" s="21"/>
       <c r="G125" s="22"/>
       <c r="H125" s="23"/>
-      <c r="I125" s="4"/>
+      <c r="I125" s="8"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="16"/>
+      <c r="A126" s="17"/>
       <c r="B126" s="12"/>
       <c r="C126" s="21"/>
       <c r="D126" s="21"/>
@@ -2500,10 +2474,10 @@
       <c r="F126" s="21"/>
       <c r="G126" s="22"/>
       <c r="H126" s="23"/>
-      <c r="I126" s="4"/>
+      <c r="I126" s="8"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="16"/>
+      <c r="A127" s="17"/>
       <c r="B127" s="12"/>
       <c r="C127" s="21"/>
       <c r="D127" s="21"/>
@@ -2511,10 +2485,10 @@
       <c r="F127" s="21"/>
       <c r="G127" s="22"/>
       <c r="H127" s="23"/>
-      <c r="I127" s="4"/>
+      <c r="I127" s="8"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="16"/>
+      <c r="A128" s="17"/>
       <c r="B128" s="12"/>
       <c r="C128" s="21"/>
       <c r="D128" s="21"/>
@@ -2522,10 +2496,10 @@
       <c r="F128" s="21"/>
       <c r="G128" s="22"/>
       <c r="H128" s="23"/>
-      <c r="I128" s="4"/>
+      <c r="I128" s="8"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="16"/>
+      <c r="A129" s="17"/>
       <c r="B129" s="12"/>
       <c r="C129" s="21"/>
       <c r="D129" s="21"/>
@@ -2533,10 +2507,10 @@
       <c r="F129" s="21"/>
       <c r="G129" s="22"/>
       <c r="H129" s="23"/>
-      <c r="I129" s="4"/>
+      <c r="I129" s="8"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="16"/>
+      <c r="A130" s="17"/>
       <c r="B130" s="12"/>
       <c r="C130" s="21"/>
       <c r="D130" s="21"/>
@@ -2544,10 +2518,10 @@
       <c r="F130" s="21"/>
       <c r="G130" s="22"/>
       <c r="H130" s="23"/>
-      <c r="I130" s="4"/>
+      <c r="I130" s="8"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="16"/>
+      <c r="A131" s="17"/>
       <c r="B131" s="12"/>
       <c r="C131" s="21"/>
       <c r="D131" s="21"/>
@@ -2555,10 +2529,10 @@
       <c r="F131" s="21"/>
       <c r="G131" s="22"/>
       <c r="H131" s="23"/>
-      <c r="I131" s="4"/>
+      <c r="I131" s="8"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="16"/>
+      <c r="A132" s="17"/>
       <c r="B132" s="12"/>
       <c r="C132" s="21"/>
       <c r="D132" s="21"/>
@@ -2566,10 +2540,10 @@
       <c r="F132" s="21"/>
       <c r="G132" s="22"/>
       <c r="H132" s="23"/>
-      <c r="I132" s="4"/>
+      <c r="I132" s="8"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="16"/>
+      <c r="A133" s="17"/>
       <c r="B133" s="12"/>
       <c r="C133" s="21"/>
       <c r="D133" s="21"/>
@@ -2577,10 +2551,10 @@
       <c r="F133" s="21"/>
       <c r="G133" s="22"/>
       <c r="H133" s="23"/>
-      <c r="I133" s="4"/>
+      <c r="I133" s="8"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="16"/>
+      <c r="A134" s="17"/>
       <c r="B134" s="12"/>
       <c r="C134" s="21"/>
       <c r="D134" s="21"/>
@@ -2588,10 +2562,10 @@
       <c r="F134" s="21"/>
       <c r="G134" s="22"/>
       <c r="H134" s="23"/>
-      <c r="I134" s="4"/>
+      <c r="I134" s="8"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="16"/>
+      <c r="A135" s="17"/>
       <c r="B135" s="12"/>
       <c r="C135" s="21"/>
       <c r="D135" s="21"/>
@@ -2599,10 +2573,10 @@
       <c r="F135" s="21"/>
       <c r="G135" s="22"/>
       <c r="H135" s="23"/>
-      <c r="I135" s="4"/>
+      <c r="I135" s="8"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="16"/>
+      <c r="A136" s="17"/>
       <c r="B136" s="12"/>
       <c r="C136" s="21"/>
       <c r="D136" s="21"/>
@@ -2610,10 +2584,10 @@
       <c r="F136" s="21"/>
       <c r="G136" s="22"/>
       <c r="H136" s="23"/>
-      <c r="I136" s="4"/>
+      <c r="I136" s="8"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="16"/>
+      <c r="A137" s="17"/>
       <c r="B137" s="12"/>
       <c r="C137" s="21"/>
       <c r="D137" s="21"/>
@@ -2621,10 +2595,10 @@
       <c r="F137" s="21"/>
       <c r="G137" s="22"/>
       <c r="H137" s="23"/>
-      <c r="I137" s="4"/>
+      <c r="I137" s="8"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="16"/>
+      <c r="A138" s="17"/>
       <c r="B138" s="12"/>
       <c r="C138" s="21"/>
       <c r="D138" s="21"/>
@@ -2632,10 +2606,10 @@
       <c r="F138" s="21"/>
       <c r="G138" s="22"/>
       <c r="H138" s="23"/>
-      <c r="I138" s="4"/>
+      <c r="I138" s="8"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="16"/>
+      <c r="A139" s="17"/>
       <c r="B139" s="12"/>
       <c r="C139" s="21"/>
       <c r="D139" s="21"/>
@@ -2643,10 +2617,10 @@
       <c r="F139" s="21"/>
       <c r="G139" s="22"/>
       <c r="H139" s="23"/>
-      <c r="I139" s="4"/>
+      <c r="I139" s="8"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="16"/>
+      <c r="A140" s="17"/>
       <c r="B140" s="12"/>
       <c r="C140" s="21"/>
       <c r="D140" s="21"/>
@@ -2654,10 +2628,10 @@
       <c r="F140" s="21"/>
       <c r="G140" s="22"/>
       <c r="H140" s="23"/>
-      <c r="I140" s="4"/>
+      <c r="I140" s="8"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="16"/>
+      <c r="A141" s="17"/>
       <c r="B141" s="12"/>
       <c r="C141" s="21"/>
       <c r="D141" s="21"/>
@@ -2665,10 +2639,10 @@
       <c r="F141" s="21"/>
       <c r="G141" s="22"/>
       <c r="H141" s="23"/>
-      <c r="I141" s="4"/>
+      <c r="I141" s="8"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="16"/>
+      <c r="A142" s="17"/>
       <c r="B142" s="12"/>
       <c r="C142" s="21"/>
       <c r="D142" s="21"/>
@@ -2676,10 +2650,10 @@
       <c r="F142" s="21"/>
       <c r="G142" s="22"/>
       <c r="H142" s="23"/>
-      <c r="I142" s="4"/>
+      <c r="I142" s="8"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="16"/>
+      <c r="A143" s="17"/>
       <c r="B143" s="12"/>
       <c r="C143" s="21"/>
       <c r="D143" s="21"/>
@@ -2687,10 +2661,10 @@
       <c r="F143" s="21"/>
       <c r="G143" s="22"/>
       <c r="H143" s="23"/>
-      <c r="I143" s="4"/>
+      <c r="I143" s="8"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="16"/>
+      <c r="A144" s="17"/>
       <c r="B144" s="12"/>
       <c r="C144" s="21"/>
       <c r="D144" s="21"/>
@@ -2698,10 +2672,10 @@
       <c r="F144" s="21"/>
       <c r="G144" s="22"/>
       <c r="H144" s="23"/>
-      <c r="I144" s="4"/>
+      <c r="I144" s="8"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="16"/>
+      <c r="A145" s="17"/>
       <c r="B145" s="12"/>
       <c r="C145" s="21"/>
       <c r="D145" s="21"/>
@@ -2709,10 +2683,10 @@
       <c r="F145" s="21"/>
       <c r="G145" s="22"/>
       <c r="H145" s="23"/>
-      <c r="I145" s="4"/>
+      <c r="I145" s="8"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="16"/>
+      <c r="A146" s="17"/>
       <c r="B146" s="12"/>
       <c r="C146" s="21"/>
       <c r="D146" s="21"/>
@@ -2720,10 +2694,10 @@
       <c r="F146" s="21"/>
       <c r="G146" s="22"/>
       <c r="H146" s="23"/>
-      <c r="I146" s="4"/>
+      <c r="I146" s="8"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="16"/>
+      <c r="A147" s="17"/>
       <c r="B147" s="12"/>
       <c r="C147" s="21"/>
       <c r="D147" s="21"/>
@@ -2731,10 +2705,10 @@
       <c r="F147" s="21"/>
       <c r="G147" s="22"/>
       <c r="H147" s="23"/>
-      <c r="I147" s="4"/>
+      <c r="I147" s="8"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="16"/>
+      <c r="A148" s="17"/>
       <c r="B148" s="12"/>
       <c r="C148" s="21"/>
       <c r="D148" s="21"/>
@@ -2742,10 +2716,10 @@
       <c r="F148" s="21"/>
       <c r="G148" s="22"/>
       <c r="H148" s="23"/>
-      <c r="I148" s="4"/>
+      <c r="I148" s="8"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="16"/>
+      <c r="A149" s="17"/>
       <c r="B149" s="12"/>
       <c r="C149" s="21"/>
       <c r="D149" s="21"/>
@@ -2753,10 +2727,10 @@
       <c r="F149" s="21"/>
       <c r="G149" s="22"/>
       <c r="H149" s="23"/>
-      <c r="I149" s="4"/>
+      <c r="I149" s="8"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="16"/>
+      <c r="A150" s="17"/>
       <c r="B150" s="12"/>
       <c r="C150" s="21"/>
       <c r="D150" s="21"/>
@@ -2764,10 +2738,10 @@
       <c r="F150" s="21"/>
       <c r="G150" s="22"/>
       <c r="H150" s="23"/>
-      <c r="I150" s="4"/>
+      <c r="I150" s="8"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="16"/>
+      <c r="A151" s="17"/>
       <c r="B151" s="12"/>
       <c r="C151" s="21"/>
       <c r="D151" s="21"/>
@@ -2775,10 +2749,10 @@
       <c r="F151" s="21"/>
       <c r="G151" s="22"/>
       <c r="H151" s="23"/>
-      <c r="I151" s="4"/>
+      <c r="I151" s="8"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="16"/>
+      <c r="A152" s="17"/>
       <c r="B152" s="12"/>
       <c r="C152" s="21"/>
       <c r="D152" s="21"/>
@@ -2786,10 +2760,10 @@
       <c r="F152" s="21"/>
       <c r="G152" s="22"/>
       <c r="H152" s="23"/>
-      <c r="I152" s="4"/>
+      <c r="I152" s="8"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="16"/>
+      <c r="A153" s="17"/>
       <c r="B153" s="12"/>
       <c r="C153" s="21"/>
       <c r="D153" s="21"/>
@@ -2797,10 +2771,10 @@
       <c r="F153" s="21"/>
       <c r="G153" s="22"/>
       <c r="H153" s="23"/>
-      <c r="I153" s="4"/>
+      <c r="I153" s="8"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="16"/>
+      <c r="A154" s="17"/>
       <c r="B154" s="12"/>
       <c r="C154" s="21"/>
       <c r="D154" s="21"/>
@@ -2808,10 +2782,10 @@
       <c r="F154" s="21"/>
       <c r="G154" s="22"/>
       <c r="H154" s="23"/>
-      <c r="I154" s="4"/>
+      <c r="I154" s="8"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="16"/>
+      <c r="A155" s="17"/>
       <c r="B155" s="12"/>
       <c r="C155" s="21"/>
       <c r="D155" s="21"/>
@@ -2819,10 +2793,10 @@
       <c r="F155" s="21"/>
       <c r="G155" s="22"/>
       <c r="H155" s="23"/>
-      <c r="I155" s="4"/>
+      <c r="I155" s="8"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="16"/>
+      <c r="A156" s="17"/>
       <c r="B156" s="12"/>
       <c r="C156" s="21"/>
       <c r="D156" s="21"/>
@@ -2830,10 +2804,10 @@
       <c r="F156" s="21"/>
       <c r="G156" s="22"/>
       <c r="H156" s="23"/>
-      <c r="I156" s="4"/>
+      <c r="I156" s="8"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="16"/>
+      <c r="A157" s="17"/>
       <c r="B157" s="12"/>
       <c r="C157" s="21"/>
       <c r="D157" s="21"/>
@@ -2841,10 +2815,10 @@
       <c r="F157" s="21"/>
       <c r="G157" s="22"/>
       <c r="H157" s="23"/>
-      <c r="I157" s="4"/>
+      <c r="I157" s="8"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="16"/>
+      <c r="A158" s="17"/>
       <c r="B158" s="12"/>
       <c r="C158" s="21"/>
       <c r="D158" s="21"/>
@@ -2852,10 +2826,10 @@
       <c r="F158" s="21"/>
       <c r="G158" s="22"/>
       <c r="H158" s="23"/>
-      <c r="I158" s="4"/>
+      <c r="I158" s="8"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="16"/>
+      <c r="A159" s="17"/>
       <c r="B159" s="12"/>
       <c r="C159" s="21"/>
       <c r="D159" s="21"/>
@@ -2863,10 +2837,10 @@
       <c r="F159" s="21"/>
       <c r="G159" s="22"/>
       <c r="H159" s="23"/>
-      <c r="I159" s="4"/>
+      <c r="I159" s="8"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="16"/>
+      <c r="A160" s="17"/>
       <c r="B160" s="12"/>
       <c r="C160" s="21"/>
       <c r="D160" s="21"/>
@@ -2874,10 +2848,10 @@
       <c r="F160" s="21"/>
       <c r="G160" s="22"/>
       <c r="H160" s="23"/>
-      <c r="I160" s="4"/>
+      <c r="I160" s="8"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="16"/>
+      <c r="A161" s="17"/>
       <c r="B161" s="12"/>
       <c r="C161" s="21"/>
       <c r="D161" s="21"/>
@@ -2885,10 +2859,10 @@
       <c r="F161" s="21"/>
       <c r="G161" s="22"/>
       <c r="H161" s="23"/>
-      <c r="I161" s="4"/>
+      <c r="I161" s="8"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="16"/>
+      <c r="A162" s="17"/>
       <c r="B162" s="12"/>
       <c r="C162" s="21"/>
       <c r="D162" s="21"/>
@@ -2896,10 +2870,10 @@
       <c r="F162" s="21"/>
       <c r="G162" s="22"/>
       <c r="H162" s="23"/>
-      <c r="I162" s="4"/>
+      <c r="I162" s="8"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="16"/>
+      <c r="A163" s="17"/>
       <c r="B163" s="12"/>
       <c r="C163" s="21"/>
       <c r="D163" s="21"/>
@@ -2907,10 +2881,10 @@
       <c r="F163" s="21"/>
       <c r="G163" s="22"/>
       <c r="H163" s="23"/>
-      <c r="I163" s="4"/>
+      <c r="I163" s="8"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="16"/>
+      <c r="A164" s="17"/>
       <c r="B164" s="12"/>
       <c r="C164" s="21"/>
       <c r="D164" s="21"/>
@@ -2918,10 +2892,10 @@
       <c r="F164" s="21"/>
       <c r="G164" s="22"/>
       <c r="H164" s="23"/>
-      <c r="I164" s="4"/>
+      <c r="I164" s="8"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="16"/>
+      <c r="A165" s="17"/>
       <c r="B165" s="12"/>
       <c r="C165" s="21"/>
       <c r="D165" s="21"/>
@@ -2929,10 +2903,10 @@
       <c r="F165" s="21"/>
       <c r="G165" s="22"/>
       <c r="H165" s="23"/>
-      <c r="I165" s="4"/>
+      <c r="I165" s="8"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="16"/>
+      <c r="A166" s="17"/>
       <c r="B166" s="12"/>
       <c r="C166" s="21"/>
       <c r="D166" s="21"/>
@@ -2940,10 +2914,10 @@
       <c r="F166" s="21"/>
       <c r="G166" s="22"/>
       <c r="H166" s="23"/>
-      <c r="I166" s="4"/>
+      <c r="I166" s="8"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="16"/>
+      <c r="A167" s="17"/>
       <c r="B167" s="12"/>
       <c r="C167" s="21"/>
       <c r="D167" s="21"/>
@@ -2951,10 +2925,10 @@
       <c r="F167" s="21"/>
       <c r="G167" s="22"/>
       <c r="H167" s="23"/>
-      <c r="I167" s="4"/>
+      <c r="I167" s="8"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="16"/>
+      <c r="A168" s="17"/>
       <c r="B168" s="12"/>
       <c r="C168" s="21"/>
       <c r="D168" s="21"/>
@@ -2962,10 +2936,10 @@
       <c r="F168" s="21"/>
       <c r="G168" s="22"/>
       <c r="H168" s="23"/>
-      <c r="I168" s="4"/>
+      <c r="I168" s="8"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="16"/>
+      <c r="A169" s="17"/>
       <c r="B169" s="12"/>
       <c r="C169" s="21"/>
       <c r="D169" s="21"/>
@@ -2973,10 +2947,10 @@
       <c r="F169" s="21"/>
       <c r="G169" s="22"/>
       <c r="H169" s="23"/>
-      <c r="I169" s="4"/>
+      <c r="I169" s="8"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="16"/>
+      <c r="A170" s="17"/>
       <c r="B170" s="12"/>
       <c r="C170" s="21"/>
       <c r="D170" s="21"/>
@@ -2984,10 +2958,10 @@
       <c r="F170" s="21"/>
       <c r="G170" s="22"/>
       <c r="H170" s="23"/>
-      <c r="I170" s="4"/>
+      <c r="I170" s="8"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="16"/>
+      <c r="A171" s="17"/>
       <c r="B171" s="12"/>
       <c r="C171" s="21"/>
       <c r="D171" s="21"/>
@@ -2995,10 +2969,10 @@
       <c r="F171" s="21"/>
       <c r="G171" s="22"/>
       <c r="H171" s="23"/>
-      <c r="I171" s="4"/>
+      <c r="I171" s="8"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="16"/>
+      <c r="A172" s="17"/>
       <c r="B172" s="12"/>
       <c r="C172" s="21"/>
       <c r="D172" s="21"/>
@@ -3006,10 +2980,10 @@
       <c r="F172" s="21"/>
       <c r="G172" s="22"/>
       <c r="H172" s="23"/>
-      <c r="I172" s="4"/>
+      <c r="I172" s="8"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="16"/>
+      <c r="A173" s="17"/>
       <c r="B173" s="12"/>
       <c r="C173" s="21"/>
       <c r="D173" s="21"/>
@@ -3017,10 +2991,10 @@
       <c r="F173" s="21"/>
       <c r="G173" s="22"/>
       <c r="H173" s="23"/>
-      <c r="I173" s="4"/>
+      <c r="I173" s="8"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="16"/>
+      <c r="A174" s="17"/>
       <c r="B174" s="12"/>
       <c r="C174" s="21"/>
       <c r="D174" s="21"/>
@@ -3028,10 +3002,10 @@
       <c r="F174" s="21"/>
       <c r="G174" s="22"/>
       <c r="H174" s="23"/>
-      <c r="I174" s="4"/>
+      <c r="I174" s="8"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="16"/>
+      <c r="A175" s="17"/>
       <c r="B175" s="12"/>
       <c r="C175" s="21"/>
       <c r="D175" s="21"/>
@@ -3039,10 +3013,10 @@
       <c r="F175" s="21"/>
       <c r="G175" s="22"/>
       <c r="H175" s="23"/>
-      <c r="I175" s="4"/>
+      <c r="I175" s="8"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="16"/>
+      <c r="A176" s="17"/>
       <c r="B176" s="12"/>
       <c r="C176" s="21"/>
       <c r="D176" s="21"/>
@@ -3050,10 +3024,10 @@
       <c r="F176" s="21"/>
       <c r="G176" s="22"/>
       <c r="H176" s="23"/>
-      <c r="I176" s="4"/>
+      <c r="I176" s="8"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="16"/>
+      <c r="A177" s="17"/>
       <c r="B177" s="12"/>
       <c r="C177" s="21"/>
       <c r="D177" s="21"/>
@@ -3061,10 +3035,10 @@
       <c r="F177" s="21"/>
       <c r="G177" s="22"/>
       <c r="H177" s="23"/>
-      <c r="I177" s="4"/>
+      <c r="I177" s="8"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="16"/>
+      <c r="A178" s="17"/>
       <c r="B178" s="12"/>
       <c r="C178" s="21"/>
       <c r="D178" s="21"/>
@@ -3072,10 +3046,10 @@
       <c r="F178" s="21"/>
       <c r="G178" s="22"/>
       <c r="H178" s="23"/>
-      <c r="I178" s="4"/>
+      <c r="I178" s="8"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="16"/>
+      <c r="A179" s="17"/>
       <c r="B179" s="12"/>
       <c r="C179" s="21"/>
       <c r="D179" s="21"/>
@@ -3083,10 +3057,10 @@
       <c r="F179" s="21"/>
       <c r="G179" s="22"/>
       <c r="H179" s="23"/>
-      <c r="I179" s="4"/>
+      <c r="I179" s="8"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="A180" s="16"/>
+      <c r="A180" s="17"/>
       <c r="B180" s="12"/>
       <c r="C180" s="21"/>
       <c r="D180" s="21"/>
@@ -3094,10 +3068,10 @@
       <c r="F180" s="21"/>
       <c r="G180" s="22"/>
       <c r="H180" s="23"/>
-      <c r="I180" s="4"/>
+      <c r="I180" s="8"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="A181" s="16"/>
+      <c r="A181" s="17"/>
       <c r="B181" s="12"/>
       <c r="C181" s="21"/>
       <c r="D181" s="21"/>
@@ -3105,10 +3079,10 @@
       <c r="F181" s="21"/>
       <c r="G181" s="22"/>
       <c r="H181" s="23"/>
-      <c r="I181" s="4"/>
+      <c r="I181" s="8"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="A182" s="16"/>
+      <c r="A182" s="17"/>
       <c r="B182" s="12"/>
       <c r="C182" s="21"/>
       <c r="D182" s="21"/>
@@ -3116,10 +3090,10 @@
       <c r="F182" s="21"/>
       <c r="G182" s="22"/>
       <c r="H182" s="23"/>
-      <c r="I182" s="4"/>
+      <c r="I182" s="8"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="A183" s="16"/>
+      <c r="A183" s="17"/>
       <c r="B183" s="12"/>
       <c r="C183" s="21"/>
       <c r="D183" s="21"/>
@@ -3127,10 +3101,10 @@
       <c r="F183" s="21"/>
       <c r="G183" s="22"/>
       <c r="H183" s="23"/>
-      <c r="I183" s="4"/>
+      <c r="I183" s="8"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="A184" s="16"/>
+      <c r="A184" s="17"/>
       <c r="B184" s="12"/>
       <c r="C184" s="21"/>
       <c r="D184" s="21"/>
@@ -3138,10 +3112,10 @@
       <c r="F184" s="21"/>
       <c r="G184" s="22"/>
       <c r="H184" s="23"/>
-      <c r="I184" s="4"/>
+      <c r="I184" s="8"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="A185" s="16"/>
+      <c r="A185" s="17"/>
       <c r="B185" s="12"/>
       <c r="C185" s="21"/>
       <c r="D185" s="21"/>
@@ -3149,10 +3123,10 @@
       <c r="F185" s="21"/>
       <c r="G185" s="22"/>
       <c r="H185" s="23"/>
-      <c r="I185" s="4"/>
+      <c r="I185" s="8"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="16"/>
+      <c r="A186" s="17"/>
       <c r="B186" s="12"/>
       <c r="C186" s="21"/>
       <c r="D186" s="21"/>
@@ -3160,10 +3134,10 @@
       <c r="F186" s="21"/>
       <c r="G186" s="22"/>
       <c r="H186" s="23"/>
-      <c r="I186" s="4"/>
+      <c r="I186" s="8"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="16"/>
+      <c r="A187" s="17"/>
       <c r="B187" s="12"/>
       <c r="C187" s="21"/>
       <c r="D187" s="21"/>
@@ -3171,10 +3145,10 @@
       <c r="F187" s="21"/>
       <c r="G187" s="22"/>
       <c r="H187" s="23"/>
-      <c r="I187" s="4"/>
+      <c r="I187" s="8"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="16"/>
+      <c r="A188" s="17"/>
       <c r="B188" s="12"/>
       <c r="C188" s="21"/>
       <c r="D188" s="21"/>
@@ -3182,10 +3156,10 @@
       <c r="F188" s="21"/>
       <c r="G188" s="22"/>
       <c r="H188" s="23"/>
-      <c r="I188" s="4"/>
+      <c r="I188" s="8"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="16"/>
+      <c r="A189" s="17"/>
       <c r="B189" s="12"/>
       <c r="C189" s="21"/>
       <c r="D189" s="21"/>
@@ -3193,10 +3167,10 @@
       <c r="F189" s="21"/>
       <c r="G189" s="22"/>
       <c r="H189" s="23"/>
-      <c r="I189" s="4"/>
+      <c r="I189" s="8"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="A190" s="16"/>
+      <c r="A190" s="17"/>
       <c r="B190" s="12"/>
       <c r="C190" s="21"/>
       <c r="D190" s="21"/>
@@ -3204,10 +3178,10 @@
       <c r="F190" s="21"/>
       <c r="G190" s="22"/>
       <c r="H190" s="23"/>
-      <c r="I190" s="4"/>
+      <c r="I190" s="8"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="16"/>
+      <c r="A191" s="17"/>
       <c r="B191" s="12"/>
       <c r="C191" s="21"/>
       <c r="D191" s="21"/>
@@ -3215,10 +3189,10 @@
       <c r="F191" s="21"/>
       <c r="G191" s="22"/>
       <c r="H191" s="23"/>
-      <c r="I191" s="4"/>
+      <c r="I191" s="8"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="16"/>
+      <c r="A192" s="17"/>
       <c r="B192" s="12"/>
       <c r="C192" s="21"/>
       <c r="D192" s="21"/>
@@ -3226,10 +3200,10 @@
       <c r="F192" s="21"/>
       <c r="G192" s="22"/>
       <c r="H192" s="23"/>
-      <c r="I192" s="4"/>
+      <c r="I192" s="8"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="16"/>
+      <c r="A193" s="17"/>
       <c r="B193" s="12"/>
       <c r="C193" s="21"/>
       <c r="D193" s="21"/>
@@ -3237,10 +3211,10 @@
       <c r="F193" s="21"/>
       <c r="G193" s="22"/>
       <c r="H193" s="23"/>
-      <c r="I193" s="4"/>
+      <c r="I193" s="8"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="16"/>
+      <c r="A194" s="17"/>
       <c r="B194" s="12"/>
       <c r="C194" s="21"/>
       <c r="D194" s="21"/>
@@ -3248,10 +3222,10 @@
       <c r="F194" s="21"/>
       <c r="G194" s="22"/>
       <c r="H194" s="23"/>
-      <c r="I194" s="4"/>
+      <c r="I194" s="8"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="16"/>
+      <c r="A195" s="17"/>
       <c r="B195" s="12"/>
       <c r="C195" s="21"/>
       <c r="D195" s="21"/>
@@ -3259,10 +3233,10 @@
       <c r="F195" s="21"/>
       <c r="G195" s="22"/>
       <c r="H195" s="23"/>
-      <c r="I195" s="4"/>
+      <c r="I195" s="8"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="16"/>
+      <c r="A196" s="17"/>
       <c r="B196" s="12"/>
       <c r="C196" s="21"/>
       <c r="D196" s="21"/>
@@ -3270,10 +3244,10 @@
       <c r="F196" s="21"/>
       <c r="G196" s="22"/>
       <c r="H196" s="23"/>
-      <c r="I196" s="4"/>
+      <c r="I196" s="8"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="A197" s="16"/>
+      <c r="A197" s="17"/>
       <c r="B197" s="12"/>
       <c r="C197" s="21"/>
       <c r="D197" s="21"/>
@@ -3281,10 +3255,10 @@
       <c r="F197" s="21"/>
       <c r="G197" s="22"/>
       <c r="H197" s="23"/>
-      <c r="I197" s="4"/>
+      <c r="I197" s="8"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="16"/>
+      <c r="A198" s="17"/>
       <c r="B198" s="12"/>
       <c r="C198" s="21"/>
       <c r="D198" s="21"/>
@@ -3292,10 +3266,10 @@
       <c r="F198" s="21"/>
       <c r="G198" s="22"/>
       <c r="H198" s="23"/>
-      <c r="I198" s="4"/>
+      <c r="I198" s="8"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="A199" s="16"/>
+      <c r="A199" s="17"/>
       <c r="B199" s="12"/>
       <c r="C199" s="21"/>
       <c r="D199" s="21"/>
@@ -3303,10 +3277,10 @@
       <c r="F199" s="21"/>
       <c r="G199" s="22"/>
       <c r="H199" s="23"/>
-      <c r="I199" s="4"/>
+      <c r="I199" s="8"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="16"/>
+      <c r="A200" s="17"/>
       <c r="B200" s="12"/>
       <c r="C200" s="21"/>
       <c r="D200" s="21"/>
@@ -3314,10 +3288,10 @@
       <c r="F200" s="21"/>
       <c r="G200" s="22"/>
       <c r="H200" s="23"/>
-      <c r="I200" s="4"/>
+      <c r="I200" s="8"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="A201" s="16"/>
+      <c r="A201" s="17"/>
       <c r="B201" s="12"/>
       <c r="C201" s="21"/>
       <c r="D201" s="21"/>
@@ -3325,10 +3299,10 @@
       <c r="F201" s="21"/>
       <c r="G201" s="22"/>
       <c r="H201" s="23"/>
-      <c r="I201" s="4"/>
+      <c r="I201" s="8"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="A202" s="16"/>
+      <c r="A202" s="17"/>
       <c r="B202" s="12"/>
       <c r="C202" s="21"/>
       <c r="D202" s="21"/>
@@ -3336,10 +3310,10 @@
       <c r="F202" s="21"/>
       <c r="G202" s="22"/>
       <c r="H202" s="23"/>
-      <c r="I202" s="4"/>
+      <c r="I202" s="8"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="A203" s="16"/>
+      <c r="A203" s="17"/>
       <c r="B203" s="12"/>
       <c r="C203" s="21"/>
       <c r="D203" s="21"/>
@@ -3347,10 +3321,10 @@
       <c r="F203" s="21"/>
       <c r="G203" s="22"/>
       <c r="H203" s="23"/>
-      <c r="I203" s="4"/>
+      <c r="I203" s="8"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="A204" s="16"/>
+      <c r="A204" s="17"/>
       <c r="B204" s="12"/>
       <c r="C204" s="21"/>
       <c r="D204" s="21"/>
@@ -3358,10 +3332,10 @@
       <c r="F204" s="21"/>
       <c r="G204" s="22"/>
       <c r="H204" s="23"/>
-      <c r="I204" s="4"/>
+      <c r="I204" s="8"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="A205" s="16"/>
+      <c r="A205" s="17"/>
       <c r="B205" s="12"/>
       <c r="C205" s="21"/>
       <c r="D205" s="21"/>
@@ -3369,3774 +3343,3768 @@
       <c r="F205" s="21"/>
       <c r="G205" s="22"/>
       <c r="H205" s="23"/>
-      <c r="I205" s="4"/>
+      <c r="I205" s="8"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="A206" s="16"/>
-      <c r="B206" s="12"/>
-      <c r="C206" s="21"/>
-      <c r="D206" s="21"/>
-      <c r="E206" s="21"/>
-      <c r="F206" s="21"/>
+      <c r="A206" s="24"/>
       <c r="G206" s="22"/>
       <c r="H206" s="23"/>
-      <c r="I206" s="4"/>
+      <c r="I206" s="8"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="24"/>
       <c r="G207" s="22"/>
       <c r="H207" s="23"/>
-      <c r="I207" s="4"/>
+      <c r="I207" s="8"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="24"/>
       <c r="G208" s="22"/>
       <c r="H208" s="23"/>
-      <c r="I208" s="4"/>
+      <c r="I208" s="8"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="24"/>
       <c r="G209" s="22"/>
       <c r="H209" s="23"/>
-      <c r="I209" s="4"/>
+      <c r="I209" s="8"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="24"/>
       <c r="G210" s="22"/>
       <c r="H210" s="23"/>
-      <c r="I210" s="4"/>
+      <c r="I210" s="8"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="24"/>
       <c r="G211" s="22"/>
       <c r="H211" s="23"/>
-      <c r="I211" s="4"/>
+      <c r="I211" s="8"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="24"/>
       <c r="G212" s="22"/>
       <c r="H212" s="23"/>
-      <c r="I212" s="4"/>
+      <c r="I212" s="8"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="24"/>
       <c r="G213" s="22"/>
       <c r="H213" s="23"/>
-      <c r="I213" s="4"/>
+      <c r="I213" s="8"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="24"/>
       <c r="G214" s="22"/>
       <c r="H214" s="23"/>
-      <c r="I214" s="4"/>
+      <c r="I214" s="8"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="24"/>
       <c r="G215" s="22"/>
       <c r="H215" s="23"/>
-      <c r="I215" s="4"/>
+      <c r="I215" s="8"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="24"/>
       <c r="G216" s="22"/>
       <c r="H216" s="23"/>
-      <c r="I216" s="4"/>
+      <c r="I216" s="8"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="24"/>
       <c r="G217" s="22"/>
       <c r="H217" s="23"/>
-      <c r="I217" s="4"/>
+      <c r="I217" s="8"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="24"/>
       <c r="G218" s="22"/>
       <c r="H218" s="23"/>
-      <c r="I218" s="4"/>
+      <c r="I218" s="8"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="24"/>
       <c r="G219" s="22"/>
       <c r="H219" s="23"/>
-      <c r="I219" s="4"/>
+      <c r="I219" s="8"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="24"/>
       <c r="G220" s="22"/>
       <c r="H220" s="23"/>
-      <c r="I220" s="4"/>
+      <c r="I220" s="8"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
       <c r="A221" s="24"/>
       <c r="G221" s="22"/>
       <c r="H221" s="23"/>
-      <c r="I221" s="4"/>
+      <c r="I221" s="8"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="24"/>
       <c r="G222" s="22"/>
       <c r="H222" s="23"/>
-      <c r="I222" s="4"/>
+      <c r="I222" s="8"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="24"/>
       <c r="G223" s="22"/>
       <c r="H223" s="23"/>
-      <c r="I223" s="4"/>
+      <c r="I223" s="8"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
       <c r="A224" s="24"/>
       <c r="G224" s="22"/>
       <c r="H224" s="23"/>
-      <c r="I224" s="4"/>
+      <c r="I224" s="8"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="24"/>
       <c r="G225" s="22"/>
       <c r="H225" s="23"/>
-      <c r="I225" s="4"/>
+      <c r="I225" s="8"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
       <c r="A226" s="24"/>
       <c r="G226" s="22"/>
       <c r="H226" s="23"/>
-      <c r="I226" s="4"/>
+      <c r="I226" s="8"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
       <c r="A227" s="24"/>
       <c r="G227" s="22"/>
       <c r="H227" s="23"/>
-      <c r="I227" s="4"/>
+      <c r="I227" s="8"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="24"/>
       <c r="G228" s="22"/>
       <c r="H228" s="23"/>
-      <c r="I228" s="4"/>
+      <c r="I228" s="8"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="24"/>
       <c r="G229" s="22"/>
       <c r="H229" s="23"/>
-      <c r="I229" s="4"/>
+      <c r="I229" s="8"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="24"/>
       <c r="G230" s="22"/>
       <c r="H230" s="23"/>
-      <c r="I230" s="4"/>
+      <c r="I230" s="8"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
       <c r="A231" s="24"/>
       <c r="G231" s="22"/>
       <c r="H231" s="23"/>
-      <c r="I231" s="4"/>
+      <c r="I231" s="8"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
       <c r="A232" s="24"/>
       <c r="G232" s="22"/>
       <c r="H232" s="23"/>
-      <c r="I232" s="4"/>
+      <c r="I232" s="8"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="24"/>
       <c r="G233" s="22"/>
       <c r="H233" s="23"/>
-      <c r="I233" s="4"/>
+      <c r="I233" s="8"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="24"/>
       <c r="G234" s="22"/>
       <c r="H234" s="23"/>
-      <c r="I234" s="4"/>
+      <c r="I234" s="8"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
       <c r="A235" s="24"/>
       <c r="G235" s="22"/>
       <c r="H235" s="23"/>
-      <c r="I235" s="4"/>
+      <c r="I235" s="8"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="24"/>
       <c r="G236" s="22"/>
       <c r="H236" s="23"/>
-      <c r="I236" s="4"/>
+      <c r="I236" s="8"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="24"/>
       <c r="G237" s="22"/>
       <c r="H237" s="23"/>
-      <c r="I237" s="4"/>
+      <c r="I237" s="8"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
       <c r="A238" s="24"/>
       <c r="G238" s="22"/>
       <c r="H238" s="23"/>
-      <c r="I238" s="4"/>
+      <c r="I238" s="8"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
       <c r="A239" s="24"/>
       <c r="G239" s="22"/>
       <c r="H239" s="23"/>
-      <c r="I239" s="4"/>
+      <c r="I239" s="8"/>
     </row>
     <row r="240" ht="15.75" customHeight="1">
       <c r="A240" s="24"/>
       <c r="G240" s="22"/>
       <c r="H240" s="23"/>
-      <c r="I240" s="4"/>
+      <c r="I240" s="8"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
       <c r="A241" s="24"/>
       <c r="G241" s="22"/>
       <c r="H241" s="23"/>
-      <c r="I241" s="4"/>
+      <c r="I241" s="8"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
       <c r="A242" s="24"/>
       <c r="G242" s="22"/>
       <c r="H242" s="23"/>
-      <c r="I242" s="4"/>
+      <c r="I242" s="8"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
       <c r="A243" s="24"/>
       <c r="G243" s="22"/>
       <c r="H243" s="23"/>
-      <c r="I243" s="4"/>
+      <c r="I243" s="8"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
       <c r="A244" s="24"/>
       <c r="G244" s="22"/>
       <c r="H244" s="23"/>
-      <c r="I244" s="4"/>
+      <c r="I244" s="8"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
       <c r="A245" s="24"/>
       <c r="G245" s="22"/>
       <c r="H245" s="23"/>
-      <c r="I245" s="4"/>
+      <c r="I245" s="8"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
       <c r="A246" s="24"/>
       <c r="G246" s="22"/>
       <c r="H246" s="23"/>
-      <c r="I246" s="4"/>
+      <c r="I246" s="8"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
       <c r="A247" s="24"/>
       <c r="G247" s="22"/>
       <c r="H247" s="23"/>
-      <c r="I247" s="4"/>
+      <c r="I247" s="8"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
       <c r="A248" s="24"/>
       <c r="G248" s="22"/>
       <c r="H248" s="23"/>
-      <c r="I248" s="4"/>
+      <c r="I248" s="8"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
       <c r="A249" s="24"/>
       <c r="G249" s="22"/>
       <c r="H249" s="23"/>
-      <c r="I249" s="4"/>
+      <c r="I249" s="8"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
       <c r="A250" s="24"/>
       <c r="G250" s="22"/>
       <c r="H250" s="23"/>
-      <c r="I250" s="4"/>
+      <c r="I250" s="8"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
       <c r="A251" s="24"/>
       <c r="G251" s="22"/>
       <c r="H251" s="23"/>
-      <c r="I251" s="4"/>
+      <c r="I251" s="8"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
       <c r="A252" s="24"/>
       <c r="G252" s="22"/>
       <c r="H252" s="23"/>
-      <c r="I252" s="4"/>
+      <c r="I252" s="8"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
       <c r="A253" s="24"/>
       <c r="G253" s="22"/>
       <c r="H253" s="23"/>
-      <c r="I253" s="4"/>
+      <c r="I253" s="8"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
       <c r="A254" s="24"/>
       <c r="G254" s="22"/>
       <c r="H254" s="23"/>
-      <c r="I254" s="4"/>
+      <c r="I254" s="8"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
       <c r="A255" s="24"/>
       <c r="G255" s="22"/>
       <c r="H255" s="23"/>
-      <c r="I255" s="4"/>
+      <c r="I255" s="8"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
       <c r="A256" s="24"/>
       <c r="G256" s="22"/>
       <c r="H256" s="23"/>
-      <c r="I256" s="4"/>
+      <c r="I256" s="8"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
       <c r="A257" s="24"/>
       <c r="G257" s="22"/>
       <c r="H257" s="23"/>
-      <c r="I257" s="4"/>
+      <c r="I257" s="8"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
       <c r="A258" s="24"/>
       <c r="G258" s="22"/>
       <c r="H258" s="23"/>
-      <c r="I258" s="4"/>
+      <c r="I258" s="8"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
       <c r="A259" s="24"/>
       <c r="G259" s="22"/>
       <c r="H259" s="23"/>
-      <c r="I259" s="4"/>
+      <c r="I259" s="8"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
       <c r="A260" s="24"/>
       <c r="G260" s="22"/>
       <c r="H260" s="23"/>
-      <c r="I260" s="4"/>
+      <c r="I260" s="8"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
       <c r="A261" s="24"/>
       <c r="G261" s="22"/>
       <c r="H261" s="23"/>
-      <c r="I261" s="4"/>
+      <c r="I261" s="8"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
       <c r="A262" s="24"/>
       <c r="G262" s="22"/>
       <c r="H262" s="23"/>
-      <c r="I262" s="4"/>
+      <c r="I262" s="8"/>
     </row>
     <row r="263" ht="15.75" customHeight="1">
       <c r="A263" s="24"/>
       <c r="G263" s="22"/>
       <c r="H263" s="23"/>
-      <c r="I263" s="4"/>
+      <c r="I263" s="8"/>
     </row>
     <row r="264" ht="15.75" customHeight="1">
       <c r="A264" s="24"/>
       <c r="G264" s="22"/>
       <c r="H264" s="23"/>
-      <c r="I264" s="4"/>
+      <c r="I264" s="8"/>
     </row>
     <row r="265" ht="15.75" customHeight="1">
       <c r="A265" s="24"/>
       <c r="G265" s="22"/>
       <c r="H265" s="23"/>
-      <c r="I265" s="4"/>
+      <c r="I265" s="8"/>
     </row>
     <row r="266" ht="15.75" customHeight="1">
       <c r="A266" s="24"/>
       <c r="G266" s="22"/>
       <c r="H266" s="23"/>
-      <c r="I266" s="4"/>
+      <c r="I266" s="8"/>
     </row>
     <row r="267" ht="15.75" customHeight="1">
       <c r="A267" s="24"/>
       <c r="G267" s="22"/>
       <c r="H267" s="23"/>
-      <c r="I267" s="4"/>
+      <c r="I267" s="8"/>
     </row>
     <row r="268" ht="15.75" customHeight="1">
       <c r="A268" s="24"/>
       <c r="G268" s="22"/>
       <c r="H268" s="23"/>
-      <c r="I268" s="4"/>
+      <c r="I268" s="8"/>
     </row>
     <row r="269" ht="15.75" customHeight="1">
       <c r="A269" s="24"/>
       <c r="G269" s="22"/>
       <c r="H269" s="23"/>
-      <c r="I269" s="4"/>
+      <c r="I269" s="8"/>
     </row>
     <row r="270" ht="15.75" customHeight="1">
       <c r="A270" s="24"/>
       <c r="G270" s="22"/>
       <c r="H270" s="23"/>
-      <c r="I270" s="4"/>
+      <c r="I270" s="8"/>
     </row>
     <row r="271" ht="15.75" customHeight="1">
       <c r="A271" s="24"/>
       <c r="G271" s="22"/>
       <c r="H271" s="23"/>
-      <c r="I271" s="4"/>
+      <c r="I271" s="8"/>
     </row>
     <row r="272" ht="15.75" customHeight="1">
       <c r="A272" s="24"/>
       <c r="G272" s="22"/>
       <c r="H272" s="23"/>
-      <c r="I272" s="4"/>
+      <c r="I272" s="8"/>
     </row>
     <row r="273" ht="15.75" customHeight="1">
       <c r="A273" s="24"/>
       <c r="G273" s="22"/>
       <c r="H273" s="23"/>
-      <c r="I273" s="4"/>
+      <c r="I273" s="8"/>
     </row>
     <row r="274" ht="15.75" customHeight="1">
       <c r="A274" s="24"/>
       <c r="G274" s="22"/>
       <c r="H274" s="23"/>
-      <c r="I274" s="4"/>
+      <c r="I274" s="8"/>
     </row>
     <row r="275" ht="15.75" customHeight="1">
       <c r="A275" s="24"/>
       <c r="G275" s="22"/>
       <c r="H275" s="23"/>
-      <c r="I275" s="4"/>
+      <c r="I275" s="8"/>
     </row>
     <row r="276" ht="15.75" customHeight="1">
       <c r="A276" s="24"/>
       <c r="G276" s="22"/>
       <c r="H276" s="23"/>
-      <c r="I276" s="4"/>
+      <c r="I276" s="8"/>
     </row>
     <row r="277" ht="15.75" customHeight="1">
       <c r="A277" s="24"/>
       <c r="G277" s="22"/>
       <c r="H277" s="23"/>
-      <c r="I277" s="4"/>
+      <c r="I277" s="8"/>
     </row>
     <row r="278" ht="15.75" customHeight="1">
       <c r="A278" s="24"/>
       <c r="G278" s="22"/>
       <c r="H278" s="23"/>
-      <c r="I278" s="4"/>
+      <c r="I278" s="8"/>
     </row>
     <row r="279" ht="15.75" customHeight="1">
       <c r="A279" s="24"/>
       <c r="G279" s="22"/>
       <c r="H279" s="23"/>
-      <c r="I279" s="4"/>
+      <c r="I279" s="8"/>
     </row>
     <row r="280" ht="15.75" customHeight="1">
       <c r="A280" s="24"/>
       <c r="G280" s="22"/>
       <c r="H280" s="23"/>
-      <c r="I280" s="4"/>
+      <c r="I280" s="8"/>
     </row>
     <row r="281" ht="15.75" customHeight="1">
       <c r="A281" s="24"/>
       <c r="G281" s="22"/>
       <c r="H281" s="23"/>
-      <c r="I281" s="4"/>
+      <c r="I281" s="8"/>
     </row>
     <row r="282" ht="15.75" customHeight="1">
       <c r="A282" s="24"/>
       <c r="G282" s="22"/>
       <c r="H282" s="23"/>
-      <c r="I282" s="4"/>
+      <c r="I282" s="8"/>
     </row>
     <row r="283" ht="15.75" customHeight="1">
       <c r="A283" s="24"/>
       <c r="G283" s="22"/>
       <c r="H283" s="23"/>
-      <c r="I283" s="4"/>
+      <c r="I283" s="8"/>
     </row>
     <row r="284" ht="15.75" customHeight="1">
       <c r="A284" s="24"/>
       <c r="G284" s="22"/>
       <c r="H284" s="23"/>
-      <c r="I284" s="4"/>
+      <c r="I284" s="8"/>
     </row>
     <row r="285" ht="15.75" customHeight="1">
       <c r="A285" s="24"/>
       <c r="G285" s="22"/>
       <c r="H285" s="23"/>
-      <c r="I285" s="4"/>
+      <c r="I285" s="8"/>
     </row>
     <row r="286" ht="15.75" customHeight="1">
       <c r="A286" s="24"/>
       <c r="G286" s="22"/>
       <c r="H286" s="23"/>
-      <c r="I286" s="4"/>
+      <c r="I286" s="8"/>
     </row>
     <row r="287" ht="15.75" customHeight="1">
       <c r="A287" s="24"/>
       <c r="G287" s="22"/>
       <c r="H287" s="23"/>
-      <c r="I287" s="4"/>
+      <c r="I287" s="8"/>
     </row>
     <row r="288" ht="15.75" customHeight="1">
       <c r="A288" s="24"/>
       <c r="G288" s="22"/>
       <c r="H288" s="23"/>
-      <c r="I288" s="4"/>
+      <c r="I288" s="8"/>
     </row>
     <row r="289" ht="15.75" customHeight="1">
       <c r="A289" s="24"/>
       <c r="G289" s="22"/>
       <c r="H289" s="23"/>
-      <c r="I289" s="4"/>
+      <c r="I289" s="8"/>
     </row>
     <row r="290" ht="15.75" customHeight="1">
       <c r="A290" s="24"/>
       <c r="G290" s="22"/>
       <c r="H290" s="23"/>
-      <c r="I290" s="4"/>
+      <c r="I290" s="8"/>
     </row>
     <row r="291" ht="15.75" customHeight="1">
       <c r="A291" s="24"/>
       <c r="G291" s="22"/>
       <c r="H291" s="23"/>
-      <c r="I291" s="4"/>
+      <c r="I291" s="8"/>
     </row>
     <row r="292" ht="15.75" customHeight="1">
       <c r="A292" s="24"/>
       <c r="G292" s="22"/>
       <c r="H292" s="23"/>
-      <c r="I292" s="4"/>
+      <c r="I292" s="8"/>
     </row>
     <row r="293" ht="15.75" customHeight="1">
       <c r="A293" s="24"/>
       <c r="G293" s="22"/>
       <c r="H293" s="23"/>
-      <c r="I293" s="4"/>
+      <c r="I293" s="8"/>
     </row>
     <row r="294" ht="15.75" customHeight="1">
       <c r="A294" s="24"/>
       <c r="G294" s="22"/>
       <c r="H294" s="23"/>
-      <c r="I294" s="4"/>
+      <c r="I294" s="8"/>
     </row>
     <row r="295" ht="15.75" customHeight="1">
       <c r="A295" s="24"/>
       <c r="G295" s="22"/>
       <c r="H295" s="23"/>
-      <c r="I295" s="4"/>
+      <c r="I295" s="8"/>
     </row>
     <row r="296" ht="15.75" customHeight="1">
       <c r="A296" s="24"/>
       <c r="G296" s="22"/>
       <c r="H296" s="23"/>
-      <c r="I296" s="4"/>
+      <c r="I296" s="8"/>
     </row>
     <row r="297" ht="15.75" customHeight="1">
       <c r="A297" s="24"/>
       <c r="G297" s="22"/>
       <c r="H297" s="23"/>
-      <c r="I297" s="4"/>
+      <c r="I297" s="8"/>
     </row>
     <row r="298" ht="15.75" customHeight="1">
       <c r="A298" s="24"/>
       <c r="G298" s="22"/>
       <c r="H298" s="23"/>
-      <c r="I298" s="4"/>
+      <c r="I298" s="8"/>
     </row>
     <row r="299" ht="15.75" customHeight="1">
       <c r="A299" s="24"/>
       <c r="G299" s="22"/>
       <c r="H299" s="23"/>
-      <c r="I299" s="4"/>
+      <c r="I299" s="8"/>
     </row>
     <row r="300" ht="15.75" customHeight="1">
       <c r="A300" s="24"/>
       <c r="G300" s="22"/>
       <c r="H300" s="23"/>
-      <c r="I300" s="4"/>
+      <c r="I300" s="8"/>
     </row>
     <row r="301" ht="15.75" customHeight="1">
       <c r="A301" s="24"/>
       <c r="G301" s="22"/>
       <c r="H301" s="23"/>
-      <c r="I301" s="4"/>
+      <c r="I301" s="8"/>
     </row>
     <row r="302" ht="15.75" customHeight="1">
       <c r="A302" s="24"/>
       <c r="G302" s="22"/>
       <c r="H302" s="23"/>
-      <c r="I302" s="4"/>
+      <c r="I302" s="8"/>
     </row>
     <row r="303" ht="15.75" customHeight="1">
       <c r="A303" s="24"/>
       <c r="G303" s="22"/>
       <c r="H303" s="23"/>
-      <c r="I303" s="4"/>
+      <c r="I303" s="8"/>
     </row>
     <row r="304" ht="15.75" customHeight="1">
       <c r="A304" s="24"/>
       <c r="G304" s="22"/>
       <c r="H304" s="23"/>
-      <c r="I304" s="4"/>
+      <c r="I304" s="8"/>
     </row>
     <row r="305" ht="15.75" customHeight="1">
       <c r="A305" s="24"/>
       <c r="G305" s="22"/>
       <c r="H305" s="23"/>
-      <c r="I305" s="4"/>
+      <c r="I305" s="8"/>
     </row>
     <row r="306" ht="15.75" customHeight="1">
       <c r="A306" s="24"/>
       <c r="G306" s="22"/>
       <c r="H306" s="23"/>
-      <c r="I306" s="4"/>
+      <c r="I306" s="8"/>
     </row>
     <row r="307" ht="15.75" customHeight="1">
       <c r="A307" s="24"/>
       <c r="G307" s="22"/>
       <c r="H307" s="23"/>
-      <c r="I307" s="4"/>
+      <c r="I307" s="8"/>
     </row>
     <row r="308" ht="15.75" customHeight="1">
       <c r="A308" s="24"/>
       <c r="G308" s="22"/>
       <c r="H308" s="23"/>
-      <c r="I308" s="4"/>
+      <c r="I308" s="8"/>
     </row>
     <row r="309" ht="15.75" customHeight="1">
       <c r="A309" s="24"/>
       <c r="G309" s="22"/>
       <c r="H309" s="23"/>
-      <c r="I309" s="4"/>
+      <c r="I309" s="8"/>
     </row>
     <row r="310" ht="15.75" customHeight="1">
       <c r="A310" s="24"/>
       <c r="G310" s="22"/>
       <c r="H310" s="23"/>
-      <c r="I310" s="4"/>
+      <c r="I310" s="8"/>
     </row>
     <row r="311" ht="15.75" customHeight="1">
       <c r="A311" s="24"/>
       <c r="G311" s="22"/>
       <c r="H311" s="23"/>
-      <c r="I311" s="4"/>
+      <c r="I311" s="8"/>
     </row>
     <row r="312" ht="15.75" customHeight="1">
       <c r="A312" s="24"/>
       <c r="G312" s="22"/>
       <c r="H312" s="23"/>
-      <c r="I312" s="4"/>
+      <c r="I312" s="8"/>
     </row>
     <row r="313" ht="15.75" customHeight="1">
       <c r="A313" s="24"/>
       <c r="G313" s="22"/>
       <c r="H313" s="23"/>
-      <c r="I313" s="4"/>
+      <c r="I313" s="8"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
       <c r="A314" s="24"/>
       <c r="G314" s="22"/>
       <c r="H314" s="23"/>
-      <c r="I314" s="4"/>
+      <c r="I314" s="8"/>
     </row>
     <row r="315" ht="15.75" customHeight="1">
       <c r="A315" s="24"/>
       <c r="G315" s="22"/>
       <c r="H315" s="23"/>
-      <c r="I315" s="4"/>
+      <c r="I315" s="8"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
       <c r="A316" s="24"/>
       <c r="G316" s="22"/>
       <c r="H316" s="23"/>
-      <c r="I316" s="4"/>
+      <c r="I316" s="8"/>
     </row>
     <row r="317" ht="15.75" customHeight="1">
       <c r="A317" s="24"/>
       <c r="G317" s="22"/>
       <c r="H317" s="23"/>
-      <c r="I317" s="4"/>
+      <c r="I317" s="8"/>
     </row>
     <row r="318" ht="15.75" customHeight="1">
       <c r="A318" s="24"/>
       <c r="G318" s="22"/>
       <c r="H318" s="23"/>
-      <c r="I318" s="4"/>
+      <c r="I318" s="8"/>
     </row>
     <row r="319" ht="15.75" customHeight="1">
       <c r="A319" s="24"/>
       <c r="G319" s="22"/>
       <c r="H319" s="23"/>
-      <c r="I319" s="4"/>
+      <c r="I319" s="8"/>
     </row>
     <row r="320" ht="15.75" customHeight="1">
       <c r="A320" s="24"/>
       <c r="G320" s="22"/>
       <c r="H320" s="23"/>
-      <c r="I320" s="4"/>
+      <c r="I320" s="8"/>
     </row>
     <row r="321" ht="15.75" customHeight="1">
       <c r="A321" s="24"/>
       <c r="G321" s="22"/>
       <c r="H321" s="23"/>
-      <c r="I321" s="4"/>
+      <c r="I321" s="8"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
       <c r="A322" s="24"/>
       <c r="G322" s="22"/>
       <c r="H322" s="23"/>
-      <c r="I322" s="4"/>
+      <c r="I322" s="8"/>
     </row>
     <row r="323" ht="15.75" customHeight="1">
       <c r="A323" s="24"/>
       <c r="G323" s="22"/>
       <c r="H323" s="23"/>
-      <c r="I323" s="4"/>
+      <c r="I323" s="8"/>
     </row>
     <row r="324" ht="15.75" customHeight="1">
       <c r="A324" s="24"/>
       <c r="G324" s="22"/>
       <c r="H324" s="23"/>
-      <c r="I324" s="4"/>
+      <c r="I324" s="8"/>
     </row>
     <row r="325" ht="15.75" customHeight="1">
       <c r="A325" s="24"/>
       <c r="G325" s="22"/>
       <c r="H325" s="23"/>
-      <c r="I325" s="4"/>
+      <c r="I325" s="8"/>
     </row>
     <row r="326" ht="15.75" customHeight="1">
       <c r="A326" s="24"/>
       <c r="G326" s="22"/>
       <c r="H326" s="23"/>
-      <c r="I326" s="4"/>
+      <c r="I326" s="8"/>
     </row>
     <row r="327" ht="15.75" customHeight="1">
       <c r="A327" s="24"/>
       <c r="G327" s="22"/>
       <c r="H327" s="23"/>
-      <c r="I327" s="4"/>
+      <c r="I327" s="8"/>
     </row>
     <row r="328" ht="15.75" customHeight="1">
       <c r="A328" s="24"/>
       <c r="G328" s="22"/>
       <c r="H328" s="23"/>
-      <c r="I328" s="4"/>
+      <c r="I328" s="8"/>
     </row>
     <row r="329" ht="15.75" customHeight="1">
       <c r="A329" s="24"/>
       <c r="G329" s="22"/>
       <c r="H329" s="23"/>
-      <c r="I329" s="4"/>
+      <c r="I329" s="8"/>
     </row>
     <row r="330" ht="15.75" customHeight="1">
       <c r="A330" s="24"/>
       <c r="G330" s="22"/>
       <c r="H330" s="23"/>
-      <c r="I330" s="4"/>
+      <c r="I330" s="8"/>
     </row>
     <row r="331" ht="15.75" customHeight="1">
       <c r="A331" s="24"/>
       <c r="G331" s="22"/>
       <c r="H331" s="23"/>
-      <c r="I331" s="4"/>
+      <c r="I331" s="8"/>
     </row>
     <row r="332" ht="15.75" customHeight="1">
       <c r="A332" s="24"/>
       <c r="G332" s="22"/>
       <c r="H332" s="23"/>
-      <c r="I332" s="4"/>
+      <c r="I332" s="8"/>
     </row>
     <row r="333" ht="15.75" customHeight="1">
       <c r="A333" s="24"/>
       <c r="G333" s="22"/>
       <c r="H333" s="23"/>
-      <c r="I333" s="4"/>
+      <c r="I333" s="8"/>
     </row>
     <row r="334" ht="15.75" customHeight="1">
       <c r="A334" s="24"/>
       <c r="G334" s="22"/>
       <c r="H334" s="23"/>
-      <c r="I334" s="4"/>
+      <c r="I334" s="8"/>
     </row>
     <row r="335" ht="15.75" customHeight="1">
       <c r="A335" s="24"/>
       <c r="G335" s="22"/>
       <c r="H335" s="23"/>
-      <c r="I335" s="4"/>
+      <c r="I335" s="8"/>
     </row>
     <row r="336" ht="15.75" customHeight="1">
       <c r="A336" s="24"/>
       <c r="G336" s="22"/>
       <c r="H336" s="23"/>
-      <c r="I336" s="4"/>
+      <c r="I336" s="8"/>
     </row>
     <row r="337" ht="15.75" customHeight="1">
       <c r="A337" s="24"/>
       <c r="G337" s="22"/>
       <c r="H337" s="23"/>
-      <c r="I337" s="4"/>
+      <c r="I337" s="8"/>
     </row>
     <row r="338" ht="15.75" customHeight="1">
       <c r="A338" s="24"/>
       <c r="G338" s="22"/>
       <c r="H338" s="23"/>
-      <c r="I338" s="4"/>
+      <c r="I338" s="8"/>
     </row>
     <row r="339" ht="15.75" customHeight="1">
       <c r="A339" s="24"/>
       <c r="G339" s="22"/>
       <c r="H339" s="23"/>
-      <c r="I339" s="4"/>
+      <c r="I339" s="8"/>
     </row>
     <row r="340" ht="15.75" customHeight="1">
       <c r="A340" s="24"/>
       <c r="G340" s="22"/>
       <c r="H340" s="23"/>
-      <c r="I340" s="4"/>
+      <c r="I340" s="8"/>
     </row>
     <row r="341" ht="15.75" customHeight="1">
       <c r="A341" s="24"/>
       <c r="G341" s="22"/>
       <c r="H341" s="23"/>
-      <c r="I341" s="4"/>
+      <c r="I341" s="8"/>
     </row>
     <row r="342" ht="15.75" customHeight="1">
       <c r="A342" s="24"/>
       <c r="G342" s="22"/>
       <c r="H342" s="23"/>
-      <c r="I342" s="4"/>
+      <c r="I342" s="8"/>
     </row>
     <row r="343" ht="15.75" customHeight="1">
       <c r="A343" s="24"/>
       <c r="G343" s="22"/>
       <c r="H343" s="23"/>
-      <c r="I343" s="4"/>
+      <c r="I343" s="8"/>
     </row>
     <row r="344" ht="15.75" customHeight="1">
       <c r="A344" s="24"/>
       <c r="G344" s="22"/>
       <c r="H344" s="23"/>
-      <c r="I344" s="4"/>
+      <c r="I344" s="8"/>
     </row>
     <row r="345" ht="15.75" customHeight="1">
       <c r="A345" s="24"/>
       <c r="G345" s="22"/>
       <c r="H345" s="23"/>
-      <c r="I345" s="4"/>
+      <c r="I345" s="8"/>
     </row>
     <row r="346" ht="15.75" customHeight="1">
       <c r="A346" s="24"/>
       <c r="G346" s="22"/>
       <c r="H346" s="23"/>
-      <c r="I346" s="4"/>
+      <c r="I346" s="8"/>
     </row>
     <row r="347" ht="15.75" customHeight="1">
       <c r="A347" s="24"/>
       <c r="G347" s="22"/>
       <c r="H347" s="23"/>
-      <c r="I347" s="4"/>
+      <c r="I347" s="8"/>
     </row>
     <row r="348" ht="15.75" customHeight="1">
       <c r="A348" s="24"/>
       <c r="G348" s="22"/>
       <c r="H348" s="23"/>
-      <c r="I348" s="4"/>
+      <c r="I348" s="8"/>
     </row>
     <row r="349" ht="15.75" customHeight="1">
       <c r="A349" s="24"/>
       <c r="G349" s="22"/>
       <c r="H349" s="23"/>
-      <c r="I349" s="4"/>
+      <c r="I349" s="8"/>
     </row>
     <row r="350" ht="15.75" customHeight="1">
       <c r="A350" s="24"/>
       <c r="G350" s="22"/>
       <c r="H350" s="23"/>
-      <c r="I350" s="4"/>
+      <c r="I350" s="8"/>
     </row>
     <row r="351" ht="15.75" customHeight="1">
       <c r="A351" s="24"/>
       <c r="G351" s="22"/>
       <c r="H351" s="23"/>
-      <c r="I351" s="4"/>
+      <c r="I351" s="8"/>
     </row>
     <row r="352" ht="15.75" customHeight="1">
       <c r="A352" s="24"/>
       <c r="G352" s="22"/>
       <c r="H352" s="23"/>
-      <c r="I352" s="4"/>
+      <c r="I352" s="8"/>
     </row>
     <row r="353" ht="15.75" customHeight="1">
       <c r="A353" s="24"/>
       <c r="G353" s="22"/>
       <c r="H353" s="23"/>
-      <c r="I353" s="4"/>
+      <c r="I353" s="8"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
       <c r="A354" s="24"/>
       <c r="G354" s="22"/>
       <c r="H354" s="23"/>
-      <c r="I354" s="4"/>
+      <c r="I354" s="8"/>
     </row>
     <row r="355" ht="15.75" customHeight="1">
       <c r="A355" s="24"/>
       <c r="G355" s="22"/>
       <c r="H355" s="23"/>
-      <c r="I355" s="4"/>
+      <c r="I355" s="8"/>
     </row>
     <row r="356" ht="15.75" customHeight="1">
       <c r="A356" s="24"/>
       <c r="G356" s="22"/>
       <c r="H356" s="23"/>
-      <c r="I356" s="4"/>
+      <c r="I356" s="8"/>
     </row>
     <row r="357" ht="15.75" customHeight="1">
       <c r="A357" s="24"/>
       <c r="G357" s="22"/>
       <c r="H357" s="23"/>
-      <c r="I357" s="4"/>
+      <c r="I357" s="8"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
       <c r="A358" s="24"/>
       <c r="G358" s="22"/>
       <c r="H358" s="23"/>
-      <c r="I358" s="4"/>
+      <c r="I358" s="8"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
       <c r="A359" s="24"/>
       <c r="G359" s="22"/>
       <c r="H359" s="23"/>
-      <c r="I359" s="4"/>
+      <c r="I359" s="8"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
       <c r="A360" s="24"/>
       <c r="G360" s="22"/>
       <c r="H360" s="23"/>
-      <c r="I360" s="4"/>
+      <c r="I360" s="8"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
       <c r="A361" s="24"/>
       <c r="G361" s="22"/>
       <c r="H361" s="23"/>
-      <c r="I361" s="4"/>
+      <c r="I361" s="8"/>
     </row>
     <row r="362" ht="15.75" customHeight="1">
       <c r="A362" s="24"/>
       <c r="G362" s="22"/>
       <c r="H362" s="23"/>
-      <c r="I362" s="4"/>
+      <c r="I362" s="8"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
       <c r="A363" s="24"/>
       <c r="G363" s="22"/>
       <c r="H363" s="23"/>
-      <c r="I363" s="4"/>
+      <c r="I363" s="8"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
       <c r="A364" s="24"/>
       <c r="G364" s="22"/>
       <c r="H364" s="23"/>
-      <c r="I364" s="4"/>
+      <c r="I364" s="8"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
       <c r="A365" s="24"/>
       <c r="G365" s="22"/>
       <c r="H365" s="23"/>
-      <c r="I365" s="4"/>
+      <c r="I365" s="8"/>
     </row>
     <row r="366" ht="15.75" customHeight="1">
       <c r="A366" s="24"/>
       <c r="G366" s="22"/>
       <c r="H366" s="23"/>
-      <c r="I366" s="4"/>
+      <c r="I366" s="8"/>
     </row>
     <row r="367" ht="15.75" customHeight="1">
       <c r="A367" s="24"/>
       <c r="G367" s="22"/>
       <c r="H367" s="23"/>
-      <c r="I367" s="4"/>
+      <c r="I367" s="8"/>
     </row>
     <row r="368" ht="15.75" customHeight="1">
       <c r="A368" s="24"/>
       <c r="G368" s="22"/>
       <c r="H368" s="23"/>
-      <c r="I368" s="4"/>
+      <c r="I368" s="8"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
       <c r="A369" s="24"/>
       <c r="G369" s="22"/>
       <c r="H369" s="23"/>
-      <c r="I369" s="4"/>
+      <c r="I369" s="8"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
       <c r="A370" s="24"/>
       <c r="G370" s="22"/>
       <c r="H370" s="23"/>
-      <c r="I370" s="4"/>
+      <c r="I370" s="8"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
       <c r="A371" s="24"/>
       <c r="G371" s="22"/>
       <c r="H371" s="23"/>
-      <c r="I371" s="4"/>
+      <c r="I371" s="8"/>
     </row>
     <row r="372" ht="15.75" customHeight="1">
       <c r="A372" s="24"/>
       <c r="G372" s="22"/>
       <c r="H372" s="23"/>
-      <c r="I372" s="4"/>
+      <c r="I372" s="8"/>
     </row>
     <row r="373" ht="15.75" customHeight="1">
       <c r="A373" s="24"/>
       <c r="G373" s="22"/>
       <c r="H373" s="23"/>
-      <c r="I373" s="4"/>
+      <c r="I373" s="8"/>
     </row>
     <row r="374" ht="15.75" customHeight="1">
       <c r="A374" s="24"/>
       <c r="G374" s="22"/>
       <c r="H374" s="23"/>
-      <c r="I374" s="4"/>
+      <c r="I374" s="8"/>
     </row>
     <row r="375" ht="15.75" customHeight="1">
       <c r="A375" s="24"/>
       <c r="G375" s="22"/>
       <c r="H375" s="23"/>
-      <c r="I375" s="4"/>
+      <c r="I375" s="8"/>
     </row>
     <row r="376" ht="15.75" customHeight="1">
       <c r="A376" s="24"/>
       <c r="G376" s="22"/>
       <c r="H376" s="23"/>
-      <c r="I376" s="4"/>
+      <c r="I376" s="8"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
       <c r="A377" s="24"/>
       <c r="G377" s="22"/>
       <c r="H377" s="23"/>
-      <c r="I377" s="4"/>
+      <c r="I377" s="8"/>
     </row>
     <row r="378" ht="15.75" customHeight="1">
       <c r="A378" s="24"/>
       <c r="G378" s="22"/>
       <c r="H378" s="23"/>
-      <c r="I378" s="4"/>
+      <c r="I378" s="8"/>
     </row>
     <row r="379" ht="15.75" customHeight="1">
       <c r="A379" s="24"/>
       <c r="G379" s="22"/>
       <c r="H379" s="23"/>
-      <c r="I379" s="4"/>
+      <c r="I379" s="8"/>
     </row>
     <row r="380" ht="15.75" customHeight="1">
       <c r="A380" s="24"/>
       <c r="G380" s="22"/>
       <c r="H380" s="23"/>
-      <c r="I380" s="4"/>
+      <c r="I380" s="8"/>
     </row>
     <row r="381" ht="15.75" customHeight="1">
       <c r="A381" s="24"/>
       <c r="G381" s="22"/>
       <c r="H381" s="23"/>
-      <c r="I381" s="4"/>
+      <c r="I381" s="8"/>
     </row>
     <row r="382" ht="15.75" customHeight="1">
       <c r="A382" s="24"/>
       <c r="G382" s="22"/>
       <c r="H382" s="23"/>
-      <c r="I382" s="4"/>
+      <c r="I382" s="8"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
       <c r="A383" s="24"/>
       <c r="G383" s="22"/>
       <c r="H383" s="23"/>
-      <c r="I383" s="4"/>
+      <c r="I383" s="8"/>
     </row>
     <row r="384" ht="15.75" customHeight="1">
       <c r="A384" s="24"/>
       <c r="G384" s="22"/>
       <c r="H384" s="23"/>
-      <c r="I384" s="4"/>
+      <c r="I384" s="8"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
       <c r="A385" s="24"/>
       <c r="G385" s="22"/>
       <c r="H385" s="23"/>
-      <c r="I385" s="4"/>
+      <c r="I385" s="8"/>
     </row>
     <row r="386" ht="15.75" customHeight="1">
       <c r="A386" s="24"/>
       <c r="G386" s="22"/>
       <c r="H386" s="23"/>
-      <c r="I386" s="4"/>
+      <c r="I386" s="8"/>
     </row>
     <row r="387" ht="15.75" customHeight="1">
       <c r="A387" s="24"/>
       <c r="G387" s="22"/>
       <c r="H387" s="23"/>
-      <c r="I387" s="4"/>
+      <c r="I387" s="8"/>
     </row>
     <row r="388" ht="15.75" customHeight="1">
       <c r="A388" s="24"/>
       <c r="G388" s="22"/>
       <c r="H388" s="23"/>
-      <c r="I388" s="4"/>
+      <c r="I388" s="8"/>
     </row>
     <row r="389" ht="15.75" customHeight="1">
       <c r="A389" s="24"/>
       <c r="G389" s="22"/>
       <c r="H389" s="23"/>
-      <c r="I389" s="4"/>
+      <c r="I389" s="8"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
       <c r="A390" s="24"/>
       <c r="G390" s="22"/>
       <c r="H390" s="23"/>
-      <c r="I390" s="4"/>
+      <c r="I390" s="8"/>
     </row>
     <row r="391" ht="15.75" customHeight="1">
       <c r="A391" s="24"/>
       <c r="G391" s="22"/>
       <c r="H391" s="23"/>
-      <c r="I391" s="4"/>
+      <c r="I391" s="8"/>
     </row>
     <row r="392" ht="15.75" customHeight="1">
       <c r="A392" s="24"/>
       <c r="G392" s="22"/>
       <c r="H392" s="23"/>
-      <c r="I392" s="4"/>
+      <c r="I392" s="8"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
       <c r="A393" s="24"/>
       <c r="G393" s="22"/>
       <c r="H393" s="23"/>
-      <c r="I393" s="4"/>
+      <c r="I393" s="8"/>
     </row>
     <row r="394" ht="15.75" customHeight="1">
       <c r="A394" s="24"/>
       <c r="G394" s="22"/>
       <c r="H394" s="23"/>
-      <c r="I394" s="4"/>
+      <c r="I394" s="8"/>
     </row>
     <row r="395" ht="15.75" customHeight="1">
       <c r="A395" s="24"/>
       <c r="G395" s="22"/>
       <c r="H395" s="23"/>
-      <c r="I395" s="4"/>
+      <c r="I395" s="8"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
       <c r="A396" s="24"/>
       <c r="G396" s="22"/>
       <c r="H396" s="23"/>
-      <c r="I396" s="4"/>
+      <c r="I396" s="8"/>
     </row>
     <row r="397" ht="15.75" customHeight="1">
       <c r="A397" s="24"/>
       <c r="G397" s="22"/>
       <c r="H397" s="23"/>
-      <c r="I397" s="4"/>
+      <c r="I397" s="8"/>
     </row>
     <row r="398" ht="15.75" customHeight="1">
       <c r="A398" s="24"/>
       <c r="G398" s="22"/>
       <c r="H398" s="23"/>
-      <c r="I398" s="4"/>
+      <c r="I398" s="8"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
       <c r="A399" s="24"/>
       <c r="G399" s="22"/>
       <c r="H399" s="23"/>
-      <c r="I399" s="4"/>
+      <c r="I399" s="8"/>
     </row>
     <row r="400" ht="15.75" customHeight="1">
       <c r="A400" s="24"/>
       <c r="G400" s="22"/>
       <c r="H400" s="23"/>
-      <c r="I400" s="4"/>
+      <c r="I400" s="8"/>
     </row>
     <row r="401" ht="15.75" customHeight="1">
       <c r="A401" s="24"/>
       <c r="G401" s="22"/>
       <c r="H401" s="23"/>
-      <c r="I401" s="4"/>
+      <c r="I401" s="8"/>
     </row>
     <row r="402" ht="15.75" customHeight="1">
       <c r="A402" s="24"/>
       <c r="G402" s="22"/>
       <c r="H402" s="23"/>
-      <c r="I402" s="4"/>
+      <c r="I402" s="8"/>
     </row>
     <row r="403" ht="15.75" customHeight="1">
       <c r="A403" s="24"/>
       <c r="G403" s="22"/>
       <c r="H403" s="23"/>
-      <c r="I403" s="4"/>
+      <c r="I403" s="8"/>
     </row>
     <row r="404" ht="15.75" customHeight="1">
       <c r="A404" s="24"/>
       <c r="G404" s="22"/>
       <c r="H404" s="23"/>
-      <c r="I404" s="4"/>
+      <c r="I404" s="8"/>
     </row>
     <row r="405" ht="15.75" customHeight="1">
       <c r="A405" s="24"/>
       <c r="G405" s="22"/>
       <c r="H405" s="23"/>
-      <c r="I405" s="4"/>
+      <c r="I405" s="8"/>
     </row>
     <row r="406" ht="15.75" customHeight="1">
       <c r="A406" s="24"/>
       <c r="G406" s="22"/>
       <c r="H406" s="23"/>
-      <c r="I406" s="4"/>
+      <c r="I406" s="8"/>
     </row>
     <row r="407" ht="15.75" customHeight="1">
       <c r="A407" s="24"/>
       <c r="G407" s="22"/>
       <c r="H407" s="23"/>
-      <c r="I407" s="4"/>
+      <c r="I407" s="8"/>
     </row>
     <row r="408" ht="15.75" customHeight="1">
       <c r="A408" s="24"/>
       <c r="G408" s="22"/>
       <c r="H408" s="23"/>
-      <c r="I408" s="4"/>
+      <c r="I408" s="8"/>
     </row>
     <row r="409" ht="15.75" customHeight="1">
       <c r="A409" s="24"/>
       <c r="G409" s="22"/>
       <c r="H409" s="23"/>
-      <c r="I409" s="4"/>
+      <c r="I409" s="8"/>
     </row>
     <row r="410" ht="15.75" customHeight="1">
       <c r="A410" s="24"/>
       <c r="G410" s="22"/>
       <c r="H410" s="23"/>
-      <c r="I410" s="4"/>
+      <c r="I410" s="8"/>
     </row>
     <row r="411" ht="15.75" customHeight="1">
       <c r="A411" s="24"/>
       <c r="G411" s="22"/>
       <c r="H411" s="23"/>
-      <c r="I411" s="4"/>
+      <c r="I411" s="8"/>
     </row>
     <row r="412" ht="15.75" customHeight="1">
       <c r="A412" s="24"/>
       <c r="G412" s="22"/>
       <c r="H412" s="23"/>
-      <c r="I412" s="4"/>
+      <c r="I412" s="8"/>
     </row>
     <row r="413" ht="15.75" customHeight="1">
       <c r="A413" s="24"/>
       <c r="G413" s="22"/>
       <c r="H413" s="23"/>
-      <c r="I413" s="4"/>
+      <c r="I413" s="8"/>
     </row>
     <row r="414" ht="15.75" customHeight="1">
       <c r="A414" s="24"/>
       <c r="G414" s="22"/>
       <c r="H414" s="23"/>
-      <c r="I414" s="4"/>
+      <c r="I414" s="8"/>
     </row>
     <row r="415" ht="15.75" customHeight="1">
       <c r="A415" s="24"/>
       <c r="G415" s="22"/>
       <c r="H415" s="23"/>
-      <c r="I415" s="4"/>
+      <c r="I415" s="8"/>
     </row>
     <row r="416" ht="15.75" customHeight="1">
       <c r="A416" s="24"/>
       <c r="G416" s="22"/>
       <c r="H416" s="23"/>
-      <c r="I416" s="4"/>
+      <c r="I416" s="8"/>
     </row>
     <row r="417" ht="15.75" customHeight="1">
       <c r="A417" s="24"/>
       <c r="G417" s="22"/>
       <c r="H417" s="23"/>
-      <c r="I417" s="4"/>
+      <c r="I417" s="8"/>
     </row>
     <row r="418" ht="15.75" customHeight="1">
       <c r="A418" s="24"/>
       <c r="G418" s="22"/>
       <c r="H418" s="23"/>
-      <c r="I418" s="4"/>
+      <c r="I418" s="8"/>
     </row>
     <row r="419" ht="15.75" customHeight="1">
       <c r="A419" s="24"/>
       <c r="G419" s="22"/>
       <c r="H419" s="23"/>
-      <c r="I419" s="4"/>
+      <c r="I419" s="8"/>
     </row>
     <row r="420" ht="15.75" customHeight="1">
       <c r="A420" s="24"/>
       <c r="G420" s="22"/>
       <c r="H420" s="23"/>
-      <c r="I420" s="4"/>
+      <c r="I420" s="8"/>
     </row>
     <row r="421" ht="15.75" customHeight="1">
       <c r="A421" s="24"/>
       <c r="G421" s="22"/>
       <c r="H421" s="23"/>
-      <c r="I421" s="4"/>
+      <c r="I421" s="8"/>
     </row>
     <row r="422" ht="15.75" customHeight="1">
       <c r="A422" s="24"/>
       <c r="G422" s="22"/>
       <c r="H422" s="23"/>
-      <c r="I422" s="4"/>
+      <c r="I422" s="8"/>
     </row>
     <row r="423" ht="15.75" customHeight="1">
       <c r="A423" s="24"/>
       <c r="G423" s="22"/>
       <c r="H423" s="23"/>
-      <c r="I423" s="4"/>
+      <c r="I423" s="8"/>
     </row>
     <row r="424" ht="15.75" customHeight="1">
       <c r="A424" s="24"/>
       <c r="G424" s="22"/>
       <c r="H424" s="23"/>
-      <c r="I424" s="4"/>
+      <c r="I424" s="8"/>
     </row>
     <row r="425" ht="15.75" customHeight="1">
       <c r="A425" s="24"/>
       <c r="G425" s="22"/>
       <c r="H425" s="23"/>
-      <c r="I425" s="4"/>
+      <c r="I425" s="8"/>
     </row>
     <row r="426" ht="15.75" customHeight="1">
       <c r="A426" s="24"/>
       <c r="G426" s="22"/>
       <c r="H426" s="23"/>
-      <c r="I426" s="4"/>
+      <c r="I426" s="8"/>
     </row>
     <row r="427" ht="15.75" customHeight="1">
       <c r="A427" s="24"/>
       <c r="G427" s="22"/>
       <c r="H427" s="23"/>
-      <c r="I427" s="4"/>
+      <c r="I427" s="8"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
       <c r="A428" s="24"/>
       <c r="G428" s="22"/>
       <c r="H428" s="23"/>
-      <c r="I428" s="4"/>
+      <c r="I428" s="8"/>
     </row>
     <row r="429" ht="15.75" customHeight="1">
       <c r="A429" s="24"/>
       <c r="G429" s="22"/>
       <c r="H429" s="23"/>
-      <c r="I429" s="4"/>
+      <c r="I429" s="8"/>
     </row>
     <row r="430" ht="15.75" customHeight="1">
       <c r="A430" s="24"/>
       <c r="G430" s="22"/>
       <c r="H430" s="23"/>
-      <c r="I430" s="4"/>
+      <c r="I430" s="8"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
       <c r="A431" s="24"/>
       <c r="G431" s="22"/>
       <c r="H431" s="23"/>
-      <c r="I431" s="4"/>
+      <c r="I431" s="8"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
       <c r="A432" s="24"/>
       <c r="G432" s="22"/>
       <c r="H432" s="23"/>
-      <c r="I432" s="4"/>
+      <c r="I432" s="8"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
       <c r="A433" s="24"/>
       <c r="G433" s="22"/>
       <c r="H433" s="23"/>
-      <c r="I433" s="4"/>
+      <c r="I433" s="8"/>
     </row>
     <row r="434" ht="15.75" customHeight="1">
       <c r="A434" s="24"/>
       <c r="G434" s="22"/>
       <c r="H434" s="23"/>
-      <c r="I434" s="4"/>
+      <c r="I434" s="8"/>
     </row>
     <row r="435" ht="15.75" customHeight="1">
       <c r="A435" s="24"/>
       <c r="G435" s="22"/>
       <c r="H435" s="23"/>
-      <c r="I435" s="4"/>
+      <c r="I435" s="8"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
       <c r="A436" s="24"/>
       <c r="G436" s="22"/>
       <c r="H436" s="23"/>
-      <c r="I436" s="4"/>
+      <c r="I436" s="8"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
       <c r="A437" s="24"/>
       <c r="G437" s="22"/>
       <c r="H437" s="23"/>
-      <c r="I437" s="4"/>
+      <c r="I437" s="8"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
       <c r="A438" s="24"/>
       <c r="G438" s="22"/>
       <c r="H438" s="23"/>
-      <c r="I438" s="4"/>
+      <c r="I438" s="8"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
       <c r="A439" s="24"/>
       <c r="G439" s="22"/>
       <c r="H439" s="23"/>
-      <c r="I439" s="4"/>
+      <c r="I439" s="8"/>
     </row>
     <row r="440" ht="15.75" customHeight="1">
       <c r="A440" s="24"/>
       <c r="G440" s="22"/>
       <c r="H440" s="23"/>
-      <c r="I440" s="4"/>
+      <c r="I440" s="8"/>
     </row>
     <row r="441" ht="15.75" customHeight="1">
       <c r="A441" s="24"/>
       <c r="G441" s="22"/>
       <c r="H441" s="23"/>
-      <c r="I441" s="4"/>
+      <c r="I441" s="8"/>
     </row>
     <row r="442" ht="15.75" customHeight="1">
       <c r="A442" s="24"/>
       <c r="G442" s="22"/>
       <c r="H442" s="23"/>
-      <c r="I442" s="4"/>
+      <c r="I442" s="8"/>
     </row>
     <row r="443" ht="15.75" customHeight="1">
       <c r="A443" s="24"/>
       <c r="G443" s="22"/>
       <c r="H443" s="23"/>
-      <c r="I443" s="4"/>
+      <c r="I443" s="8"/>
     </row>
     <row r="444" ht="15.75" customHeight="1">
       <c r="A444" s="24"/>
       <c r="G444" s="22"/>
       <c r="H444" s="23"/>
-      <c r="I444" s="4"/>
+      <c r="I444" s="8"/>
     </row>
     <row r="445" ht="15.75" customHeight="1">
       <c r="A445" s="24"/>
       <c r="G445" s="22"/>
       <c r="H445" s="23"/>
-      <c r="I445" s="4"/>
+      <c r="I445" s="8"/>
     </row>
     <row r="446" ht="15.75" customHeight="1">
       <c r="A446" s="24"/>
       <c r="G446" s="22"/>
       <c r="H446" s="23"/>
-      <c r="I446" s="4"/>
+      <c r="I446" s="8"/>
     </row>
     <row r="447" ht="15.75" customHeight="1">
       <c r="A447" s="24"/>
       <c r="G447" s="22"/>
       <c r="H447" s="23"/>
-      <c r="I447" s="4"/>
+      <c r="I447" s="8"/>
     </row>
     <row r="448" ht="15.75" customHeight="1">
       <c r="A448" s="24"/>
       <c r="G448" s="22"/>
       <c r="H448" s="23"/>
-      <c r="I448" s="4"/>
+      <c r="I448" s="8"/>
     </row>
     <row r="449" ht="15.75" customHeight="1">
       <c r="A449" s="24"/>
       <c r="G449" s="22"/>
       <c r="H449" s="23"/>
-      <c r="I449" s="4"/>
+      <c r="I449" s="8"/>
     </row>
     <row r="450" ht="15.75" customHeight="1">
       <c r="A450" s="24"/>
       <c r="G450" s="22"/>
       <c r="H450" s="23"/>
-      <c r="I450" s="4"/>
+      <c r="I450" s="8"/>
     </row>
     <row r="451" ht="15.75" customHeight="1">
       <c r="A451" s="24"/>
       <c r="G451" s="22"/>
       <c r="H451" s="23"/>
-      <c r="I451" s="4"/>
+      <c r="I451" s="8"/>
     </row>
     <row r="452" ht="15.75" customHeight="1">
       <c r="A452" s="24"/>
       <c r="G452" s="22"/>
       <c r="H452" s="23"/>
-      <c r="I452" s="4"/>
+      <c r="I452" s="8"/>
     </row>
     <row r="453" ht="15.75" customHeight="1">
       <c r="A453" s="24"/>
       <c r="G453" s="22"/>
       <c r="H453" s="23"/>
-      <c r="I453" s="4"/>
+      <c r="I453" s="8"/>
     </row>
     <row r="454" ht="15.75" customHeight="1">
       <c r="A454" s="24"/>
       <c r="G454" s="22"/>
       <c r="H454" s="23"/>
-      <c r="I454" s="4"/>
+      <c r="I454" s="8"/>
     </row>
     <row r="455" ht="15.75" customHeight="1">
       <c r="A455" s="24"/>
       <c r="G455" s="22"/>
       <c r="H455" s="23"/>
-      <c r="I455" s="4"/>
+      <c r="I455" s="8"/>
     </row>
     <row r="456" ht="15.75" customHeight="1">
       <c r="A456" s="24"/>
       <c r="G456" s="22"/>
       <c r="H456" s="23"/>
-      <c r="I456" s="4"/>
+      <c r="I456" s="8"/>
     </row>
     <row r="457" ht="15.75" customHeight="1">
       <c r="A457" s="24"/>
       <c r="G457" s="22"/>
       <c r="H457" s="23"/>
-      <c r="I457" s="4"/>
+      <c r="I457" s="8"/>
     </row>
     <row r="458" ht="15.75" customHeight="1">
       <c r="A458" s="24"/>
       <c r="G458" s="22"/>
       <c r="H458" s="23"/>
-      <c r="I458" s="4"/>
+      <c r="I458" s="8"/>
     </row>
     <row r="459" ht="15.75" customHeight="1">
       <c r="A459" s="24"/>
       <c r="G459" s="22"/>
       <c r="H459" s="23"/>
-      <c r="I459" s="4"/>
+      <c r="I459" s="8"/>
     </row>
     <row r="460" ht="15.75" customHeight="1">
       <c r="A460" s="24"/>
       <c r="G460" s="22"/>
       <c r="H460" s="23"/>
-      <c r="I460" s="4"/>
+      <c r="I460" s="8"/>
     </row>
     <row r="461" ht="15.75" customHeight="1">
       <c r="A461" s="24"/>
       <c r="G461" s="22"/>
       <c r="H461" s="23"/>
-      <c r="I461" s="4"/>
+      <c r="I461" s="8"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
       <c r="A462" s="24"/>
       <c r="G462" s="22"/>
       <c r="H462" s="23"/>
-      <c r="I462" s="4"/>
+      <c r="I462" s="8"/>
     </row>
     <row r="463" ht="15.75" customHeight="1">
       <c r="A463" s="24"/>
       <c r="G463" s="22"/>
       <c r="H463" s="23"/>
-      <c r="I463" s="4"/>
+      <c r="I463" s="8"/>
     </row>
     <row r="464" ht="15.75" customHeight="1">
       <c r="A464" s="24"/>
       <c r="G464" s="22"/>
       <c r="H464" s="23"/>
-      <c r="I464" s="4"/>
+      <c r="I464" s="8"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
       <c r="A465" s="24"/>
       <c r="G465" s="22"/>
       <c r="H465" s="23"/>
-      <c r="I465" s="4"/>
+      <c r="I465" s="8"/>
     </row>
     <row r="466" ht="15.75" customHeight="1">
       <c r="A466" s="24"/>
       <c r="G466" s="22"/>
       <c r="H466" s="23"/>
-      <c r="I466" s="4"/>
+      <c r="I466" s="8"/>
     </row>
     <row r="467" ht="15.75" customHeight="1">
       <c r="A467" s="24"/>
       <c r="G467" s="22"/>
       <c r="H467" s="23"/>
-      <c r="I467" s="4"/>
+      <c r="I467" s="8"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
       <c r="A468" s="24"/>
       <c r="G468" s="22"/>
       <c r="H468" s="23"/>
-      <c r="I468" s="4"/>
+      <c r="I468" s="8"/>
     </row>
     <row r="469" ht="15.75" customHeight="1">
       <c r="A469" s="24"/>
       <c r="G469" s="22"/>
       <c r="H469" s="23"/>
-      <c r="I469" s="4"/>
+      <c r="I469" s="8"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
       <c r="A470" s="24"/>
       <c r="G470" s="22"/>
       <c r="H470" s="23"/>
-      <c r="I470" s="4"/>
+      <c r="I470" s="8"/>
     </row>
     <row r="471" ht="15.75" customHeight="1">
       <c r="A471" s="24"/>
       <c r="G471" s="22"/>
       <c r="H471" s="23"/>
-      <c r="I471" s="4"/>
+      <c r="I471" s="8"/>
     </row>
     <row r="472" ht="15.75" customHeight="1">
       <c r="A472" s="24"/>
       <c r="G472" s="22"/>
       <c r="H472" s="23"/>
-      <c r="I472" s="4"/>
+      <c r="I472" s="8"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
       <c r="A473" s="24"/>
       <c r="G473" s="22"/>
       <c r="H473" s="23"/>
-      <c r="I473" s="4"/>
+      <c r="I473" s="8"/>
     </row>
     <row r="474" ht="15.75" customHeight="1">
       <c r="A474" s="24"/>
       <c r="G474" s="22"/>
       <c r="H474" s="23"/>
-      <c r="I474" s="4"/>
+      <c r="I474" s="8"/>
     </row>
     <row r="475" ht="15.75" customHeight="1">
       <c r="A475" s="24"/>
       <c r="G475" s="22"/>
       <c r="H475" s="23"/>
-      <c r="I475" s="4"/>
+      <c r="I475" s="8"/>
     </row>
     <row r="476" ht="15.75" customHeight="1">
       <c r="A476" s="24"/>
       <c r="G476" s="22"/>
       <c r="H476" s="23"/>
-      <c r="I476" s="4"/>
+      <c r="I476" s="8"/>
     </row>
     <row r="477" ht="15.75" customHeight="1">
       <c r="A477" s="24"/>
       <c r="G477" s="22"/>
       <c r="H477" s="23"/>
-      <c r="I477" s="4"/>
+      <c r="I477" s="8"/>
     </row>
     <row r="478" ht="15.75" customHeight="1">
       <c r="A478" s="24"/>
       <c r="G478" s="22"/>
       <c r="H478" s="23"/>
-      <c r="I478" s="4"/>
+      <c r="I478" s="8"/>
     </row>
     <row r="479" ht="15.75" customHeight="1">
       <c r="A479" s="24"/>
       <c r="G479" s="22"/>
       <c r="H479" s="23"/>
-      <c r="I479" s="4"/>
+      <c r="I479" s="8"/>
     </row>
     <row r="480" ht="15.75" customHeight="1">
       <c r="A480" s="24"/>
       <c r="G480" s="22"/>
       <c r="H480" s="23"/>
-      <c r="I480" s="4"/>
+      <c r="I480" s="8"/>
     </row>
     <row r="481" ht="15.75" customHeight="1">
       <c r="A481" s="24"/>
       <c r="G481" s="22"/>
       <c r="H481" s="23"/>
-      <c r="I481" s="4"/>
+      <c r="I481" s="8"/>
     </row>
     <row r="482" ht="15.75" customHeight="1">
       <c r="A482" s="24"/>
       <c r="G482" s="22"/>
       <c r="H482" s="23"/>
-      <c r="I482" s="4"/>
+      <c r="I482" s="8"/>
     </row>
     <row r="483" ht="15.75" customHeight="1">
       <c r="A483" s="24"/>
       <c r="G483" s="22"/>
       <c r="H483" s="23"/>
-      <c r="I483" s="4"/>
+      <c r="I483" s="8"/>
     </row>
     <row r="484" ht="15.75" customHeight="1">
       <c r="A484" s="24"/>
       <c r="G484" s="22"/>
       <c r="H484" s="23"/>
-      <c r="I484" s="4"/>
+      <c r="I484" s="8"/>
     </row>
     <row r="485" ht="15.75" customHeight="1">
       <c r="A485" s="24"/>
       <c r="G485" s="22"/>
       <c r="H485" s="23"/>
-      <c r="I485" s="4"/>
+      <c r="I485" s="8"/>
     </row>
     <row r="486" ht="15.75" customHeight="1">
       <c r="A486" s="24"/>
       <c r="G486" s="22"/>
       <c r="H486" s="23"/>
-      <c r="I486" s="4"/>
+      <c r="I486" s="8"/>
     </row>
     <row r="487" ht="15.75" customHeight="1">
       <c r="A487" s="24"/>
       <c r="G487" s="22"/>
       <c r="H487" s="23"/>
-      <c r="I487" s="4"/>
+      <c r="I487" s="8"/>
     </row>
     <row r="488" ht="15.75" customHeight="1">
       <c r="A488" s="24"/>
       <c r="G488" s="22"/>
       <c r="H488" s="23"/>
-      <c r="I488" s="4"/>
+      <c r="I488" s="8"/>
     </row>
     <row r="489" ht="15.75" customHeight="1">
       <c r="A489" s="24"/>
       <c r="G489" s="22"/>
       <c r="H489" s="23"/>
-      <c r="I489" s="4"/>
+      <c r="I489" s="8"/>
     </row>
     <row r="490" ht="15.75" customHeight="1">
       <c r="A490" s="24"/>
       <c r="G490" s="22"/>
       <c r="H490" s="23"/>
-      <c r="I490" s="4"/>
+      <c r="I490" s="8"/>
     </row>
     <row r="491" ht="15.75" customHeight="1">
       <c r="A491" s="24"/>
       <c r="G491" s="22"/>
       <c r="H491" s="23"/>
-      <c r="I491" s="4"/>
+      <c r="I491" s="8"/>
     </row>
     <row r="492" ht="15.75" customHeight="1">
       <c r="A492" s="24"/>
       <c r="G492" s="22"/>
       <c r="H492" s="23"/>
-      <c r="I492" s="4"/>
+      <c r="I492" s="8"/>
     </row>
     <row r="493" ht="15.75" customHeight="1">
       <c r="A493" s="24"/>
       <c r="G493" s="22"/>
       <c r="H493" s="23"/>
-      <c r="I493" s="4"/>
+      <c r="I493" s="8"/>
     </row>
     <row r="494" ht="15.75" customHeight="1">
       <c r="A494" s="24"/>
       <c r="G494" s="22"/>
       <c r="H494" s="23"/>
-      <c r="I494" s="4"/>
+      <c r="I494" s="8"/>
     </row>
     <row r="495" ht="15.75" customHeight="1">
       <c r="A495" s="24"/>
       <c r="G495" s="22"/>
       <c r="H495" s="23"/>
-      <c r="I495" s="4"/>
+      <c r="I495" s="8"/>
     </row>
     <row r="496" ht="15.75" customHeight="1">
       <c r="A496" s="24"/>
       <c r="G496" s="22"/>
       <c r="H496" s="23"/>
-      <c r="I496" s="4"/>
+      <c r="I496" s="8"/>
     </row>
     <row r="497" ht="15.75" customHeight="1">
       <c r="A497" s="24"/>
       <c r="G497" s="22"/>
       <c r="H497" s="23"/>
-      <c r="I497" s="4"/>
+      <c r="I497" s="8"/>
     </row>
     <row r="498" ht="15.75" customHeight="1">
       <c r="A498" s="24"/>
       <c r="G498" s="22"/>
       <c r="H498" s="23"/>
-      <c r="I498" s="4"/>
+      <c r="I498" s="8"/>
     </row>
     <row r="499" ht="15.75" customHeight="1">
       <c r="A499" s="24"/>
       <c r="G499" s="22"/>
       <c r="H499" s="23"/>
-      <c r="I499" s="4"/>
+      <c r="I499" s="8"/>
     </row>
     <row r="500" ht="15.75" customHeight="1">
       <c r="A500" s="24"/>
       <c r="G500" s="22"/>
       <c r="H500" s="23"/>
-      <c r="I500" s="4"/>
+      <c r="I500" s="8"/>
     </row>
     <row r="501" ht="15.75" customHeight="1">
       <c r="A501" s="24"/>
       <c r="G501" s="22"/>
       <c r="H501" s="23"/>
-      <c r="I501" s="4"/>
+      <c r="I501" s="8"/>
     </row>
     <row r="502" ht="15.75" customHeight="1">
       <c r="A502" s="24"/>
       <c r="G502" s="22"/>
       <c r="H502" s="23"/>
-      <c r="I502" s="4"/>
+      <c r="I502" s="8"/>
     </row>
     <row r="503" ht="15.75" customHeight="1">
       <c r="A503" s="24"/>
       <c r="G503" s="22"/>
       <c r="H503" s="23"/>
-      <c r="I503" s="4"/>
+      <c r="I503" s="8"/>
     </row>
     <row r="504" ht="15.75" customHeight="1">
       <c r="A504" s="24"/>
       <c r="G504" s="22"/>
       <c r="H504" s="23"/>
-      <c r="I504" s="4"/>
+      <c r="I504" s="8"/>
     </row>
     <row r="505" ht="15.75" customHeight="1">
       <c r="A505" s="24"/>
       <c r="G505" s="22"/>
       <c r="H505" s="23"/>
-      <c r="I505" s="4"/>
+      <c r="I505" s="8"/>
     </row>
     <row r="506" ht="15.75" customHeight="1">
       <c r="A506" s="24"/>
       <c r="G506" s="22"/>
       <c r="H506" s="23"/>
-      <c r="I506" s="4"/>
+      <c r="I506" s="8"/>
     </row>
     <row r="507" ht="15.75" customHeight="1">
       <c r="A507" s="24"/>
       <c r="G507" s="22"/>
       <c r="H507" s="23"/>
-      <c r="I507" s="4"/>
+      <c r="I507" s="8"/>
     </row>
     <row r="508" ht="15.75" customHeight="1">
       <c r="A508" s="24"/>
       <c r="G508" s="22"/>
       <c r="H508" s="23"/>
-      <c r="I508" s="4"/>
+      <c r="I508" s="8"/>
     </row>
     <row r="509" ht="15.75" customHeight="1">
       <c r="A509" s="24"/>
       <c r="G509" s="22"/>
       <c r="H509" s="23"/>
-      <c r="I509" s="4"/>
+      <c r="I509" s="8"/>
     </row>
     <row r="510" ht="15.75" customHeight="1">
       <c r="A510" s="24"/>
       <c r="G510" s="22"/>
       <c r="H510" s="23"/>
-      <c r="I510" s="4"/>
+      <c r="I510" s="8"/>
     </row>
     <row r="511" ht="15.75" customHeight="1">
       <c r="A511" s="24"/>
       <c r="G511" s="22"/>
       <c r="H511" s="23"/>
-      <c r="I511" s="4"/>
+      <c r="I511" s="8"/>
     </row>
     <row r="512" ht="15.75" customHeight="1">
       <c r="A512" s="24"/>
       <c r="G512" s="22"/>
       <c r="H512" s="23"/>
-      <c r="I512" s="4"/>
+      <c r="I512" s="8"/>
     </row>
     <row r="513" ht="15.75" customHeight="1">
       <c r="A513" s="24"/>
       <c r="G513" s="22"/>
       <c r="H513" s="23"/>
-      <c r="I513" s="4"/>
+      <c r="I513" s="8"/>
     </row>
     <row r="514" ht="15.75" customHeight="1">
       <c r="A514" s="24"/>
       <c r="G514" s="22"/>
       <c r="H514" s="23"/>
-      <c r="I514" s="4"/>
+      <c r="I514" s="8"/>
     </row>
     <row r="515" ht="15.75" customHeight="1">
       <c r="A515" s="24"/>
       <c r="G515" s="22"/>
       <c r="H515" s="23"/>
-      <c r="I515" s="4"/>
+      <c r="I515" s="8"/>
     </row>
     <row r="516" ht="15.75" customHeight="1">
       <c r="A516" s="24"/>
       <c r="G516" s="22"/>
       <c r="H516" s="23"/>
-      <c r="I516" s="4"/>
+      <c r="I516" s="8"/>
     </row>
     <row r="517" ht="15.75" customHeight="1">
       <c r="A517" s="24"/>
       <c r="G517" s="22"/>
       <c r="H517" s="23"/>
-      <c r="I517" s="4"/>
+      <c r="I517" s="8"/>
     </row>
     <row r="518" ht="15.75" customHeight="1">
       <c r="A518" s="24"/>
       <c r="G518" s="22"/>
       <c r="H518" s="23"/>
-      <c r="I518" s="4"/>
+      <c r="I518" s="8"/>
     </row>
     <row r="519" ht="15.75" customHeight="1">
       <c r="A519" s="24"/>
       <c r="G519" s="22"/>
       <c r="H519" s="23"/>
-      <c r="I519" s="4"/>
+      <c r="I519" s="8"/>
     </row>
     <row r="520" ht="15.75" customHeight="1">
       <c r="A520" s="24"/>
       <c r="G520" s="22"/>
       <c r="H520" s="23"/>
-      <c r="I520" s="4"/>
+      <c r="I520" s="8"/>
     </row>
     <row r="521" ht="15.75" customHeight="1">
       <c r="A521" s="24"/>
       <c r="G521" s="22"/>
       <c r="H521" s="23"/>
-      <c r="I521" s="4"/>
+      <c r="I521" s="8"/>
     </row>
     <row r="522" ht="15.75" customHeight="1">
       <c r="A522" s="24"/>
       <c r="G522" s="22"/>
       <c r="H522" s="23"/>
-      <c r="I522" s="4"/>
+      <c r="I522" s="8"/>
     </row>
     <row r="523" ht="15.75" customHeight="1">
       <c r="A523" s="24"/>
       <c r="G523" s="22"/>
       <c r="H523" s="23"/>
-      <c r="I523" s="4"/>
+      <c r="I523" s="8"/>
     </row>
     <row r="524" ht="15.75" customHeight="1">
       <c r="A524" s="24"/>
       <c r="G524" s="22"/>
       <c r="H524" s="23"/>
-      <c r="I524" s="4"/>
+      <c r="I524" s="8"/>
     </row>
     <row r="525" ht="15.75" customHeight="1">
       <c r="A525" s="24"/>
       <c r="G525" s="22"/>
       <c r="H525" s="23"/>
-      <c r="I525" s="4"/>
+      <c r="I525" s="8"/>
     </row>
     <row r="526" ht="15.75" customHeight="1">
       <c r="A526" s="24"/>
       <c r="G526" s="22"/>
       <c r="H526" s="23"/>
-      <c r="I526" s="4"/>
+      <c r="I526" s="8"/>
     </row>
     <row r="527" ht="15.75" customHeight="1">
       <c r="A527" s="24"/>
       <c r="G527" s="22"/>
       <c r="H527" s="23"/>
-      <c r="I527" s="4"/>
+      <c r="I527" s="8"/>
     </row>
     <row r="528" ht="15.75" customHeight="1">
       <c r="A528" s="24"/>
       <c r="G528" s="22"/>
       <c r="H528" s="23"/>
-      <c r="I528" s="4"/>
+      <c r="I528" s="8"/>
     </row>
     <row r="529" ht="15.75" customHeight="1">
       <c r="A529" s="24"/>
       <c r="G529" s="22"/>
       <c r="H529" s="23"/>
-      <c r="I529" s="4"/>
+      <c r="I529" s="8"/>
     </row>
     <row r="530" ht="15.75" customHeight="1">
       <c r="A530" s="24"/>
       <c r="G530" s="22"/>
       <c r="H530" s="23"/>
-      <c r="I530" s="4"/>
+      <c r="I530" s="8"/>
     </row>
     <row r="531" ht="15.75" customHeight="1">
       <c r="A531" s="24"/>
       <c r="G531" s="22"/>
       <c r="H531" s="23"/>
-      <c r="I531" s="4"/>
+      <c r="I531" s="8"/>
     </row>
     <row r="532" ht="15.75" customHeight="1">
       <c r="A532" s="24"/>
       <c r="G532" s="22"/>
       <c r="H532" s="23"/>
-      <c r="I532" s="4"/>
+      <c r="I532" s="8"/>
     </row>
     <row r="533" ht="15.75" customHeight="1">
       <c r="A533" s="24"/>
       <c r="G533" s="22"/>
       <c r="H533" s="23"/>
-      <c r="I533" s="4"/>
+      <c r="I533" s="8"/>
     </row>
     <row r="534" ht="15.75" customHeight="1">
       <c r="A534" s="24"/>
       <c r="G534" s="22"/>
       <c r="H534" s="23"/>
-      <c r="I534" s="4"/>
+      <c r="I534" s="8"/>
     </row>
     <row r="535" ht="15.75" customHeight="1">
       <c r="A535" s="24"/>
       <c r="G535" s="22"/>
       <c r="H535" s="23"/>
-      <c r="I535" s="4"/>
+      <c r="I535" s="8"/>
     </row>
     <row r="536" ht="15.75" customHeight="1">
       <c r="A536" s="24"/>
       <c r="G536" s="22"/>
       <c r="H536" s="23"/>
-      <c r="I536" s="4"/>
+      <c r="I536" s="8"/>
     </row>
     <row r="537" ht="15.75" customHeight="1">
       <c r="A537" s="24"/>
       <c r="G537" s="22"/>
       <c r="H537" s="23"/>
-      <c r="I537" s="4"/>
+      <c r="I537" s="8"/>
     </row>
     <row r="538" ht="15.75" customHeight="1">
       <c r="A538" s="24"/>
       <c r="G538" s="22"/>
       <c r="H538" s="23"/>
-      <c r="I538" s="4"/>
+      <c r="I538" s="8"/>
     </row>
     <row r="539" ht="15.75" customHeight="1">
       <c r="A539" s="24"/>
       <c r="G539" s="22"/>
       <c r="H539" s="23"/>
-      <c r="I539" s="4"/>
+      <c r="I539" s="8"/>
     </row>
     <row r="540" ht="15.75" customHeight="1">
       <c r="A540" s="24"/>
       <c r="G540" s="22"/>
       <c r="H540" s="23"/>
-      <c r="I540" s="4"/>
+      <c r="I540" s="8"/>
     </row>
     <row r="541" ht="15.75" customHeight="1">
       <c r="A541" s="24"/>
       <c r="G541" s="22"/>
       <c r="H541" s="23"/>
-      <c r="I541" s="4"/>
+      <c r="I541" s="8"/>
     </row>
     <row r="542" ht="15.75" customHeight="1">
       <c r="A542" s="24"/>
       <c r="G542" s="22"/>
       <c r="H542" s="23"/>
-      <c r="I542" s="4"/>
+      <c r="I542" s="8"/>
     </row>
     <row r="543" ht="15.75" customHeight="1">
       <c r="A543" s="24"/>
       <c r="G543" s="22"/>
       <c r="H543" s="23"/>
-      <c r="I543" s="4"/>
+      <c r="I543" s="8"/>
     </row>
     <row r="544" ht="15.75" customHeight="1">
       <c r="A544" s="24"/>
       <c r="G544" s="22"/>
       <c r="H544" s="23"/>
-      <c r="I544" s="4"/>
+      <c r="I544" s="8"/>
     </row>
     <row r="545" ht="15.75" customHeight="1">
       <c r="A545" s="24"/>
       <c r="G545" s="22"/>
       <c r="H545" s="23"/>
-      <c r="I545" s="4"/>
+      <c r="I545" s="8"/>
     </row>
     <row r="546" ht="15.75" customHeight="1">
       <c r="A546" s="24"/>
       <c r="G546" s="22"/>
       <c r="H546" s="23"/>
-      <c r="I546" s="4"/>
+      <c r="I546" s="8"/>
     </row>
     <row r="547" ht="15.75" customHeight="1">
       <c r="A547" s="24"/>
       <c r="G547" s="22"/>
       <c r="H547" s="23"/>
-      <c r="I547" s="4"/>
+      <c r="I547" s="8"/>
     </row>
     <row r="548" ht="15.75" customHeight="1">
       <c r="A548" s="24"/>
       <c r="G548" s="22"/>
       <c r="H548" s="23"/>
-      <c r="I548" s="4"/>
+      <c r="I548" s="8"/>
     </row>
     <row r="549" ht="15.75" customHeight="1">
       <c r="A549" s="24"/>
       <c r="G549" s="22"/>
       <c r="H549" s="23"/>
-      <c r="I549" s="4"/>
+      <c r="I549" s="8"/>
     </row>
     <row r="550" ht="15.75" customHeight="1">
       <c r="A550" s="24"/>
       <c r="G550" s="22"/>
       <c r="H550" s="23"/>
-      <c r="I550" s="4"/>
+      <c r="I550" s="8"/>
     </row>
     <row r="551" ht="15.75" customHeight="1">
       <c r="A551" s="24"/>
       <c r="G551" s="22"/>
       <c r="H551" s="23"/>
-      <c r="I551" s="4"/>
+      <c r="I551" s="8"/>
     </row>
     <row r="552" ht="15.75" customHeight="1">
       <c r="A552" s="24"/>
       <c r="G552" s="22"/>
       <c r="H552" s="23"/>
-      <c r="I552" s="4"/>
+      <c r="I552" s="8"/>
     </row>
     <row r="553" ht="15.75" customHeight="1">
       <c r="A553" s="24"/>
       <c r="G553" s="22"/>
       <c r="H553" s="23"/>
-      <c r="I553" s="4"/>
+      <c r="I553" s="8"/>
     </row>
     <row r="554" ht="15.75" customHeight="1">
       <c r="A554" s="24"/>
       <c r="G554" s="22"/>
       <c r="H554" s="23"/>
-      <c r="I554" s="4"/>
+      <c r="I554" s="8"/>
     </row>
     <row r="555" ht="15.75" customHeight="1">
       <c r="A555" s="24"/>
       <c r="G555" s="22"/>
       <c r="H555" s="23"/>
-      <c r="I555" s="4"/>
+      <c r="I555" s="8"/>
     </row>
     <row r="556" ht="15.75" customHeight="1">
       <c r="A556" s="24"/>
       <c r="G556" s="22"/>
       <c r="H556" s="23"/>
-      <c r="I556" s="4"/>
+      <c r="I556" s="8"/>
     </row>
     <row r="557" ht="15.75" customHeight="1">
       <c r="A557" s="24"/>
       <c r="G557" s="22"/>
       <c r="H557" s="23"/>
-      <c r="I557" s="4"/>
+      <c r="I557" s="8"/>
     </row>
     <row r="558" ht="15.75" customHeight="1">
       <c r="A558" s="24"/>
       <c r="G558" s="22"/>
       <c r="H558" s="23"/>
-      <c r="I558" s="4"/>
+      <c r="I558" s="8"/>
     </row>
     <row r="559" ht="15.75" customHeight="1">
       <c r="A559" s="24"/>
       <c r="G559" s="22"/>
       <c r="H559" s="23"/>
-      <c r="I559" s="4"/>
+      <c r="I559" s="8"/>
     </row>
     <row r="560" ht="15.75" customHeight="1">
       <c r="A560" s="24"/>
       <c r="G560" s="22"/>
       <c r="H560" s="23"/>
-      <c r="I560" s="4"/>
+      <c r="I560" s="8"/>
     </row>
     <row r="561" ht="15.75" customHeight="1">
       <c r="A561" s="24"/>
       <c r="G561" s="22"/>
       <c r="H561" s="23"/>
-      <c r="I561" s="4"/>
+      <c r="I561" s="8"/>
     </row>
     <row r="562" ht="15.75" customHeight="1">
       <c r="A562" s="24"/>
       <c r="G562" s="22"/>
       <c r="H562" s="23"/>
-      <c r="I562" s="4"/>
+      <c r="I562" s="8"/>
     </row>
     <row r="563" ht="15.75" customHeight="1">
       <c r="A563" s="24"/>
       <c r="G563" s="22"/>
       <c r="H563" s="23"/>
-      <c r="I563" s="4"/>
+      <c r="I563" s="8"/>
     </row>
     <row r="564" ht="15.75" customHeight="1">
       <c r="A564" s="24"/>
       <c r="G564" s="22"/>
       <c r="H564" s="23"/>
-      <c r="I564" s="4"/>
+      <c r="I564" s="8"/>
     </row>
     <row r="565" ht="15.75" customHeight="1">
       <c r="A565" s="24"/>
       <c r="G565" s="22"/>
       <c r="H565" s="23"/>
-      <c r="I565" s="4"/>
+      <c r="I565" s="8"/>
     </row>
     <row r="566" ht="15.75" customHeight="1">
       <c r="A566" s="24"/>
       <c r="G566" s="22"/>
       <c r="H566" s="23"/>
-      <c r="I566" s="4"/>
+      <c r="I566" s="8"/>
     </row>
     <row r="567" ht="15.75" customHeight="1">
       <c r="A567" s="24"/>
       <c r="G567" s="22"/>
       <c r="H567" s="23"/>
-      <c r="I567" s="4"/>
+      <c r="I567" s="8"/>
     </row>
     <row r="568" ht="15.75" customHeight="1">
       <c r="A568" s="24"/>
       <c r="G568" s="22"/>
       <c r="H568" s="23"/>
-      <c r="I568" s="4"/>
+      <c r="I568" s="8"/>
     </row>
     <row r="569" ht="15.75" customHeight="1">
       <c r="A569" s="24"/>
       <c r="G569" s="22"/>
       <c r="H569" s="23"/>
-      <c r="I569" s="4"/>
+      <c r="I569" s="8"/>
     </row>
     <row r="570" ht="15.75" customHeight="1">
       <c r="A570" s="24"/>
       <c r="G570" s="22"/>
       <c r="H570" s="23"/>
-      <c r="I570" s="4"/>
+      <c r="I570" s="8"/>
     </row>
     <row r="571" ht="15.75" customHeight="1">
       <c r="A571" s="24"/>
       <c r="G571" s="22"/>
       <c r="H571" s="23"/>
-      <c r="I571" s="4"/>
+      <c r="I571" s="8"/>
     </row>
     <row r="572" ht="15.75" customHeight="1">
       <c r="A572" s="24"/>
       <c r="G572" s="22"/>
       <c r="H572" s="23"/>
-      <c r="I572" s="4"/>
+      <c r="I572" s="8"/>
     </row>
     <row r="573" ht="15.75" customHeight="1">
       <c r="A573" s="24"/>
       <c r="G573" s="22"/>
       <c r="H573" s="23"/>
-      <c r="I573" s="4"/>
+      <c r="I573" s="8"/>
     </row>
     <row r="574" ht="15.75" customHeight="1">
       <c r="A574" s="24"/>
       <c r="G574" s="22"/>
       <c r="H574" s="23"/>
-      <c r="I574" s="4"/>
+      <c r="I574" s="8"/>
     </row>
     <row r="575" ht="15.75" customHeight="1">
       <c r="A575" s="24"/>
       <c r="G575" s="22"/>
       <c r="H575" s="23"/>
-      <c r="I575" s="4"/>
+      <c r="I575" s="8"/>
     </row>
     <row r="576" ht="15.75" customHeight="1">
       <c r="A576" s="24"/>
       <c r="G576" s="22"/>
       <c r="H576" s="23"/>
-      <c r="I576" s="4"/>
+      <c r="I576" s="8"/>
     </row>
     <row r="577" ht="15.75" customHeight="1">
       <c r="A577" s="24"/>
       <c r="G577" s="22"/>
       <c r="H577" s="23"/>
-      <c r="I577" s="4"/>
+      <c r="I577" s="8"/>
     </row>
     <row r="578" ht="15.75" customHeight="1">
       <c r="A578" s="24"/>
       <c r="G578" s="22"/>
       <c r="H578" s="23"/>
-      <c r="I578" s="4"/>
+      <c r="I578" s="8"/>
     </row>
     <row r="579" ht="15.75" customHeight="1">
       <c r="A579" s="24"/>
       <c r="G579" s="22"/>
       <c r="H579" s="23"/>
-      <c r="I579" s="4"/>
+      <c r="I579" s="8"/>
     </row>
     <row r="580" ht="15.75" customHeight="1">
       <c r="A580" s="24"/>
       <c r="G580" s="22"/>
       <c r="H580" s="23"/>
-      <c r="I580" s="4"/>
+      <c r="I580" s="8"/>
     </row>
     <row r="581" ht="15.75" customHeight="1">
       <c r="A581" s="24"/>
       <c r="G581" s="22"/>
       <c r="H581" s="23"/>
-      <c r="I581" s="4"/>
+      <c r="I581" s="8"/>
     </row>
     <row r="582" ht="15.75" customHeight="1">
       <c r="A582" s="24"/>
       <c r="G582" s="22"/>
       <c r="H582" s="23"/>
-      <c r="I582" s="4"/>
+      <c r="I582" s="8"/>
     </row>
     <row r="583" ht="15.75" customHeight="1">
       <c r="A583" s="24"/>
       <c r="G583" s="22"/>
       <c r="H583" s="23"/>
-      <c r="I583" s="4"/>
+      <c r="I583" s="8"/>
     </row>
     <row r="584" ht="15.75" customHeight="1">
       <c r="A584" s="24"/>
       <c r="G584" s="22"/>
       <c r="H584" s="23"/>
-      <c r="I584" s="4"/>
+      <c r="I584" s="8"/>
     </row>
     <row r="585" ht="15.75" customHeight="1">
       <c r="A585" s="24"/>
       <c r="G585" s="22"/>
       <c r="H585" s="23"/>
-      <c r="I585" s="4"/>
+      <c r="I585" s="8"/>
     </row>
     <row r="586" ht="15.75" customHeight="1">
       <c r="A586" s="24"/>
       <c r="G586" s="22"/>
       <c r="H586" s="23"/>
-      <c r="I586" s="4"/>
+      <c r="I586" s="8"/>
     </row>
     <row r="587" ht="15.75" customHeight="1">
       <c r="A587" s="24"/>
       <c r="G587" s="22"/>
       <c r="H587" s="23"/>
-      <c r="I587" s="4"/>
+      <c r="I587" s="8"/>
     </row>
     <row r="588" ht="15.75" customHeight="1">
       <c r="A588" s="24"/>
       <c r="G588" s="22"/>
       <c r="H588" s="23"/>
-      <c r="I588" s="4"/>
+      <c r="I588" s="8"/>
     </row>
     <row r="589" ht="15.75" customHeight="1">
       <c r="A589" s="24"/>
       <c r="G589" s="22"/>
       <c r="H589" s="23"/>
-      <c r="I589" s="4"/>
+      <c r="I589" s="8"/>
     </row>
     <row r="590" ht="15.75" customHeight="1">
       <c r="A590" s="24"/>
       <c r="G590" s="22"/>
       <c r="H590" s="23"/>
-      <c r="I590" s="4"/>
+      <c r="I590" s="8"/>
     </row>
     <row r="591" ht="15.75" customHeight="1">
       <c r="A591" s="24"/>
       <c r="G591" s="22"/>
       <c r="H591" s="23"/>
-      <c r="I591" s="4"/>
+      <c r="I591" s="8"/>
     </row>
     <row r="592" ht="15.75" customHeight="1">
       <c r="A592" s="24"/>
       <c r="G592" s="22"/>
       <c r="H592" s="23"/>
-      <c r="I592" s="4"/>
+      <c r="I592" s="8"/>
     </row>
     <row r="593" ht="15.75" customHeight="1">
       <c r="A593" s="24"/>
       <c r="G593" s="22"/>
       <c r="H593" s="23"/>
-      <c r="I593" s="4"/>
+      <c r="I593" s="8"/>
     </row>
     <row r="594" ht="15.75" customHeight="1">
       <c r="A594" s="24"/>
       <c r="G594" s="22"/>
       <c r="H594" s="23"/>
-      <c r="I594" s="4"/>
+      <c r="I594" s="8"/>
     </row>
     <row r="595" ht="15.75" customHeight="1">
       <c r="A595" s="24"/>
       <c r="G595" s="22"/>
       <c r="H595" s="23"/>
-      <c r="I595" s="4"/>
+      <c r="I595" s="8"/>
     </row>
     <row r="596" ht="15.75" customHeight="1">
       <c r="A596" s="24"/>
       <c r="G596" s="22"/>
       <c r="H596" s="23"/>
-      <c r="I596" s="4"/>
+      <c r="I596" s="8"/>
     </row>
     <row r="597" ht="15.75" customHeight="1">
       <c r="A597" s="24"/>
       <c r="G597" s="22"/>
       <c r="H597" s="23"/>
-      <c r="I597" s="4"/>
+      <c r="I597" s="8"/>
     </row>
     <row r="598" ht="15.75" customHeight="1">
       <c r="A598" s="24"/>
       <c r="G598" s="22"/>
       <c r="H598" s="23"/>
-      <c r="I598" s="4"/>
+      <c r="I598" s="8"/>
     </row>
     <row r="599" ht="15.75" customHeight="1">
       <c r="A599" s="24"/>
       <c r="G599" s="22"/>
       <c r="H599" s="23"/>
-      <c r="I599" s="4"/>
+      <c r="I599" s="8"/>
     </row>
     <row r="600" ht="15.75" customHeight="1">
       <c r="A600" s="24"/>
       <c r="G600" s="22"/>
       <c r="H600" s="23"/>
-      <c r="I600" s="4"/>
+      <c r="I600" s="8"/>
     </row>
     <row r="601" ht="15.75" customHeight="1">
       <c r="A601" s="24"/>
       <c r="G601" s="22"/>
       <c r="H601" s="23"/>
-      <c r="I601" s="4"/>
+      <c r="I601" s="8"/>
     </row>
     <row r="602" ht="15.75" customHeight="1">
       <c r="A602" s="24"/>
       <c r="G602" s="22"/>
       <c r="H602" s="23"/>
-      <c r="I602" s="4"/>
+      <c r="I602" s="8"/>
     </row>
     <row r="603" ht="15.75" customHeight="1">
       <c r="A603" s="24"/>
       <c r="G603" s="22"/>
       <c r="H603" s="23"/>
-      <c r="I603" s="4"/>
+      <c r="I603" s="8"/>
     </row>
     <row r="604" ht="15.75" customHeight="1">
       <c r="A604" s="24"/>
       <c r="G604" s="22"/>
       <c r="H604" s="23"/>
-      <c r="I604" s="4"/>
+      <c r="I604" s="8"/>
     </row>
     <row r="605" ht="15.75" customHeight="1">
       <c r="A605" s="24"/>
       <c r="G605" s="22"/>
       <c r="H605" s="23"/>
-      <c r="I605" s="4"/>
+      <c r="I605" s="8"/>
     </row>
     <row r="606" ht="15.75" customHeight="1">
       <c r="A606" s="24"/>
       <c r="G606" s="22"/>
       <c r="H606" s="23"/>
-      <c r="I606" s="4"/>
+      <c r="I606" s="8"/>
     </row>
     <row r="607" ht="15.75" customHeight="1">
       <c r="A607" s="24"/>
       <c r="G607" s="22"/>
       <c r="H607" s="23"/>
-      <c r="I607" s="4"/>
+      <c r="I607" s="8"/>
     </row>
     <row r="608" ht="15.75" customHeight="1">
       <c r="A608" s="24"/>
       <c r="G608" s="22"/>
       <c r="H608" s="23"/>
-      <c r="I608" s="4"/>
+      <c r="I608" s="8"/>
     </row>
     <row r="609" ht="15.75" customHeight="1">
       <c r="A609" s="24"/>
       <c r="G609" s="22"/>
       <c r="H609" s="23"/>
-      <c r="I609" s="4"/>
+      <c r="I609" s="8"/>
     </row>
     <row r="610" ht="15.75" customHeight="1">
       <c r="A610" s="24"/>
       <c r="G610" s="22"/>
       <c r="H610" s="23"/>
-      <c r="I610" s="4"/>
+      <c r="I610" s="8"/>
     </row>
     <row r="611" ht="15.75" customHeight="1">
       <c r="A611" s="24"/>
       <c r="G611" s="22"/>
       <c r="H611" s="23"/>
-      <c r="I611" s="4"/>
+      <c r="I611" s="8"/>
     </row>
     <row r="612" ht="15.75" customHeight="1">
       <c r="A612" s="24"/>
       <c r="G612" s="22"/>
       <c r="H612" s="23"/>
-      <c r="I612" s="4"/>
+      <c r="I612" s="8"/>
     </row>
     <row r="613" ht="15.75" customHeight="1">
       <c r="A613" s="24"/>
       <c r="G613" s="22"/>
       <c r="H613" s="23"/>
-      <c r="I613" s="4"/>
+      <c r="I613" s="8"/>
     </row>
     <row r="614" ht="15.75" customHeight="1">
       <c r="A614" s="24"/>
       <c r="G614" s="22"/>
       <c r="H614" s="23"/>
-      <c r="I614" s="4"/>
+      <c r="I614" s="8"/>
     </row>
     <row r="615" ht="15.75" customHeight="1">
       <c r="A615" s="24"/>
       <c r="G615" s="22"/>
       <c r="H615" s="23"/>
-      <c r="I615" s="4"/>
+      <c r="I615" s="8"/>
     </row>
     <row r="616" ht="15.75" customHeight="1">
       <c r="A616" s="24"/>
       <c r="G616" s="22"/>
       <c r="H616" s="23"/>
-      <c r="I616" s="4"/>
+      <c r="I616" s="8"/>
     </row>
     <row r="617" ht="15.75" customHeight="1">
       <c r="A617" s="24"/>
       <c r="G617" s="22"/>
       <c r="H617" s="23"/>
-      <c r="I617" s="4"/>
+      <c r="I617" s="8"/>
     </row>
     <row r="618" ht="15.75" customHeight="1">
       <c r="A618" s="24"/>
       <c r="G618" s="22"/>
       <c r="H618" s="23"/>
-      <c r="I618" s="4"/>
+      <c r="I618" s="8"/>
     </row>
     <row r="619" ht="15.75" customHeight="1">
       <c r="A619" s="24"/>
       <c r="G619" s="22"/>
       <c r="H619" s="23"/>
-      <c r="I619" s="4"/>
+      <c r="I619" s="8"/>
     </row>
     <row r="620" ht="15.75" customHeight="1">
       <c r="A620" s="24"/>
       <c r="G620" s="22"/>
       <c r="H620" s="23"/>
-      <c r="I620" s="4"/>
+      <c r="I620" s="8"/>
     </row>
     <row r="621" ht="15.75" customHeight="1">
       <c r="A621" s="24"/>
       <c r="G621" s="22"/>
       <c r="H621" s="23"/>
-      <c r="I621" s="4"/>
+      <c r="I621" s="8"/>
     </row>
     <row r="622" ht="15.75" customHeight="1">
       <c r="A622" s="24"/>
       <c r="G622" s="22"/>
       <c r="H622" s="23"/>
-      <c r="I622" s="4"/>
+      <c r="I622" s="8"/>
     </row>
     <row r="623" ht="15.75" customHeight="1">
       <c r="A623" s="24"/>
       <c r="G623" s="22"/>
       <c r="H623" s="23"/>
-      <c r="I623" s="4"/>
+      <c r="I623" s="8"/>
     </row>
     <row r="624" ht="15.75" customHeight="1">
       <c r="A624" s="24"/>
       <c r="G624" s="22"/>
       <c r="H624" s="23"/>
-      <c r="I624" s="4"/>
+      <c r="I624" s="8"/>
     </row>
     <row r="625" ht="15.75" customHeight="1">
       <c r="A625" s="24"/>
       <c r="G625" s="22"/>
       <c r="H625" s="23"/>
-      <c r="I625" s="4"/>
+      <c r="I625" s="8"/>
     </row>
     <row r="626" ht="15.75" customHeight="1">
       <c r="A626" s="24"/>
       <c r="G626" s="22"/>
       <c r="H626" s="23"/>
-      <c r="I626" s="4"/>
+      <c r="I626" s="8"/>
     </row>
     <row r="627" ht="15.75" customHeight="1">
       <c r="A627" s="24"/>
       <c r="G627" s="22"/>
       <c r="H627" s="23"/>
-      <c r="I627" s="4"/>
+      <c r="I627" s="8"/>
     </row>
     <row r="628" ht="15.75" customHeight="1">
       <c r="A628" s="24"/>
       <c r="G628" s="22"/>
       <c r="H628" s="23"/>
-      <c r="I628" s="4"/>
+      <c r="I628" s="8"/>
     </row>
     <row r="629" ht="15.75" customHeight="1">
       <c r="A629" s="24"/>
       <c r="G629" s="22"/>
       <c r="H629" s="23"/>
-      <c r="I629" s="4"/>
+      <c r="I629" s="8"/>
     </row>
     <row r="630" ht="15.75" customHeight="1">
       <c r="A630" s="24"/>
       <c r="G630" s="22"/>
       <c r="H630" s="23"/>
-      <c r="I630" s="4"/>
+      <c r="I630" s="8"/>
     </row>
     <row r="631" ht="15.75" customHeight="1">
       <c r="A631" s="24"/>
       <c r="G631" s="22"/>
       <c r="H631" s="23"/>
-      <c r="I631" s="4"/>
+      <c r="I631" s="8"/>
     </row>
     <row r="632" ht="15.75" customHeight="1">
       <c r="A632" s="24"/>
       <c r="G632" s="22"/>
       <c r="H632" s="23"/>
-      <c r="I632" s="4"/>
+      <c r="I632" s="8"/>
     </row>
     <row r="633" ht="15.75" customHeight="1">
       <c r="A633" s="24"/>
       <c r="G633" s="22"/>
       <c r="H633" s="23"/>
-      <c r="I633" s="4"/>
+      <c r="I633" s="8"/>
     </row>
     <row r="634" ht="15.75" customHeight="1">
       <c r="A634" s="24"/>
       <c r="G634" s="22"/>
       <c r="H634" s="23"/>
-      <c r="I634" s="4"/>
+      <c r="I634" s="8"/>
     </row>
     <row r="635" ht="15.75" customHeight="1">
       <c r="A635" s="24"/>
       <c r="G635" s="22"/>
       <c r="H635" s="23"/>
-      <c r="I635" s="4"/>
+      <c r="I635" s="8"/>
     </row>
     <row r="636" ht="15.75" customHeight="1">
       <c r="A636" s="24"/>
       <c r="G636" s="22"/>
       <c r="H636" s="23"/>
-      <c r="I636" s="4"/>
+      <c r="I636" s="8"/>
     </row>
     <row r="637" ht="15.75" customHeight="1">
       <c r="A637" s="24"/>
       <c r="G637" s="22"/>
       <c r="H637" s="23"/>
-      <c r="I637" s="4"/>
+      <c r="I637" s="8"/>
     </row>
     <row r="638" ht="15.75" customHeight="1">
       <c r="A638" s="24"/>
       <c r="G638" s="22"/>
       <c r="H638" s="23"/>
-      <c r="I638" s="4"/>
+      <c r="I638" s="8"/>
     </row>
     <row r="639" ht="15.75" customHeight="1">
       <c r="A639" s="24"/>
       <c r="G639" s="22"/>
       <c r="H639" s="23"/>
-      <c r="I639" s="4"/>
+      <c r="I639" s="8"/>
     </row>
     <row r="640" ht="15.75" customHeight="1">
       <c r="A640" s="24"/>
       <c r="G640" s="22"/>
       <c r="H640" s="23"/>
-      <c r="I640" s="4"/>
+      <c r="I640" s="8"/>
     </row>
     <row r="641" ht="15.75" customHeight="1">
       <c r="A641" s="24"/>
       <c r="G641" s="22"/>
       <c r="H641" s="23"/>
-      <c r="I641" s="4"/>
+      <c r="I641" s="8"/>
     </row>
     <row r="642" ht="15.75" customHeight="1">
       <c r="A642" s="24"/>
       <c r="G642" s="22"/>
       <c r="H642" s="23"/>
-      <c r="I642" s="4"/>
+      <c r="I642" s="8"/>
     </row>
     <row r="643" ht="15.75" customHeight="1">
       <c r="A643" s="24"/>
       <c r="G643" s="22"/>
       <c r="H643" s="23"/>
-      <c r="I643" s="4"/>
+      <c r="I643" s="8"/>
     </row>
     <row r="644" ht="15.75" customHeight="1">
       <c r="A644" s="24"/>
       <c r="G644" s="22"/>
       <c r="H644" s="23"/>
-      <c r="I644" s="4"/>
+      <c r="I644" s="8"/>
     </row>
     <row r="645" ht="15.75" customHeight="1">
       <c r="A645" s="24"/>
       <c r="G645" s="22"/>
       <c r="H645" s="23"/>
-      <c r="I645" s="4"/>
+      <c r="I645" s="8"/>
     </row>
     <row r="646" ht="15.75" customHeight="1">
       <c r="A646" s="24"/>
       <c r="G646" s="22"/>
       <c r="H646" s="23"/>
-      <c r="I646" s="4"/>
+      <c r="I646" s="8"/>
     </row>
     <row r="647" ht="15.75" customHeight="1">
       <c r="A647" s="24"/>
       <c r="G647" s="22"/>
       <c r="H647" s="23"/>
-      <c r="I647" s="4"/>
+      <c r="I647" s="8"/>
     </row>
     <row r="648" ht="15.75" customHeight="1">
       <c r="A648" s="24"/>
       <c r="G648" s="22"/>
       <c r="H648" s="23"/>
-      <c r="I648" s="4"/>
+      <c r="I648" s="8"/>
     </row>
     <row r="649" ht="15.75" customHeight="1">
       <c r="A649" s="24"/>
       <c r="G649" s="22"/>
       <c r="H649" s="23"/>
-      <c r="I649" s="4"/>
+      <c r="I649" s="8"/>
     </row>
     <row r="650" ht="15.75" customHeight="1">
       <c r="A650" s="24"/>
       <c r="G650" s="22"/>
       <c r="H650" s="23"/>
-      <c r="I650" s="4"/>
+      <c r="I650" s="8"/>
     </row>
     <row r="651" ht="15.75" customHeight="1">
       <c r="A651" s="24"/>
       <c r="G651" s="22"/>
       <c r="H651" s="23"/>
-      <c r="I651" s="4"/>
+      <c r="I651" s="8"/>
     </row>
     <row r="652" ht="15.75" customHeight="1">
       <c r="A652" s="24"/>
       <c r="G652" s="22"/>
       <c r="H652" s="23"/>
-      <c r="I652" s="4"/>
+      <c r="I652" s="8"/>
     </row>
     <row r="653" ht="15.75" customHeight="1">
       <c r="A653" s="24"/>
       <c r="G653" s="22"/>
       <c r="H653" s="23"/>
-      <c r="I653" s="4"/>
+      <c r="I653" s="8"/>
     </row>
     <row r="654" ht="15.75" customHeight="1">
       <c r="A654" s="24"/>
       <c r="G654" s="22"/>
       <c r="H654" s="23"/>
-      <c r="I654" s="4"/>
+      <c r="I654" s="8"/>
     </row>
     <row r="655" ht="15.75" customHeight="1">
       <c r="A655" s="24"/>
       <c r="G655" s="22"/>
       <c r="H655" s="23"/>
-      <c r="I655" s="4"/>
+      <c r="I655" s="8"/>
     </row>
     <row r="656" ht="15.75" customHeight="1">
       <c r="A656" s="24"/>
       <c r="G656" s="22"/>
       <c r="H656" s="23"/>
-      <c r="I656" s="4"/>
+      <c r="I656" s="8"/>
     </row>
     <row r="657" ht="15.75" customHeight="1">
       <c r="A657" s="24"/>
       <c r="G657" s="22"/>
       <c r="H657" s="23"/>
-      <c r="I657" s="4"/>
+      <c r="I657" s="8"/>
     </row>
     <row r="658" ht="15.75" customHeight="1">
       <c r="A658" s="24"/>
       <c r="G658" s="22"/>
       <c r="H658" s="23"/>
-      <c r="I658" s="4"/>
+      <c r="I658" s="8"/>
     </row>
     <row r="659" ht="15.75" customHeight="1">
       <c r="A659" s="24"/>
       <c r="G659" s="22"/>
       <c r="H659" s="23"/>
-      <c r="I659" s="4"/>
+      <c r="I659" s="8"/>
     </row>
     <row r="660" ht="15.75" customHeight="1">
       <c r="A660" s="24"/>
       <c r="G660" s="22"/>
       <c r="H660" s="23"/>
-      <c r="I660" s="4"/>
+      <c r="I660" s="8"/>
     </row>
     <row r="661" ht="15.75" customHeight="1">
       <c r="A661" s="24"/>
       <c r="G661" s="22"/>
       <c r="H661" s="23"/>
-      <c r="I661" s="4"/>
+      <c r="I661" s="8"/>
     </row>
     <row r="662" ht="15.75" customHeight="1">
       <c r="A662" s="24"/>
       <c r="G662" s="22"/>
       <c r="H662" s="23"/>
-      <c r="I662" s="4"/>
+      <c r="I662" s="8"/>
     </row>
     <row r="663" ht="15.75" customHeight="1">
       <c r="A663" s="24"/>
       <c r="G663" s="22"/>
       <c r="H663" s="23"/>
-      <c r="I663" s="4"/>
+      <c r="I663" s="8"/>
     </row>
     <row r="664" ht="15.75" customHeight="1">
       <c r="A664" s="24"/>
       <c r="G664" s="22"/>
       <c r="H664" s="23"/>
-      <c r="I664" s="4"/>
+      <c r="I664" s="8"/>
     </row>
     <row r="665" ht="15.75" customHeight="1">
       <c r="A665" s="24"/>
       <c r="G665" s="22"/>
       <c r="H665" s="23"/>
-      <c r="I665" s="4"/>
+      <c r="I665" s="8"/>
     </row>
     <row r="666" ht="15.75" customHeight="1">
       <c r="A666" s="24"/>
       <c r="G666" s="22"/>
       <c r="H666" s="23"/>
-      <c r="I666" s="4"/>
+      <c r="I666" s="8"/>
     </row>
     <row r="667" ht="15.75" customHeight="1">
       <c r="A667" s="24"/>
       <c r="G667" s="22"/>
       <c r="H667" s="23"/>
-      <c r="I667" s="4"/>
+      <c r="I667" s="8"/>
     </row>
     <row r="668" ht="15.75" customHeight="1">
       <c r="A668" s="24"/>
       <c r="G668" s="22"/>
       <c r="H668" s="23"/>
-      <c r="I668" s="4"/>
+      <c r="I668" s="8"/>
     </row>
     <row r="669" ht="15.75" customHeight="1">
       <c r="A669" s="24"/>
       <c r="G669" s="22"/>
       <c r="H669" s="23"/>
-      <c r="I669" s="4"/>
+      <c r="I669" s="8"/>
     </row>
     <row r="670" ht="15.75" customHeight="1">
       <c r="A670" s="24"/>
       <c r="G670" s="22"/>
       <c r="H670" s="23"/>
-      <c r="I670" s="4"/>
+      <c r="I670" s="8"/>
     </row>
     <row r="671" ht="15.75" customHeight="1">
       <c r="A671" s="24"/>
       <c r="G671" s="22"/>
       <c r="H671" s="23"/>
-      <c r="I671" s="4"/>
+      <c r="I671" s="8"/>
     </row>
     <row r="672" ht="15.75" customHeight="1">
       <c r="A672" s="24"/>
       <c r="G672" s="22"/>
       <c r="H672" s="23"/>
-      <c r="I672" s="4"/>
+      <c r="I672" s="8"/>
     </row>
     <row r="673" ht="15.75" customHeight="1">
       <c r="A673" s="24"/>
       <c r="G673" s="22"/>
       <c r="H673" s="23"/>
-      <c r="I673" s="4"/>
+      <c r="I673" s="8"/>
     </row>
     <row r="674" ht="15.75" customHeight="1">
       <c r="A674" s="24"/>
       <c r="G674" s="22"/>
       <c r="H674" s="23"/>
-      <c r="I674" s="4"/>
+      <c r="I674" s="8"/>
     </row>
     <row r="675" ht="15.75" customHeight="1">
       <c r="A675" s="24"/>
       <c r="G675" s="22"/>
       <c r="H675" s="23"/>
-      <c r="I675" s="4"/>
+      <c r="I675" s="8"/>
     </row>
     <row r="676" ht="15.75" customHeight="1">
       <c r="A676" s="24"/>
       <c r="G676" s="22"/>
       <c r="H676" s="23"/>
-      <c r="I676" s="4"/>
+      <c r="I676" s="8"/>
     </row>
     <row r="677" ht="15.75" customHeight="1">
       <c r="A677" s="24"/>
       <c r="G677" s="22"/>
       <c r="H677" s="23"/>
-      <c r="I677" s="4"/>
+      <c r="I677" s="8"/>
     </row>
     <row r="678" ht="15.75" customHeight="1">
       <c r="A678" s="24"/>
       <c r="G678" s="22"/>
       <c r="H678" s="23"/>
-      <c r="I678" s="4"/>
+      <c r="I678" s="8"/>
     </row>
     <row r="679" ht="15.75" customHeight="1">
       <c r="A679" s="24"/>
       <c r="G679" s="22"/>
       <c r="H679" s="23"/>
-      <c r="I679" s="4"/>
+      <c r="I679" s="8"/>
     </row>
     <row r="680" ht="15.75" customHeight="1">
       <c r="A680" s="24"/>
       <c r="G680" s="22"/>
       <c r="H680" s="23"/>
-      <c r="I680" s="4"/>
+      <c r="I680" s="8"/>
     </row>
     <row r="681" ht="15.75" customHeight="1">
       <c r="A681" s="24"/>
       <c r="G681" s="22"/>
       <c r="H681" s="23"/>
-      <c r="I681" s="4"/>
+      <c r="I681" s="8"/>
     </row>
     <row r="682" ht="15.75" customHeight="1">
       <c r="A682" s="24"/>
       <c r="G682" s="22"/>
       <c r="H682" s="23"/>
-      <c r="I682" s="4"/>
+      <c r="I682" s="8"/>
     </row>
     <row r="683" ht="15.75" customHeight="1">
       <c r="A683" s="24"/>
       <c r="G683" s="22"/>
       <c r="H683" s="23"/>
-      <c r="I683" s="4"/>
+      <c r="I683" s="8"/>
     </row>
     <row r="684" ht="15.75" customHeight="1">
       <c r="A684" s="24"/>
       <c r="G684" s="22"/>
       <c r="H684" s="23"/>
-      <c r="I684" s="4"/>
+      <c r="I684" s="8"/>
     </row>
     <row r="685" ht="15.75" customHeight="1">
       <c r="A685" s="24"/>
       <c r="G685" s="22"/>
       <c r="H685" s="23"/>
-      <c r="I685" s="4"/>
+      <c r="I685" s="8"/>
     </row>
     <row r="686" ht="15.75" customHeight="1">
       <c r="A686" s="24"/>
       <c r="G686" s="22"/>
       <c r="H686" s="23"/>
-      <c r="I686" s="4"/>
+      <c r="I686" s="8"/>
     </row>
     <row r="687" ht="15.75" customHeight="1">
       <c r="A687" s="24"/>
       <c r="G687" s="22"/>
       <c r="H687" s="23"/>
-      <c r="I687" s="4"/>
+      <c r="I687" s="8"/>
     </row>
     <row r="688" ht="15.75" customHeight="1">
       <c r="A688" s="24"/>
       <c r="G688" s="22"/>
       <c r="H688" s="23"/>
-      <c r="I688" s="4"/>
+      <c r="I688" s="8"/>
     </row>
     <row r="689" ht="15.75" customHeight="1">
       <c r="A689" s="24"/>
       <c r="G689" s="22"/>
       <c r="H689" s="23"/>
-      <c r="I689" s="4"/>
+      <c r="I689" s="8"/>
     </row>
     <row r="690" ht="15.75" customHeight="1">
       <c r="A690" s="24"/>
       <c r="G690" s="22"/>
       <c r="H690" s="23"/>
-      <c r="I690" s="4"/>
+      <c r="I690" s="8"/>
     </row>
     <row r="691" ht="15.75" customHeight="1">
       <c r="A691" s="24"/>
       <c r="G691" s="22"/>
       <c r="H691" s="23"/>
-      <c r="I691" s="4"/>
+      <c r="I691" s="8"/>
     </row>
     <row r="692" ht="15.75" customHeight="1">
       <c r="A692" s="24"/>
       <c r="G692" s="22"/>
       <c r="H692" s="23"/>
-      <c r="I692" s="4"/>
+      <c r="I692" s="8"/>
     </row>
     <row r="693" ht="15.75" customHeight="1">
       <c r="A693" s="24"/>
       <c r="G693" s="22"/>
       <c r="H693" s="23"/>
-      <c r="I693" s="4"/>
+      <c r="I693" s="8"/>
     </row>
     <row r="694" ht="15.75" customHeight="1">
       <c r="A694" s="24"/>
       <c r="G694" s="22"/>
       <c r="H694" s="23"/>
-      <c r="I694" s="4"/>
+      <c r="I694" s="8"/>
     </row>
     <row r="695" ht="15.75" customHeight="1">
       <c r="A695" s="24"/>
       <c r="G695" s="22"/>
       <c r="H695" s="23"/>
-      <c r="I695" s="4"/>
+      <c r="I695" s="8"/>
     </row>
     <row r="696" ht="15.75" customHeight="1">
       <c r="A696" s="24"/>
       <c r="G696" s="22"/>
       <c r="H696" s="23"/>
-      <c r="I696" s="4"/>
+      <c r="I696" s="8"/>
     </row>
     <row r="697" ht="15.75" customHeight="1">
       <c r="A697" s="24"/>
       <c r="G697" s="22"/>
       <c r="H697" s="23"/>
-      <c r="I697" s="4"/>
+      <c r="I697" s="8"/>
     </row>
     <row r="698" ht="15.75" customHeight="1">
       <c r="A698" s="24"/>
       <c r="G698" s="22"/>
       <c r="H698" s="23"/>
-      <c r="I698" s="4"/>
+      <c r="I698" s="8"/>
     </row>
     <row r="699" ht="15.75" customHeight="1">
       <c r="A699" s="24"/>
       <c r="G699" s="22"/>
       <c r="H699" s="23"/>
-      <c r="I699" s="4"/>
+      <c r="I699" s="8"/>
     </row>
     <row r="700" ht="15.75" customHeight="1">
       <c r="A700" s="24"/>
       <c r="G700" s="22"/>
       <c r="H700" s="23"/>
-      <c r="I700" s="4"/>
+      <c r="I700" s="8"/>
     </row>
     <row r="701" ht="15.75" customHeight="1">
       <c r="A701" s="24"/>
       <c r="G701" s="22"/>
       <c r="H701" s="23"/>
-      <c r="I701" s="4"/>
+      <c r="I701" s="8"/>
     </row>
     <row r="702" ht="15.75" customHeight="1">
       <c r="A702" s="24"/>
       <c r="G702" s="22"/>
       <c r="H702" s="23"/>
-      <c r="I702" s="4"/>
+      <c r="I702" s="8"/>
     </row>
     <row r="703" ht="15.75" customHeight="1">
       <c r="A703" s="24"/>
       <c r="G703" s="22"/>
       <c r="H703" s="23"/>
-      <c r="I703" s="4"/>
+      <c r="I703" s="8"/>
     </row>
     <row r="704" ht="15.75" customHeight="1">
       <c r="A704" s="24"/>
       <c r="G704" s="22"/>
       <c r="H704" s="23"/>
-      <c r="I704" s="4"/>
+      <c r="I704" s="8"/>
     </row>
     <row r="705" ht="15.75" customHeight="1">
       <c r="A705" s="24"/>
       <c r="G705" s="22"/>
       <c r="H705" s="23"/>
-      <c r="I705" s="4"/>
+      <c r="I705" s="8"/>
     </row>
     <row r="706" ht="15.75" customHeight="1">
       <c r="A706" s="24"/>
       <c r="G706" s="22"/>
       <c r="H706" s="23"/>
-      <c r="I706" s="4"/>
+      <c r="I706" s="8"/>
     </row>
     <row r="707" ht="15.75" customHeight="1">
       <c r="A707" s="24"/>
       <c r="G707" s="22"/>
       <c r="H707" s="23"/>
-      <c r="I707" s="4"/>
+      <c r="I707" s="8"/>
     </row>
     <row r="708" ht="15.75" customHeight="1">
       <c r="A708" s="24"/>
       <c r="G708" s="22"/>
       <c r="H708" s="23"/>
-      <c r="I708" s="4"/>
+      <c r="I708" s="8"/>
     </row>
     <row r="709" ht="15.75" customHeight="1">
       <c r="A709" s="24"/>
       <c r="G709" s="22"/>
       <c r="H709" s="23"/>
-      <c r="I709" s="4"/>
+      <c r="I709" s="8"/>
     </row>
     <row r="710" ht="15.75" customHeight="1">
       <c r="A710" s="24"/>
       <c r="G710" s="22"/>
       <c r="H710" s="23"/>
-      <c r="I710" s="4"/>
+      <c r="I710" s="8"/>
     </row>
     <row r="711" ht="15.75" customHeight="1">
       <c r="A711" s="24"/>
       <c r="G711" s="22"/>
       <c r="H711" s="23"/>
-      <c r="I711" s="4"/>
+      <c r="I711" s="8"/>
     </row>
     <row r="712" ht="15.75" customHeight="1">
       <c r="A712" s="24"/>
       <c r="G712" s="22"/>
       <c r="H712" s="23"/>
-      <c r="I712" s="4"/>
+      <c r="I712" s="8"/>
     </row>
     <row r="713" ht="15.75" customHeight="1">
       <c r="A713" s="24"/>
       <c r="G713" s="22"/>
       <c r="H713" s="23"/>
-      <c r="I713" s="4"/>
+      <c r="I713" s="8"/>
     </row>
     <row r="714" ht="15.75" customHeight="1">
       <c r="A714" s="24"/>
       <c r="G714" s="22"/>
       <c r="H714" s="23"/>
-      <c r="I714" s="4"/>
+      <c r="I714" s="8"/>
     </row>
     <row r="715" ht="15.75" customHeight="1">
       <c r="A715" s="24"/>
       <c r="G715" s="22"/>
       <c r="H715" s="23"/>
-      <c r="I715" s="4"/>
+      <c r="I715" s="8"/>
     </row>
     <row r="716" ht="15.75" customHeight="1">
       <c r="A716" s="24"/>
       <c r="G716" s="22"/>
       <c r="H716" s="23"/>
-      <c r="I716" s="4"/>
+      <c r="I716" s="8"/>
     </row>
     <row r="717" ht="15.75" customHeight="1">
       <c r="A717" s="24"/>
       <c r="G717" s="22"/>
       <c r="H717" s="23"/>
-      <c r="I717" s="4"/>
+      <c r="I717" s="8"/>
     </row>
     <row r="718" ht="15.75" customHeight="1">
       <c r="A718" s="24"/>
       <c r="G718" s="22"/>
       <c r="H718" s="23"/>
-      <c r="I718" s="4"/>
+      <c r="I718" s="8"/>
     </row>
     <row r="719" ht="15.75" customHeight="1">
       <c r="A719" s="24"/>
       <c r="G719" s="22"/>
       <c r="H719" s="23"/>
-      <c r="I719" s="4"/>
+      <c r="I719" s="8"/>
     </row>
     <row r="720" ht="15.75" customHeight="1">
       <c r="A720" s="24"/>
       <c r="G720" s="22"/>
       <c r="H720" s="23"/>
-      <c r="I720" s="4"/>
+      <c r="I720" s="8"/>
     </row>
     <row r="721" ht="15.75" customHeight="1">
       <c r="A721" s="24"/>
       <c r="G721" s="22"/>
       <c r="H721" s="23"/>
-      <c r="I721" s="4"/>
+      <c r="I721" s="8"/>
     </row>
     <row r="722" ht="15.75" customHeight="1">
       <c r="A722" s="24"/>
       <c r="G722" s="22"/>
       <c r="H722" s="23"/>
-      <c r="I722" s="4"/>
+      <c r="I722" s="8"/>
     </row>
     <row r="723" ht="15.75" customHeight="1">
       <c r="A723" s="24"/>
       <c r="G723" s="22"/>
       <c r="H723" s="23"/>
-      <c r="I723" s="4"/>
+      <c r="I723" s="8"/>
     </row>
     <row r="724" ht="15.75" customHeight="1">
       <c r="A724" s="24"/>
       <c r="G724" s="22"/>
       <c r="H724" s="23"/>
-      <c r="I724" s="4"/>
+      <c r="I724" s="8"/>
     </row>
     <row r="725" ht="15.75" customHeight="1">
       <c r="A725" s="24"/>
       <c r="G725" s="22"/>
       <c r="H725" s="23"/>
-      <c r="I725" s="4"/>
+      <c r="I725" s="8"/>
     </row>
     <row r="726" ht="15.75" customHeight="1">
       <c r="A726" s="24"/>
       <c r="G726" s="22"/>
       <c r="H726" s="23"/>
-      <c r="I726" s="4"/>
+      <c r="I726" s="8"/>
     </row>
     <row r="727" ht="15.75" customHeight="1">
       <c r="A727" s="24"/>
       <c r="G727" s="22"/>
       <c r="H727" s="23"/>
-      <c r="I727" s="4"/>
+      <c r="I727" s="8"/>
     </row>
     <row r="728" ht="15.75" customHeight="1">
       <c r="A728" s="24"/>
       <c r="G728" s="22"/>
       <c r="H728" s="23"/>
-      <c r="I728" s="4"/>
+      <c r="I728" s="8"/>
     </row>
     <row r="729" ht="15.75" customHeight="1">
       <c r="A729" s="24"/>
       <c r="G729" s="22"/>
       <c r="H729" s="23"/>
-      <c r="I729" s="4"/>
+      <c r="I729" s="8"/>
     </row>
     <row r="730" ht="15.75" customHeight="1">
       <c r="A730" s="24"/>
       <c r="G730" s="22"/>
       <c r="H730" s="23"/>
-      <c r="I730" s="4"/>
+      <c r="I730" s="8"/>
     </row>
     <row r="731" ht="15.75" customHeight="1">
       <c r="A731" s="24"/>
       <c r="G731" s="22"/>
       <c r="H731" s="23"/>
-      <c r="I731" s="4"/>
+      <c r="I731" s="8"/>
     </row>
     <row r="732" ht="15.75" customHeight="1">
       <c r="A732" s="24"/>
       <c r="G732" s="22"/>
       <c r="H732" s="23"/>
-      <c r="I732" s="4"/>
+      <c r="I732" s="8"/>
     </row>
     <row r="733" ht="15.75" customHeight="1">
       <c r="A733" s="24"/>
       <c r="G733" s="22"/>
       <c r="H733" s="23"/>
-      <c r="I733" s="4"/>
+      <c r="I733" s="8"/>
     </row>
     <row r="734" ht="15.75" customHeight="1">
       <c r="A734" s="24"/>
       <c r="G734" s="22"/>
       <c r="H734" s="23"/>
-      <c r="I734" s="4"/>
+      <c r="I734" s="8"/>
     </row>
     <row r="735" ht="15.75" customHeight="1">
       <c r="A735" s="24"/>
       <c r="G735" s="22"/>
       <c r="H735" s="23"/>
-      <c r="I735" s="4"/>
+      <c r="I735" s="8"/>
     </row>
     <row r="736" ht="15.75" customHeight="1">
       <c r="A736" s="24"/>
       <c r="G736" s="22"/>
       <c r="H736" s="23"/>
-      <c r="I736" s="4"/>
+      <c r="I736" s="8"/>
     </row>
     <row r="737" ht="15.75" customHeight="1">
       <c r="A737" s="24"/>
       <c r="G737" s="22"/>
       <c r="H737" s="23"/>
-      <c r="I737" s="4"/>
+      <c r="I737" s="8"/>
     </row>
     <row r="738" ht="15.75" customHeight="1">
       <c r="A738" s="24"/>
       <c r="G738" s="22"/>
       <c r="H738" s="23"/>
-      <c r="I738" s="4"/>
+      <c r="I738" s="8"/>
     </row>
     <row r="739" ht="15.75" customHeight="1">
       <c r="A739" s="24"/>
       <c r="G739" s="22"/>
       <c r="H739" s="23"/>
-      <c r="I739" s="4"/>
+      <c r="I739" s="8"/>
     </row>
     <row r="740" ht="15.75" customHeight="1">
       <c r="A740" s="24"/>
       <c r="G740" s="22"/>
       <c r="H740" s="23"/>
-      <c r="I740" s="4"/>
+      <c r="I740" s="8"/>
     </row>
     <row r="741" ht="15.75" customHeight="1">
       <c r="A741" s="24"/>
       <c r="G741" s="22"/>
       <c r="H741" s="23"/>
-      <c r="I741" s="4"/>
+      <c r="I741" s="8"/>
     </row>
     <row r="742" ht="15.75" customHeight="1">
       <c r="A742" s="24"/>
       <c r="G742" s="22"/>
       <c r="H742" s="23"/>
-      <c r="I742" s="4"/>
+      <c r="I742" s="8"/>
     </row>
     <row r="743" ht="15.75" customHeight="1">
       <c r="A743" s="24"/>
       <c r="G743" s="22"/>
       <c r="H743" s="23"/>
-      <c r="I743" s="4"/>
+      <c r="I743" s="8"/>
     </row>
     <row r="744" ht="15.75" customHeight="1">
       <c r="A744" s="24"/>
       <c r="G744" s="22"/>
       <c r="H744" s="23"/>
-      <c r="I744" s="4"/>
+      <c r="I744" s="8"/>
     </row>
     <row r="745" ht="15.75" customHeight="1">
       <c r="A745" s="24"/>
       <c r="G745" s="22"/>
       <c r="H745" s="23"/>
-      <c r="I745" s="4"/>
+      <c r="I745" s="8"/>
     </row>
     <row r="746" ht="15.75" customHeight="1">
       <c r="A746" s="24"/>
       <c r="G746" s="22"/>
       <c r="H746" s="23"/>
-      <c r="I746" s="4"/>
+      <c r="I746" s="8"/>
     </row>
     <row r="747" ht="15.75" customHeight="1">
       <c r="A747" s="24"/>
       <c r="G747" s="22"/>
       <c r="H747" s="23"/>
-      <c r="I747" s="4"/>
+      <c r="I747" s="8"/>
     </row>
     <row r="748" ht="15.75" customHeight="1">
       <c r="A748" s="24"/>
       <c r="G748" s="22"/>
       <c r="H748" s="23"/>
-      <c r="I748" s="4"/>
+      <c r="I748" s="8"/>
     </row>
     <row r="749" ht="15.75" customHeight="1">
       <c r="A749" s="24"/>
       <c r="G749" s="22"/>
       <c r="H749" s="23"/>
-      <c r="I749" s="4"/>
+      <c r="I749" s="8"/>
     </row>
     <row r="750" ht="15.75" customHeight="1">
       <c r="A750" s="24"/>
       <c r="G750" s="22"/>
       <c r="H750" s="23"/>
-      <c r="I750" s="4"/>
+      <c r="I750" s="8"/>
     </row>
     <row r="751" ht="15.75" customHeight="1">
       <c r="A751" s="24"/>
       <c r="G751" s="22"/>
       <c r="H751" s="23"/>
-      <c r="I751" s="4"/>
+      <c r="I751" s="8"/>
     </row>
     <row r="752" ht="15.75" customHeight="1">
       <c r="A752" s="24"/>
       <c r="G752" s="22"/>
       <c r="H752" s="23"/>
-      <c r="I752" s="4"/>
+      <c r="I752" s="8"/>
     </row>
     <row r="753" ht="15.75" customHeight="1">
       <c r="A753" s="24"/>
       <c r="G753" s="22"/>
       <c r="H753" s="23"/>
-      <c r="I753" s="4"/>
+      <c r="I753" s="8"/>
     </row>
     <row r="754" ht="15.75" customHeight="1">
       <c r="A754" s="24"/>
       <c r="G754" s="22"/>
       <c r="H754" s="23"/>
-      <c r="I754" s="4"/>
+      <c r="I754" s="8"/>
     </row>
     <row r="755" ht="15.75" customHeight="1">
       <c r="A755" s="24"/>
       <c r="G755" s="22"/>
       <c r="H755" s="23"/>
-      <c r="I755" s="4"/>
+      <c r="I755" s="8"/>
     </row>
     <row r="756" ht="15.75" customHeight="1">
       <c r="A756" s="24"/>
       <c r="G756" s="22"/>
       <c r="H756" s="23"/>
-      <c r="I756" s="4"/>
+      <c r="I756" s="8"/>
     </row>
     <row r="757" ht="15.75" customHeight="1">
       <c r="A757" s="24"/>
       <c r="G757" s="22"/>
       <c r="H757" s="23"/>
-      <c r="I757" s="4"/>
+      <c r="I757" s="8"/>
     </row>
     <row r="758" ht="15.75" customHeight="1">
       <c r="A758" s="24"/>
       <c r="G758" s="22"/>
       <c r="H758" s="23"/>
-      <c r="I758" s="4"/>
+      <c r="I758" s="8"/>
     </row>
     <row r="759" ht="15.75" customHeight="1">
       <c r="A759" s="24"/>
       <c r="G759" s="22"/>
       <c r="H759" s="23"/>
-      <c r="I759" s="4"/>
+      <c r="I759" s="8"/>
     </row>
     <row r="760" ht="15.75" customHeight="1">
       <c r="A760" s="24"/>
       <c r="G760" s="22"/>
       <c r="H760" s="23"/>
-      <c r="I760" s="4"/>
+      <c r="I760" s="8"/>
     </row>
     <row r="761" ht="15.75" customHeight="1">
       <c r="A761" s="24"/>
       <c r="G761" s="22"/>
       <c r="H761" s="23"/>
-      <c r="I761" s="4"/>
+      <c r="I761" s="8"/>
     </row>
     <row r="762" ht="15.75" customHeight="1">
       <c r="A762" s="24"/>
       <c r="G762" s="22"/>
       <c r="H762" s="23"/>
-      <c r="I762" s="4"/>
+      <c r="I762" s="8"/>
     </row>
     <row r="763" ht="15.75" customHeight="1">
       <c r="A763" s="24"/>
       <c r="G763" s="22"/>
       <c r="H763" s="23"/>
-      <c r="I763" s="4"/>
+      <c r="I763" s="8"/>
     </row>
     <row r="764" ht="15.75" customHeight="1">
       <c r="A764" s="24"/>
       <c r="G764" s="22"/>
       <c r="H764" s="23"/>
-      <c r="I764" s="4"/>
+      <c r="I764" s="8"/>
     </row>
     <row r="765" ht="15.75" customHeight="1">
       <c r="A765" s="24"/>
       <c r="G765" s="22"/>
       <c r="H765" s="23"/>
-      <c r="I765" s="4"/>
+      <c r="I765" s="8"/>
     </row>
     <row r="766" ht="15.75" customHeight="1">
       <c r="A766" s="24"/>
       <c r="G766" s="22"/>
       <c r="H766" s="23"/>
-      <c r="I766" s="4"/>
+      <c r="I766" s="8"/>
     </row>
     <row r="767" ht="15.75" customHeight="1">
       <c r="A767" s="24"/>
       <c r="G767" s="22"/>
       <c r="H767" s="23"/>
-      <c r="I767" s="4"/>
+      <c r="I767" s="8"/>
     </row>
     <row r="768" ht="15.75" customHeight="1">
       <c r="A768" s="24"/>
       <c r="G768" s="22"/>
       <c r="H768" s="23"/>
-      <c r="I768" s="4"/>
+      <c r="I768" s="8"/>
     </row>
     <row r="769" ht="15.75" customHeight="1">
       <c r="A769" s="24"/>
       <c r="G769" s="22"/>
       <c r="H769" s="23"/>
-      <c r="I769" s="4"/>
+      <c r="I769" s="8"/>
     </row>
     <row r="770" ht="15.75" customHeight="1">
       <c r="A770" s="24"/>
       <c r="G770" s="22"/>
       <c r="H770" s="23"/>
-      <c r="I770" s="4"/>
+      <c r="I770" s="8"/>
     </row>
     <row r="771" ht="15.75" customHeight="1">
       <c r="A771" s="24"/>
       <c r="G771" s="22"/>
       <c r="H771" s="23"/>
-      <c r="I771" s="4"/>
+      <c r="I771" s="8"/>
     </row>
     <row r="772" ht="15.75" customHeight="1">
       <c r="A772" s="24"/>
       <c r="G772" s="22"/>
       <c r="H772" s="23"/>
-      <c r="I772" s="4"/>
+      <c r="I772" s="8"/>
     </row>
     <row r="773" ht="15.75" customHeight="1">
       <c r="A773" s="24"/>
       <c r="G773" s="22"/>
       <c r="H773" s="23"/>
-      <c r="I773" s="4"/>
+      <c r="I773" s="8"/>
     </row>
     <row r="774" ht="15.75" customHeight="1">
       <c r="A774" s="24"/>
       <c r="G774" s="22"/>
       <c r="H774" s="23"/>
-      <c r="I774" s="4"/>
+      <c r="I774" s="8"/>
     </row>
     <row r="775" ht="15.75" customHeight="1">
       <c r="A775" s="24"/>
       <c r="G775" s="22"/>
       <c r="H775" s="23"/>
-      <c r="I775" s="4"/>
+      <c r="I775" s="8"/>
     </row>
     <row r="776" ht="15.75" customHeight="1">
       <c r="A776" s="24"/>
       <c r="G776" s="22"/>
       <c r="H776" s="23"/>
-      <c r="I776" s="4"/>
+      <c r="I776" s="8"/>
     </row>
     <row r="777" ht="15.75" customHeight="1">
       <c r="A777" s="24"/>
       <c r="G777" s="22"/>
       <c r="H777" s="23"/>
-      <c r="I777" s="4"/>
+      <c r="I777" s="8"/>
     </row>
     <row r="778" ht="15.75" customHeight="1">
       <c r="A778" s="24"/>
       <c r="G778" s="22"/>
       <c r="H778" s="23"/>
-      <c r="I778" s="4"/>
+      <c r="I778" s="8"/>
     </row>
     <row r="779" ht="15.75" customHeight="1">
       <c r="A779" s="24"/>
       <c r="G779" s="22"/>
       <c r="H779" s="23"/>
-      <c r="I779" s="4"/>
+      <c r="I779" s="8"/>
     </row>
     <row r="780" ht="15.75" customHeight="1">
       <c r="A780" s="24"/>
       <c r="G780" s="22"/>
       <c r="H780" s="23"/>
-      <c r="I780" s="4"/>
+      <c r="I780" s="8"/>
     </row>
     <row r="781" ht="15.75" customHeight="1">
       <c r="A781" s="24"/>
       <c r="G781" s="22"/>
       <c r="H781" s="23"/>
-      <c r="I781" s="4"/>
+      <c r="I781" s="8"/>
     </row>
     <row r="782" ht="15.75" customHeight="1">
       <c r="A782" s="24"/>
       <c r="G782" s="22"/>
       <c r="H782" s="23"/>
-      <c r="I782" s="4"/>
+      <c r="I782" s="8"/>
     </row>
     <row r="783" ht="15.75" customHeight="1">
       <c r="A783" s="24"/>
       <c r="G783" s="22"/>
       <c r="H783" s="23"/>
-      <c r="I783" s="4"/>
+      <c r="I783" s="8"/>
     </row>
     <row r="784" ht="15.75" customHeight="1">
       <c r="A784" s="24"/>
       <c r="G784" s="22"/>
       <c r="H784" s="23"/>
-      <c r="I784" s="4"/>
+      <c r="I784" s="8"/>
     </row>
     <row r="785" ht="15.75" customHeight="1">
       <c r="A785" s="24"/>
       <c r="G785" s="22"/>
       <c r="H785" s="23"/>
-      <c r="I785" s="4"/>
+      <c r="I785" s="8"/>
     </row>
     <row r="786" ht="15.75" customHeight="1">
       <c r="A786" s="24"/>
       <c r="G786" s="22"/>
       <c r="H786" s="23"/>
-      <c r="I786" s="4"/>
+      <c r="I786" s="8"/>
     </row>
     <row r="787" ht="15.75" customHeight="1">
       <c r="A787" s="24"/>
       <c r="G787" s="22"/>
       <c r="H787" s="23"/>
-      <c r="I787" s="4"/>
+      <c r="I787" s="8"/>
     </row>
     <row r="788" ht="15.75" customHeight="1">
       <c r="A788" s="24"/>
       <c r="G788" s="22"/>
       <c r="H788" s="23"/>
-      <c r="I788" s="4"/>
+      <c r="I788" s="8"/>
     </row>
     <row r="789" ht="15.75" customHeight="1">
       <c r="A789" s="24"/>
       <c r="G789" s="22"/>
       <c r="H789" s="23"/>
-      <c r="I789" s="4"/>
+      <c r="I789" s="8"/>
     </row>
     <row r="790" ht="15.75" customHeight="1">
       <c r="A790" s="24"/>
       <c r="G790" s="22"/>
       <c r="H790" s="23"/>
-      <c r="I790" s="4"/>
+      <c r="I790" s="8"/>
     </row>
     <row r="791" ht="15.75" customHeight="1">
       <c r="A791" s="24"/>
       <c r="G791" s="22"/>
       <c r="H791" s="23"/>
-      <c r="I791" s="4"/>
+      <c r="I791" s="8"/>
     </row>
     <row r="792" ht="15.75" customHeight="1">
       <c r="A792" s="24"/>
       <c r="G792" s="22"/>
       <c r="H792" s="23"/>
-      <c r="I792" s="4"/>
+      <c r="I792" s="8"/>
     </row>
     <row r="793" ht="15.75" customHeight="1">
       <c r="A793" s="24"/>
       <c r="G793" s="22"/>
       <c r="H793" s="23"/>
-      <c r="I793" s="4"/>
+      <c r="I793" s="8"/>
     </row>
     <row r="794" ht="15.75" customHeight="1">
       <c r="A794" s="24"/>
       <c r="G794" s="22"/>
       <c r="H794" s="23"/>
-      <c r="I794" s="4"/>
+      <c r="I794" s="8"/>
     </row>
     <row r="795" ht="15.75" customHeight="1">
       <c r="A795" s="24"/>
       <c r="G795" s="22"/>
       <c r="H795" s="23"/>
-      <c r="I795" s="4"/>
+      <c r="I795" s="8"/>
     </row>
     <row r="796" ht="15.75" customHeight="1">
       <c r="A796" s="24"/>
       <c r="G796" s="22"/>
       <c r="H796" s="23"/>
-      <c r="I796" s="4"/>
+      <c r="I796" s="8"/>
     </row>
     <row r="797" ht="15.75" customHeight="1">
       <c r="A797" s="24"/>
       <c r="G797" s="22"/>
       <c r="H797" s="23"/>
-      <c r="I797" s="4"/>
+      <c r="I797" s="8"/>
     </row>
     <row r="798" ht="15.75" customHeight="1">
       <c r="A798" s="24"/>
       <c r="G798" s="22"/>
       <c r="H798" s="23"/>
-      <c r="I798" s="4"/>
+      <c r="I798" s="8"/>
     </row>
     <row r="799" ht="15.75" customHeight="1">
       <c r="A799" s="24"/>
       <c r="G799" s="22"/>
       <c r="H799" s="23"/>
-      <c r="I799" s="4"/>
+      <c r="I799" s="8"/>
     </row>
     <row r="800" ht="15.75" customHeight="1">
       <c r="A800" s="24"/>
       <c r="G800" s="22"/>
       <c r="H800" s="23"/>
-      <c r="I800" s="4"/>
+      <c r="I800" s="8"/>
     </row>
     <row r="801" ht="15.75" customHeight="1">
       <c r="A801" s="24"/>
       <c r="G801" s="22"/>
       <c r="H801" s="23"/>
-      <c r="I801" s="4"/>
+      <c r="I801" s="8"/>
     </row>
     <row r="802" ht="15.75" customHeight="1">
       <c r="A802" s="24"/>
       <c r="G802" s="22"/>
       <c r="H802" s="23"/>
-      <c r="I802" s="4"/>
+      <c r="I802" s="8"/>
     </row>
     <row r="803" ht="15.75" customHeight="1">
       <c r="A803" s="24"/>
       <c r="G803" s="22"/>
       <c r="H803" s="23"/>
-      <c r="I803" s="4"/>
+      <c r="I803" s="8"/>
     </row>
     <row r="804" ht="15.75" customHeight="1">
       <c r="A804" s="24"/>
       <c r="G804" s="22"/>
       <c r="H804" s="23"/>
-      <c r="I804" s="4"/>
+      <c r="I804" s="8"/>
     </row>
     <row r="805" ht="15.75" customHeight="1">
       <c r="A805" s="24"/>
       <c r="G805" s="22"/>
       <c r="H805" s="23"/>
-      <c r="I805" s="4"/>
+      <c r="I805" s="8"/>
     </row>
     <row r="806" ht="15.75" customHeight="1">
       <c r="A806" s="24"/>
       <c r="G806" s="22"/>
       <c r="H806" s="23"/>
-      <c r="I806" s="4"/>
+      <c r="I806" s="8"/>
     </row>
     <row r="807" ht="15.75" customHeight="1">
       <c r="A807" s="24"/>
       <c r="G807" s="22"/>
       <c r="H807" s="23"/>
-      <c r="I807" s="4"/>
+      <c r="I807" s="8"/>
     </row>
     <row r="808" ht="15.75" customHeight="1">
       <c r="A808" s="24"/>
       <c r="G808" s="22"/>
       <c r="H808" s="23"/>
-      <c r="I808" s="4"/>
+      <c r="I808" s="8"/>
     </row>
     <row r="809" ht="15.75" customHeight="1">
       <c r="A809" s="24"/>
       <c r="G809" s="22"/>
       <c r="H809" s="23"/>
-      <c r="I809" s="4"/>
+      <c r="I809" s="8"/>
     </row>
     <row r="810" ht="15.75" customHeight="1">
       <c r="A810" s="24"/>
       <c r="G810" s="22"/>
       <c r="H810" s="23"/>
-      <c r="I810" s="4"/>
+      <c r="I810" s="8"/>
     </row>
     <row r="811" ht="15.75" customHeight="1">
       <c r="A811" s="24"/>
       <c r="G811" s="22"/>
       <c r="H811" s="23"/>
-      <c r="I811" s="4"/>
+      <c r="I811" s="8"/>
     </row>
     <row r="812" ht="15.75" customHeight="1">
       <c r="A812" s="24"/>
       <c r="G812" s="22"/>
       <c r="H812" s="23"/>
-      <c r="I812" s="4"/>
+      <c r="I812" s="8"/>
     </row>
     <row r="813" ht="15.75" customHeight="1">
       <c r="A813" s="24"/>
       <c r="G813" s="22"/>
       <c r="H813" s="23"/>
-      <c r="I813" s="4"/>
+      <c r="I813" s="8"/>
     </row>
     <row r="814" ht="15.75" customHeight="1">
       <c r="A814" s="24"/>
       <c r="G814" s="22"/>
       <c r="H814" s="23"/>
-      <c r="I814" s="4"/>
+      <c r="I814" s="8"/>
     </row>
     <row r="815" ht="15.75" customHeight="1">
       <c r="A815" s="24"/>
       <c r="G815" s="22"/>
       <c r="H815" s="23"/>
-      <c r="I815" s="4"/>
+      <c r="I815" s="8"/>
     </row>
     <row r="816" ht="15.75" customHeight="1">
       <c r="A816" s="24"/>
       <c r="G816" s="22"/>
       <c r="H816" s="23"/>
-      <c r="I816" s="4"/>
+      <c r="I816" s="8"/>
     </row>
     <row r="817" ht="15.75" customHeight="1">
       <c r="A817" s="24"/>
       <c r="G817" s="22"/>
       <c r="H817" s="23"/>
-      <c r="I817" s="4"/>
+      <c r="I817" s="8"/>
     </row>
     <row r="818" ht="15.75" customHeight="1">
       <c r="A818" s="24"/>
       <c r="G818" s="22"/>
       <c r="H818" s="23"/>
-      <c r="I818" s="4"/>
+      <c r="I818" s="8"/>
     </row>
     <row r="819" ht="15.75" customHeight="1">
       <c r="A819" s="24"/>
       <c r="G819" s="22"/>
       <c r="H819" s="23"/>
-      <c r="I819" s="4"/>
+      <c r="I819" s="8"/>
     </row>
     <row r="820" ht="15.75" customHeight="1">
       <c r="A820" s="24"/>
       <c r="G820" s="22"/>
       <c r="H820" s="23"/>
-      <c r="I820" s="4"/>
+      <c r="I820" s="8"/>
     </row>
     <row r="821" ht="15.75" customHeight="1">
       <c r="A821" s="24"/>
       <c r="G821" s="22"/>
       <c r="H821" s="23"/>
-      <c r="I821" s="4"/>
+      <c r="I821" s="8"/>
     </row>
     <row r="822" ht="15.75" customHeight="1">
       <c r="A822" s="24"/>
       <c r="G822" s="22"/>
       <c r="H822" s="23"/>
-      <c r="I822" s="4"/>
+      <c r="I822" s="8"/>
     </row>
     <row r="823" ht="15.75" customHeight="1">
       <c r="A823" s="24"/>
       <c r="G823" s="22"/>
       <c r="H823" s="23"/>
-      <c r="I823" s="4"/>
+      <c r="I823" s="8"/>
     </row>
     <row r="824" ht="15.75" customHeight="1">
       <c r="A824" s="24"/>
       <c r="G824" s="22"/>
       <c r="H824" s="23"/>
-      <c r="I824" s="4"/>
+      <c r="I824" s="8"/>
     </row>
     <row r="825" ht="15.75" customHeight="1">
       <c r="A825" s="24"/>
       <c r="G825" s="22"/>
       <c r="H825" s="23"/>
-      <c r="I825" s="4"/>
+      <c r="I825" s="8"/>
     </row>
     <row r="826" ht="15.75" customHeight="1">
       <c r="A826" s="24"/>
       <c r="G826" s="22"/>
       <c r="H826" s="23"/>
-      <c r="I826" s="4"/>
+      <c r="I826" s="8"/>
     </row>
     <row r="827" ht="15.75" customHeight="1">
       <c r="A827" s="24"/>
       <c r="G827" s="22"/>
       <c r="H827" s="23"/>
-      <c r="I827" s="4"/>
+      <c r="I827" s="8"/>
     </row>
     <row r="828" ht="15.75" customHeight="1">
       <c r="A828" s="24"/>
       <c r="G828" s="22"/>
       <c r="H828" s="23"/>
-      <c r="I828" s="4"/>
+      <c r="I828" s="8"/>
     </row>
     <row r="829" ht="15.75" customHeight="1">
       <c r="A829" s="24"/>
       <c r="G829" s="22"/>
       <c r="H829" s="23"/>
-      <c r="I829" s="4"/>
+      <c r="I829" s="8"/>
     </row>
     <row r="830" ht="15.75" customHeight="1">
       <c r="A830" s="24"/>
       <c r="G830" s="22"/>
       <c r="H830" s="23"/>
-      <c r="I830" s="4"/>
+      <c r="I830" s="8"/>
     </row>
     <row r="831" ht="15.75" customHeight="1">
       <c r="A831" s="24"/>
       <c r="G831" s="22"/>
       <c r="H831" s="23"/>
-      <c r="I831" s="4"/>
+      <c r="I831" s="8"/>
     </row>
     <row r="832" ht="15.75" customHeight="1">
       <c r="A832" s="24"/>
       <c r="G832" s="22"/>
       <c r="H832" s="23"/>
-      <c r="I832" s="4"/>
     </row>
     <row r="833" ht="15.75" customHeight="1">
       <c r="A833" s="24"/>
@@ -7888,9 +7856,7 @@
       <c r="G982" s="22"/>
       <c r="H982" s="23"/>
     </row>
-    <row r="983" ht="15.75" customHeight="1">
-      <c r="A983" s="24"/>
-      <c r="G983" s="22"/>
+    <row r="983">
       <c r="H983" s="23"/>
     </row>
     <row r="984">
@@ -7902,17 +7868,14 @@
     <row r="986">
       <c r="H986" s="23"/>
     </row>
-    <row r="987">
-      <c r="H987" s="23"/>
-    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$I$18">
-    <sortState ref="A1:I18">
-      <sortCondition descending="1" ref="G1:G18"/>
-      <sortCondition descending="1" ref="I1:I18"/>
+  <autoFilter ref="$A$1:$I$17">
+    <sortState ref="A1:I17">
+      <sortCondition descending="1" ref="G1:G17"/>
+      <sortCondition descending="1" ref="I1:I17"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="G2:G18">
+  <conditionalFormatting sqref="G2:G17">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -7924,7 +7887,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G18">
+  <conditionalFormatting sqref="G2:G17">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -7936,7 +7899,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:H18">
+  <conditionalFormatting sqref="G2:H17">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7946,7 +7909,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I18">
+  <conditionalFormatting sqref="I2:I17">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -7959,25 +7922,25 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Допустимо 1–5 - Введите сложность от 1 до 5" sqref="I2:I832">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Допустимо 1–5 - Введите сложность от 1 до 5" sqref="I2:I831">
       <formula1>1.0</formula1>
       <formula2>5.0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C18">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C17">
       <formula1>"Не влияет,Небольшое улучшение,Второстепенная функция,Важная система,Нужно для Vertical Slice,Без этого релиз невозможен"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E18">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E17">
       <formula1>"Нет нового,Мелкий объект,Небольшой контент,Новая механика,Крупная система,Фундаментальная механика"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D18">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D17">
       <formula1>"Не влияет,Косметика,Небольшое улучшение,Заметно лучше,Исправляет серьёзную проблему,Исправляет критичную проблему"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F18">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F17">
       <formula1>"Не влияет,Слабое,Небольшое,Улучшает цикл,Сильно повышает интерес,Критично для удержания"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="A5"/>
+    <hyperlink r:id="rId1" ref="A4"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
@@ -7997,158 +7960,158 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B3" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B4" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="s">
+      <c r="B5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="8" t="s">
         <v>50</v>
       </c>
     </row>
